--- a/research/traditional_assets/database/data/italy/italy_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_rubber_tires.xlsx
@@ -650,10 +650,10 @@
         <v>0.08279413026688406</v>
       </c>
       <c r="X2">
-        <v>0.1452859116915663</v>
+        <v>0.1452672782222516</v>
       </c>
       <c r="Y2">
-        <v>-0.06249178142468226</v>
+        <v>-0.06247314795536751</v>
       </c>
       <c r="Z2">
         <v>0.7999400461024799</v>
@@ -662,10 +662,10 @@
         <v>0.07590628585604864</v>
       </c>
       <c r="AB2">
-        <v>0.1084754534306975</v>
+        <v>0.1084650546733469</v>
       </c>
       <c r="AC2">
-        <v>-0.03256916757464889</v>
+        <v>-0.03255876881729823</v>
       </c>
       <c r="AD2">
         <v>4487.9</v>
@@ -787,10 +787,10 @@
         <v>0.08279413026688406</v>
       </c>
       <c r="X3">
-        <v>0.1452859116915663</v>
+        <v>0.1452672782222516</v>
       </c>
       <c r="Y3">
-        <v>-0.06249178142468226</v>
+        <v>-0.06247314795536751</v>
       </c>
       <c r="Z3">
         <v>0.7999400461024799</v>
@@ -799,10 +799,10 @@
         <v>0.07590628585604864</v>
       </c>
       <c r="AB3">
-        <v>0.1084754534306975</v>
+        <v>0.1084650546733469</v>
       </c>
       <c r="AC3">
-        <v>-0.03256916757464889</v>
+        <v>-0.03255876881729823</v>
       </c>
       <c r="AD3">
         <v>4487.9</v>
@@ -1139,7 +1139,7 @@
         <v>3.28159126365055</v>
       </c>
       <c r="F2">
-        <v>6.76945044588288</v>
+        <v>6.86146718910247</v>
       </c>
       <c r="G2">
         <v>3.04822386741832</v>
@@ -1157,13 +1157,13 @@
         <v>5667.3</v>
       </c>
       <c r="L2">
-        <v>8563.62922306665</v>
+        <v>8577.82619715388</v>
       </c>
       <c r="M2">
         <v>9290.200000000001</v>
       </c>
       <c r="N2">
-        <v>9425.01322306665</v>
+        <v>9439.21019715388</v>
       </c>
       <c r="O2">
         <v>4487.9</v>
@@ -1172,16 +1172,16 @@
         <v>1726.384</v>
       </c>
       <c r="Q2">
-        <v>0.108475453430698</v>
+        <v>0.108465054673347</v>
       </c>
       <c r="R2">
-        <v>0.107221453117129</v>
+        <v>0.107081095179188</v>
       </c>
       <c r="S2">
         <v>0.0619913717662617</v>
       </c>
       <c r="T2">
-        <v>0.0566713717662617</v>
+        <v>0.0559113717662617</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.145285911691566</v>
+        <v>0.145267278222252</v>
       </c>
       <c r="X2">
-        <v>0.117575084237186</v>
+        <v>0.117561640938462</v>
       </c>
       <c r="Y2">
         <v>1.36920452470844</v>
@@ -1236,7 +1236,7 @@
         <v>5667.3</v>
       </c>
       <c r="AK2">
-        <v>0.07265964280446037</v>
+        <v>0.07264603383006794</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1079072976614515</v>
+        <v>0.1078956651156416</v>
       </c>
       <c r="C2">
-        <v>10215.79950050499</v>
+        <v>10215.9325301295</v>
       </c>
       <c r="D2">
-        <v>9350.799500504989</v>
+        <v>9350.932530129496</v>
       </c>
       <c r="E2">
         <v>-4487.9</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1079072976614515</v>
+        <v>0.1078956651156416</v>
       </c>
       <c r="T2">
         <v>0.8547702034345667</v>
       </c>
       <c r="U2">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V2">
         <v>0.24</v>
       </c>
       <c r="W2">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1078585938647267</v>
+        <v>0.1078363492370267</v>
       </c>
       <c r="C3">
-        <v>10119.47905836423</v>
+        <v>10120.75301137926</v>
       </c>
       <c r="D3">
-        <v>9356.031058364233</v>
+        <v>9357.305011379261</v>
       </c>
       <c r="E3">
         <v>-4386.348</v>
@@ -1539,37 +1539,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M3">
-        <v>7.460781149483429</v>
+        <v>7.31860834948343</v>
       </c>
       <c r="N3">
-        <v>863.9861576260267</v>
+        <v>864.1283304260268</v>
       </c>
       <c r="O3">
-        <v>207.3566778302464</v>
+        <v>207.3907993022464</v>
       </c>
       <c r="P3">
-        <v>656.6294797957803</v>
+        <v>656.7375311237804</v>
       </c>
       <c r="Q3">
-        <v>1287.52947979578</v>
+        <v>1287.63753112378</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1083840809566304</v>
+        <v>0.1083723591104687</v>
       </c>
       <c r="T3">
         <v>0.8613320757033573</v>
       </c>
       <c r="U3">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V3">
         <v>0.24</v>
       </c>
       <c r="W3">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>116.8037128171019</v>
+        <v>119.0727659087017</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1078098900680018</v>
+        <v>0.1077770333584118</v>
       </c>
       <c r="C4">
-        <v>10023.16447337369</v>
+        <v>10025.58218399964</v>
       </c>
       <c r="D4">
-        <v>9361.268473373688</v>
+        <v>9363.68618399964</v>
       </c>
       <c r="E4">
         <v>-4284.795999999999</v>
@@ -1621,37 +1621,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M4">
-        <v>14.92156229896686</v>
+        <v>14.63721669896686</v>
       </c>
       <c r="N4">
-        <v>856.5253764765433</v>
+        <v>856.8097220765433</v>
       </c>
       <c r="O4">
-        <v>205.5660903543704</v>
+        <v>205.6343332983704</v>
       </c>
       <c r="P4">
-        <v>650.9592861221729</v>
+        <v>651.1753887781729</v>
       </c>
       <c r="Q4">
-        <v>1281.859286122173</v>
+        <v>1282.075388778173</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1088705945231394</v>
+        <v>0.1088587815541699</v>
       </c>
       <c r="T4">
         <v>0.8680278637327354</v>
       </c>
       <c r="U4">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V4">
         <v>0.24</v>
       </c>
       <c r="W4">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>58.40185640855097</v>
+        <v>59.53638295435085</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1077611862712769</v>
+        <v>0.1077177174797968</v>
       </c>
       <c r="C5">
-        <v>9926.855755375191</v>
+        <v>9930.420065783888</v>
       </c>
       <c r="D5">
-        <v>9366.511755375192</v>
+        <v>9370.076065783889</v>
       </c>
       <c r="E5">
         <v>-4183.244</v>
@@ -1703,37 +1703,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M5">
-        <v>22.38234344845029</v>
+        <v>21.95582504845029</v>
       </c>
       <c r="N5">
-        <v>849.0645953270598</v>
+        <v>849.4911137270599</v>
       </c>
       <c r="O5">
-        <v>203.7755028784943</v>
+        <v>203.8778672944944</v>
       </c>
       <c r="P5">
-        <v>645.2890924485655</v>
+        <v>645.6132464325656</v>
       </c>
       <c r="Q5">
-        <v>1276.189092448566</v>
+        <v>1276.513246432566</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1093671392972052</v>
+        <v>0.1093552333266072</v>
       </c>
       <c r="T5">
         <v>0.8748617092472555</v>
       </c>
       <c r="U5">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V5">
         <v>0.24</v>
       </c>
       <c r="W5">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.93457093903397</v>
+        <v>39.69092196956724</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1077124824745521</v>
+        <v>0.1076584016011819</v>
       </c>
       <c r="C6">
-        <v>9830.552914232641</v>
+        <v>9835.266674573861</v>
       </c>
       <c r="D6">
-        <v>9371.760914232642</v>
+        <v>9376.474674573861</v>
       </c>
       <c r="E6">
         <v>-4081.692</v>
@@ -1785,37 +1785,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M6">
-        <v>29.84312459793372</v>
+        <v>29.27443339793372</v>
       </c>
       <c r="N6">
-        <v>841.6038141775764</v>
+        <v>842.1725053775764</v>
       </c>
       <c r="O6">
-        <v>201.9849154026183</v>
+        <v>202.1214012906183</v>
       </c>
       <c r="P6">
-        <v>639.6188987749581</v>
+        <v>640.051104086958</v>
       </c>
       <c r="Q6">
-        <v>1270.518898774958</v>
+        <v>1270.951104086958</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1098740287540642</v>
+        <v>0.1098620278443036</v>
       </c>
       <c r="T6">
         <v>0.881837926543328</v>
       </c>
       <c r="U6">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V6">
         <v>0.24</v>
       </c>
       <c r="W6">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.20092820427548</v>
+        <v>29.76819147717542</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1076637786778272</v>
+        <v>0.107599085722567</v>
       </c>
       <c r="C7">
-        <v>9734.255959832068</v>
+        <v>9740.122028260192</v>
       </c>
       <c r="D7">
-        <v>9377.015959832068</v>
+        <v>9382.882028260192</v>
       </c>
       <c r="E7">
         <v>-3980.139999999999</v>
@@ -1867,37 +1867,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M7">
-        <v>37.30390574741715</v>
+        <v>36.59304174741715</v>
       </c>
       <c r="N7">
-        <v>834.143033028093</v>
+        <v>834.853897028093</v>
       </c>
       <c r="O7">
-        <v>200.1943279267423</v>
+        <v>200.3649352867423</v>
       </c>
       <c r="P7">
-        <v>633.9487051013507</v>
+        <v>634.4889617413507</v>
       </c>
       <c r="Q7">
-        <v>1264.848705101351</v>
+        <v>1265.388961741351</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1103915895679096</v>
+        <v>0.1103794917202673</v>
       </c>
       <c r="T7">
         <v>0.8889610115719494</v>
       </c>
       <c r="U7">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V7">
         <v>0.24</v>
       </c>
       <c r="W7">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.36074256342039</v>
+        <v>23.81455318174034</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1076150748811023</v>
+        <v>0.1075397698439521</v>
       </c>
       <c r="C8">
-        <v>9637.964902081669</v>
+        <v>9644.986144782446</v>
       </c>
       <c r="D8">
-        <v>9382.276902081669</v>
+        <v>9389.298144782446</v>
       </c>
       <c r="E8">
         <v>-3878.588</v>
@@ -1949,37 +1949,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M8">
-        <v>44.76468689690058</v>
+        <v>43.91165009690057</v>
       </c>
       <c r="N8">
-        <v>826.6822518786096</v>
+        <v>827.5352886786096</v>
       </c>
       <c r="O8">
-        <v>198.4037404508663</v>
+        <v>198.6084692828663</v>
       </c>
       <c r="P8">
-        <v>628.2785114277433</v>
+        <v>628.9268193957433</v>
       </c>
       <c r="Q8">
-        <v>1259.178511427743</v>
+        <v>1259.826819395743</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1109201623139645</v>
+        <v>0.1109079654659323</v>
       </c>
       <c r="T8">
         <v>0.8962356516011797</v>
       </c>
       <c r="U8">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.46728546951699</v>
+        <v>19.84546098478362</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1075663710843775</v>
+        <v>0.1074804539653371</v>
       </c>
       <c r="C9">
-        <v>9541.679750911906</v>
+        <v>9549.859042129292</v>
       </c>
       <c r="D9">
-        <v>9387.543750911906</v>
+        <v>9395.723042129292</v>
       </c>
       <c r="E9">
         <v>-3777.036</v>
@@ -2031,37 +2031,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M9">
-        <v>52.22546804638402</v>
+        <v>51.23025844638401</v>
       </c>
       <c r="N9">
-        <v>819.2214707291262</v>
+        <v>820.2166803291261</v>
       </c>
       <c r="O9">
-        <v>196.6131529749903</v>
+        <v>196.8520032789903</v>
       </c>
       <c r="P9">
-        <v>622.6083177541359</v>
+        <v>623.3646770501359</v>
       </c>
       <c r="Q9">
-        <v>1253.508317754136</v>
+        <v>1254.264677050136</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1114601022158485</v>
+        <v>0.1114478042383858</v>
       </c>
       <c r="T9">
         <v>0.9036667355020064</v>
       </c>
       <c r="U9">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V9">
         <v>0.24</v>
       </c>
       <c r="W9">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.68624468815742</v>
+        <v>17.01039512981453</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1075176672876526</v>
+        <v>0.1074211380867222</v>
       </c>
       <c r="C10">
-        <v>9445.400516275546</v>
+        <v>9454.740738338669</v>
       </c>
       <c r="D10">
-        <v>9392.816516275545</v>
+        <v>9402.156738338668</v>
       </c>
       <c r="E10">
         <v>-3675.483999999999</v>
@@ -2113,37 +2113,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M10">
-        <v>59.68624919586743</v>
+        <v>58.54886679586744</v>
       </c>
       <c r="N10">
-        <v>811.7606895796428</v>
+        <v>812.8980719796427</v>
       </c>
       <c r="O10">
-        <v>194.8225654991143</v>
+        <v>195.0955372751143</v>
       </c>
       <c r="P10">
-        <v>616.9381240805285</v>
+        <v>617.8025347045285</v>
       </c>
       <c r="Q10">
-        <v>1247.838124080528</v>
+        <v>1248.702534704528</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1120117799416866</v>
+        <v>0.1119993786363275</v>
       </c>
       <c r="T10">
         <v>0.9112593647050249</v>
       </c>
       <c r="U10">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.60046410213774</v>
+        <v>14.88409573858771</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1074689634909277</v>
+        <v>0.1073618222081073</v>
       </c>
       <c r="C11">
-        <v>9349.127208147729</v>
+        <v>9359.631251497953</v>
       </c>
       <c r="D11">
-        <v>9398.09520814773</v>
+        <v>9408.599251497953</v>
       </c>
       <c r="E11">
         <v>-3573.932</v>
@@ -2195,37 +2195,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M11">
-        <v>67.14703034535087</v>
+        <v>65.86747514535087</v>
       </c>
       <c r="N11">
-        <v>804.2999084301592</v>
+        <v>805.5794636301592</v>
       </c>
       <c r="O11">
-        <v>193.0319780232382</v>
+        <v>193.3390712712382</v>
       </c>
       <c r="P11">
-        <v>611.2679304069211</v>
+        <v>612.2403923589211</v>
       </c>
       <c r="Q11">
-        <v>1242.167930406921</v>
+        <v>1243.140392358921</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1125755824527079</v>
+        <v>0.1125630755485096</v>
       </c>
       <c r="T11">
         <v>0.9190188648795384</v>
       </c>
       <c r="U11">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.97819031301132</v>
+        <v>13.23030732318908</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1074202596942029</v>
+        <v>0.1073025063294924</v>
       </c>
       <c r="C12">
-        <v>9252.859836526033</v>
+        <v>9264.53059974413</v>
       </c>
       <c r="D12">
-        <v>9403.379836526034</v>
+        <v>9415.050599744131</v>
       </c>
       <c r="E12">
         <v>-3472.38</v>
@@ -2277,37 +2277,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M12">
-        <v>74.60781149483429</v>
+        <v>73.18608349483429</v>
       </c>
       <c r="N12">
-        <v>796.8391272806758</v>
+        <v>798.2608552806759</v>
       </c>
       <c r="O12">
-        <v>191.2413905473622</v>
+        <v>191.5826052673622</v>
       </c>
       <c r="P12">
-        <v>605.5977367333137</v>
+        <v>606.6782500133137</v>
       </c>
       <c r="Q12">
-        <v>1236.497736733314</v>
+        <v>1237.578250013314</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1131519139084186</v>
+        <v>0.1131392990587402</v>
       </c>
       <c r="T12">
         <v>0.9269507983912635</v>
       </c>
       <c r="U12">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.68037128171019</v>
+        <v>11.90727659087017</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.107371555897478</v>
+        <v>0.1072431904508774</v>
       </c>
       <c r="C13">
-        <v>9156.598411430537</v>
+        <v>9169.438801263967</v>
       </c>
       <c r="D13">
-        <v>9408.670411430538</v>
+        <v>9421.510801263967</v>
       </c>
       <c r="E13">
         <v>-3370.828</v>
@@ -2359,37 +2359,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M13">
-        <v>82.06859264431773</v>
+        <v>80.50469184431773</v>
       </c>
       <c r="N13">
-        <v>789.3783461311924</v>
+        <v>790.9422469311924</v>
       </c>
       <c r="O13">
-        <v>189.4508030714862</v>
+        <v>189.8261392634862</v>
       </c>
       <c r="P13">
-        <v>599.9275430597063</v>
+        <v>601.1161076677062</v>
       </c>
       <c r="Q13">
-        <v>1230.827543059706</v>
+        <v>1232.016107667706</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1137411966327969</v>
+        <v>0.1137284714118974</v>
       </c>
       <c r="T13">
         <v>0.935060977599881</v>
       </c>
       <c r="U13">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.61851934700926</v>
+        <v>10.82479690079106</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1073228521007531</v>
+        <v>0.1071838745722625</v>
       </c>
       <c r="C14">
-        <v>9060.342942903884</v>
+        <v>9074.355874294186</v>
       </c>
       <c r="D14">
-        <v>9413.966942903884</v>
+        <v>9427.979874294186</v>
       </c>
       <c r="E14">
         <v>-3269.276</v>
@@ -2441,37 +2441,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M14">
-        <v>89.52937379380116</v>
+        <v>87.82330019380115</v>
       </c>
       <c r="N14">
-        <v>781.917564981709</v>
+        <v>783.623638581709</v>
       </c>
       <c r="O14">
-        <v>187.6602155956102</v>
+        <v>188.0696732596101</v>
       </c>
       <c r="P14">
-        <v>594.2573493860989</v>
+        <v>595.5539653220989</v>
       </c>
       <c r="Q14">
-        <v>1225.157349386099</v>
+        <v>1226.453965322099</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1143438721463656</v>
+        <v>0.1143310340458081</v>
       </c>
       <c r="T14">
         <v>0.9433554790632398</v>
       </c>
       <c r="U14">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.733642734758494</v>
+        <v>9.922730492391809</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1072741483040283</v>
+        <v>0.1071245586936476</v>
       </c>
       <c r="C15">
-        <v>8964.093441011331</v>
+        <v>8979.281837121614</v>
       </c>
       <c r="D15">
-        <v>9419.269441011331</v>
+        <v>9434.457837121614</v>
       </c>
       <c r="E15">
         <v>-3167.723999999999</v>
@@ -2523,37 +2523,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M15">
-        <v>96.99015494328459</v>
+        <v>95.14190854328459</v>
       </c>
       <c r="N15">
-        <v>774.4567838322256</v>
+        <v>776.3050302322256</v>
       </c>
       <c r="O15">
-        <v>185.8696281197341</v>
+        <v>186.3132072557341</v>
       </c>
       <c r="P15">
-        <v>588.5871557124915</v>
+        <v>589.9918229764914</v>
       </c>
       <c r="Q15">
-        <v>1219.487155712492</v>
+        <v>1220.891822976491</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1149604022694417</v>
+        <v>0.1149474486942915</v>
       </c>
       <c r="T15">
         <v>0.9518406587211589</v>
       </c>
       <c r="U15">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.984900985930917</v>
+        <v>9.159443531438592</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1073424845073034</v>
+        <v>0.1072248428150327</v>
       </c>
       <c r="C16">
-        <v>8855.103204030511</v>
+        <v>8866.782871685522</v>
       </c>
       <c r="D16">
-        <v>9411.831204030512</v>
+        <v>9423.510871685523</v>
       </c>
       <c r="E16">
         <v>-3066.172</v>
@@ -2605,37 +2605,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M16">
-        <v>106.014836892768</v>
+        <v>104.593108892768</v>
       </c>
       <c r="N16">
-        <v>765.4321018827421</v>
+        <v>766.8538298827422</v>
       </c>
       <c r="O16">
-        <v>183.7037044518581</v>
+        <v>184.0449191718581</v>
       </c>
       <c r="P16">
-        <v>581.728397430884</v>
+        <v>582.808910710884</v>
       </c>
       <c r="Q16">
-        <v>1212.628397430884</v>
+        <v>1213.708910710884</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1155912703023567</v>
+        <v>0.1155781985671582</v>
       </c>
       <c r="T16">
         <v>0.9605231681385642</v>
       </c>
       <c r="U16">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.220046970000643</v>
+        <v>8.331781586767285</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1073021407105785</v>
+        <v>0.1071769269364177</v>
       </c>
       <c r="C17">
-        <v>8757.941111432643</v>
+        <v>8770.458174474114</v>
       </c>
       <c r="D17">
-        <v>9416.221111432644</v>
+        <v>9428.738174474114</v>
       </c>
       <c r="E17">
         <v>-2964.62</v>
@@ -2687,37 +2687,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M17">
-        <v>113.5873252422514</v>
+        <v>112.0640452422514</v>
       </c>
       <c r="N17">
-        <v>757.8596135332588</v>
+        <v>759.3828935332588</v>
       </c>
       <c r="O17">
-        <v>181.8863072479821</v>
+        <v>182.2518944479821</v>
       </c>
       <c r="P17">
-        <v>575.9733062852766</v>
+        <v>577.1309990852767</v>
       </c>
       <c r="Q17">
-        <v>1206.873306285277</v>
+        <v>1208.030999085277</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1162369822889874</v>
+        <v>0.1162237896135041</v>
       </c>
       <c r="T17">
         <v>0.9694099718952026</v>
       </c>
       <c r="U17">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.672043838667269</v>
+        <v>7.776329480982803</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1072617969138537</v>
+        <v>0.1071290110578028</v>
       </c>
       <c r="C18">
-        <v>8660.783115865283</v>
+        <v>8674.139279741305</v>
       </c>
       <c r="D18">
-        <v>9420.615115865283</v>
+        <v>9433.971279741305</v>
       </c>
       <c r="E18">
         <v>-2863.067999999999</v>
@@ -2769,37 +2769,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M18">
-        <v>121.1598135917349</v>
+        <v>119.5349815917348</v>
       </c>
       <c r="N18">
-        <v>750.2871251837753</v>
+        <v>751.9119571837753</v>
       </c>
       <c r="O18">
-        <v>180.0689100441061</v>
+        <v>180.4588697241061</v>
       </c>
       <c r="P18">
-        <v>570.2182151396692</v>
+        <v>571.4530874596692</v>
       </c>
       <c r="Q18">
-        <v>1201.118215139669</v>
+        <v>1202.353087459669</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1168980683705379</v>
+        <v>0.1168847518752393</v>
       </c>
       <c r="T18">
         <v>0.9785083662174755</v>
       </c>
       <c r="U18">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.192541098750564</v>
+        <v>7.290308888421376</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1072214531171288</v>
+        <v>0.1070810951791879</v>
       </c>
       <c r="C19">
-        <v>8563.62922306665</v>
+        <v>8577.826197153881</v>
       </c>
       <c r="D19">
-        <v>9425.01322306665</v>
+        <v>9439.210197153881</v>
       </c>
       <c r="E19">
         <v>-2761.516</v>
@@ -2851,37 +2851,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M19">
-        <v>128.7323019412183</v>
+        <v>127.0059179412183</v>
       </c>
       <c r="N19">
-        <v>742.7146368342919</v>
+        <v>744.4410208342919</v>
       </c>
       <c r="O19">
-        <v>178.25151284023</v>
+        <v>178.66584500023</v>
       </c>
       <c r="P19">
-        <v>564.4631239940619</v>
+        <v>565.7751758340619</v>
       </c>
       <c r="Q19">
-        <v>1195.363123994062</v>
+        <v>1196.675175834062</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1175750842371859</v>
+        <v>0.1175616409384619</v>
       </c>
       <c r="T19">
         <v>0.9878259989571523</v>
       </c>
       <c r="U19">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.769450445882884</v>
+        <v>6.861467189102471</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1074820693204039</v>
+        <v>0.107265739300573</v>
       </c>
       <c r="C20">
-        <v>8433.738168038988</v>
+        <v>8456.11792030656</v>
       </c>
       <c r="D20">
-        <v>9396.674168038988</v>
+        <v>9419.05392030656</v>
       </c>
       <c r="E20">
         <v>-2659.963999999999</v>
@@ -2933,37 +2933,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M20">
-        <v>140.3262494907017</v>
+        <v>137.5843454907017</v>
       </c>
       <c r="N20">
-        <v>731.1206892848083</v>
+        <v>733.8625932848084</v>
       </c>
       <c r="O20">
-        <v>175.468965428354</v>
+        <v>176.127022388354</v>
       </c>
       <c r="P20">
-        <v>555.6517238564543</v>
+        <v>557.7355708964544</v>
       </c>
       <c r="Q20">
-        <v>1186.551723856454</v>
+        <v>1188.635570896454</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1182686126859473</v>
+        <v>0.1182550394910316</v>
       </c>
       <c r="T20">
         <v>0.9973708910319431</v>
       </c>
       <c r="U20">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.05834337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.210149148418975</v>
+        <v>6.333910559863837</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1074584455236791</v>
+        <v>0.107230743421958</v>
       </c>
       <c r="C21">
-        <v>8334.747962204385</v>
+        <v>8358.379555620919</v>
       </c>
       <c r="D21">
-        <v>9399.235962204384</v>
+        <v>9422.867555620918</v>
       </c>
       <c r="E21">
         <v>-2558.411999999999</v>
@@ -3015,37 +3015,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M21">
-        <v>148.1221522401852</v>
+        <v>145.2279202401851</v>
       </c>
       <c r="N21">
-        <v>723.324786535325</v>
+        <v>726.2190185353249</v>
       </c>
       <c r="O21">
-        <v>173.597948768478</v>
+        <v>174.292564448478</v>
       </c>
       <c r="P21">
-        <v>549.726837766847</v>
+        <v>551.926454086847</v>
       </c>
       <c r="Q21">
-        <v>1180.626837766847</v>
+        <v>1182.826454086847</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1189792652939375</v>
+        <v>0.1189655589955164</v>
       </c>
       <c r="T21">
         <v>1.00715145945426</v>
       </c>
       <c r="U21">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.05834337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.88329919323903</v>
+        <v>6.000546846186793</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1076628217269542</v>
+        <v>0.1071957475433431</v>
       </c>
       <c r="C22">
-        <v>8211.079272018573</v>
+        <v>8260.644280354954</v>
       </c>
       <c r="D22">
-        <v>9377.119272018574</v>
+        <v>9426.684280354955</v>
       </c>
       <c r="E22">
         <v>-2456.86</v>
@@ -3097,45 +3097,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M22">
-        <v>158.9646149896686</v>
+        <v>152.8714949896686</v>
       </c>
       <c r="N22">
-        <v>712.4823237858416</v>
+        <v>718.5754437858416</v>
       </c>
       <c r="O22">
-        <v>170.995757708602</v>
+        <v>172.458106508602</v>
       </c>
       <c r="P22">
-        <v>541.4865660772396</v>
+        <v>546.1173372772396</v>
       </c>
       <c r="Q22">
-        <v>1172.386566077239</v>
+        <v>1177.01733727724</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1197076842171273</v>
+        <v>0.1196938414876135</v>
       </c>
       <c r="T22">
         <v>1.017176542087134</v>
       </c>
       <c r="U22">
-        <v>0.07826759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.05948337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.482018365106896</v>
+        <v>5.700519503877453</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1076505979302293</v>
+        <v>0.1072884316647282</v>
       </c>
       <c r="C23">
-        <v>8110.847150471645</v>
+        <v>8148.990695578026</v>
       </c>
       <c r="D23">
-        <v>9378.439150471646</v>
+        <v>9416.582695578027</v>
       </c>
       <c r="E23">
         <v>-2355.308</v>
@@ -3179,37 +3179,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M23">
-        <v>166.912845739152</v>
+        <v>162.221143339152</v>
       </c>
       <c r="N23">
-        <v>704.5340930363582</v>
+        <v>709.2257954363581</v>
       </c>
       <c r="O23">
-        <v>169.088182328726</v>
+        <v>170.2141909047259</v>
       </c>
       <c r="P23">
-        <v>535.4459107076323</v>
+        <v>539.0116045316322</v>
       </c>
       <c r="Q23">
-        <v>1166.345910707632</v>
+        <v>1169.911604531632</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1204545441257144</v>
+        <v>0.120440561511156</v>
       </c>
       <c r="T23">
         <v>1.027455424280335</v>
       </c>
       <c r="U23">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.220969871530378</v>
+        <v>5.371968911312603</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1076383741335045</v>
+        <v>0.1072595157861133</v>
       </c>
       <c r="C24">
-        <v>8010.615400536581</v>
+        <v>8050.587894896553</v>
       </c>
       <c r="D24">
-        <v>9379.759400536581</v>
+        <v>9419.731894896553</v>
       </c>
       <c r="E24">
         <v>-2253.755999999999</v>
@@ -3261,37 +3261,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M24">
-        <v>174.8610764886355</v>
+        <v>169.9459596886354</v>
       </c>
       <c r="N24">
-        <v>696.5858622868747</v>
+        <v>701.5009790868747</v>
       </c>
       <c r="O24">
-        <v>167.1806069488499</v>
+        <v>168.3602349808499</v>
       </c>
       <c r="P24">
-        <v>529.4052553380247</v>
+        <v>533.1407441060248</v>
       </c>
       <c r="Q24">
-        <v>1160.305255338025</v>
+        <v>1164.040744106025</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1212205542883678</v>
+        <v>0.1212064282019689</v>
       </c>
       <c r="T24">
         <v>1.037997867555412</v>
       </c>
       <c r="U24">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.983653059188087</v>
+        <v>5.12778850625294</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1076261503367796</v>
+        <v>0.1072305999074984</v>
       </c>
       <c r="C25">
-        <v>7910.384022370339</v>
+        <v>7952.187201300945</v>
       </c>
       <c r="D25">
-        <v>9381.080022370339</v>
+        <v>9422.883201300945</v>
       </c>
       <c r="E25">
         <v>-2152.203999999999</v>
@@ -3343,37 +3343,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M25">
-        <v>182.8093072381189</v>
+        <v>177.6707760381189</v>
       </c>
       <c r="N25">
-        <v>688.6376315373913</v>
+        <v>693.7761627373912</v>
       </c>
       <c r="O25">
-        <v>165.2730315689739</v>
+        <v>166.5062790569739</v>
       </c>
       <c r="P25">
-        <v>523.3645999684173</v>
+        <v>527.2698836804174</v>
       </c>
       <c r="Q25">
-        <v>1154.264599968417</v>
+        <v>1158.169883680417</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1220064608188824</v>
+        <v>0.1219921875341015</v>
       </c>
       <c r="T25">
         <v>1.048814140525946</v>
       </c>
       <c r="U25">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.766972491397301</v>
+        <v>4.904841179894115</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1076139265400547</v>
+        <v>0.1072016840288834</v>
       </c>
       <c r="C26">
-        <v>7810.153016129974</v>
+        <v>7853.788616906653</v>
       </c>
       <c r="D26">
-        <v>9382.401016129974</v>
+        <v>9426.036616906653</v>
       </c>
       <c r="E26">
         <v>-2050.652</v>
@@ -3425,37 +3425,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M26">
-        <v>190.7575379876023</v>
+        <v>185.3955923876023</v>
       </c>
       <c r="N26">
-        <v>680.6894007879079</v>
+        <v>686.0513463879079</v>
       </c>
       <c r="O26">
-        <v>163.3654561890979</v>
+        <v>164.6523231330979</v>
       </c>
       <c r="P26">
-        <v>517.3239445988099</v>
+        <v>521.39902325481</v>
       </c>
       <c r="Q26">
-        <v>1148.22394459881</v>
+        <v>1152.29902325481</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1228130491001999</v>
+        <v>0.1227986247433956</v>
       </c>
       <c r="T26">
         <v>1.059915052258863</v>
       </c>
       <c r="U26">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.56834863758908</v>
+        <v>4.700472797398528</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1076017027433299</v>
+        <v>0.1071727681502685</v>
       </c>
       <c r="C27">
-        <v>7709.92238197262</v>
+        <v>7755.392143831938</v>
       </c>
       <c r="D27">
-        <v>9383.72238197262</v>
+        <v>9429.192143831939</v>
       </c>
       <c r="E27">
         <v>-1949.099999999999</v>
@@ -3507,37 +3507,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M27">
-        <v>198.7057687370857</v>
+        <v>193.1204087370857</v>
       </c>
       <c r="N27">
-        <v>672.7411700384243</v>
+        <v>678.3265300384244</v>
       </c>
       <c r="O27">
-        <v>161.4578808092218</v>
+        <v>162.7983672092219</v>
       </c>
       <c r="P27">
-        <v>511.2832892292025</v>
+        <v>515.5281628292025</v>
       </c>
       <c r="Q27">
-        <v>1142.183289229203</v>
+        <v>1146.428162829202</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1236411464023526</v>
+        <v>0.1236265669449375</v>
       </c>
       <c r="T27">
         <v>1.071311988304657</v>
       </c>
       <c r="U27">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V27">
         <v>0.24</v>
       </c>
       <c r="W27">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.385614692085516</v>
+        <v>4.512453885502587</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.107866118946605</v>
+        <v>0.1071438522716536</v>
       </c>
       <c r="C28">
-        <v>7579.87036325969</v>
+        <v>7656.99778419792</v>
       </c>
       <c r="D28">
-        <v>9355.222363259691</v>
+        <v>9432.349784197921</v>
       </c>
       <c r="E28">
         <v>-1847.547999999999</v>
@@ -3589,45 +3589,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M28">
-        <v>210.3504922865692</v>
+        <v>200.8452250865691</v>
       </c>
       <c r="N28">
-        <v>661.096446488941</v>
+        <v>670.601713688941</v>
       </c>
       <c r="O28">
-        <v>158.6631471573458</v>
+        <v>160.9444112853458</v>
       </c>
       <c r="P28">
-        <v>502.4332993315951</v>
+        <v>509.6573024035952</v>
       </c>
       <c r="Q28">
-        <v>1133.333299331595</v>
+        <v>1140.557302403595</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1244916247126716</v>
+        <v>0.1244768859627372</v>
       </c>
       <c r="T28">
         <v>1.083016949648986</v>
       </c>
       <c r="U28">
-        <v>0.07966759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.06054737176626167</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.142832894292931</v>
+        <v>4.338897966829411</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1078645351498801</v>
+        <v>0.1073201363930387</v>
       </c>
       <c r="C29">
-        <v>7478.488556922703</v>
+        <v>7536.228184651249</v>
       </c>
       <c r="D29">
-        <v>9355.392556922703</v>
+        <v>9413.132184651249</v>
       </c>
       <c r="E29">
         <v>-1745.995999999999</v>
@@ -3671,37 +3671,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M29">
-        <v>218.4408958360526</v>
+        <v>211.3119454360526</v>
       </c>
       <c r="N29">
-        <v>653.0060429394575</v>
+        <v>660.1349933394575</v>
       </c>
       <c r="O29">
-        <v>156.7214503054698</v>
+        <v>158.4323984014698</v>
       </c>
       <c r="P29">
-        <v>496.2845926339877</v>
+        <v>501.7025949379877</v>
       </c>
       <c r="Q29">
-        <v>1127.184592633988</v>
+        <v>1132.602594937988</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1253654037986157</v>
+        <v>0.1253505013919836</v>
       </c>
       <c r="T29">
         <v>1.095042594865763</v>
       </c>
       <c r="U29">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.989394638948748</v>
+        <v>4.123983322273791</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1078629513531553</v>
+        <v>0.1072988205144237</v>
       </c>
       <c r="C30">
-        <v>7377.106756778276</v>
+        <v>7436.99577048619</v>
       </c>
       <c r="D30">
-        <v>9355.562756778276</v>
+        <v>9415.45177048619</v>
       </c>
       <c r="E30">
         <v>-1644.443999999999</v>
@@ -3753,37 +3753,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M30">
-        <v>226.531299385536</v>
+        <v>219.138313785536</v>
       </c>
       <c r="N30">
-        <v>644.9156393899741</v>
+        <v>652.3086249899741</v>
       </c>
       <c r="O30">
-        <v>154.7797534535938</v>
+        <v>156.5540699975938</v>
       </c>
       <c r="P30">
-        <v>490.1358859363803</v>
+        <v>495.7545549923803</v>
       </c>
       <c r="Q30">
-        <v>1121.03588593638</v>
+        <v>1126.65455499238</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1262634545258361</v>
+        <v>0.1262483839164868</v>
       </c>
       <c r="T30">
         <v>1.107402285783005</v>
       </c>
       <c r="U30">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.846916258986293</v>
+        <v>3.976698203621155</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1078613675564304</v>
+        <v>0.1072775046358088</v>
       </c>
       <c r="C31">
-        <v>7275.724962826756</v>
+        <v>7337.764499788478</v>
       </c>
       <c r="D31">
-        <v>9355.732962826756</v>
+        <v>9417.772499788478</v>
       </c>
       <c r="E31">
         <v>-1542.892</v>
@@ -3835,37 +3835,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M31">
-        <v>234.6217029350194</v>
+        <v>226.9646821350194</v>
       </c>
       <c r="N31">
-        <v>636.8252358404907</v>
+        <v>644.4822566404907</v>
       </c>
       <c r="O31">
-        <v>152.8380566017178</v>
+        <v>154.6757415937178</v>
       </c>
       <c r="P31">
-        <v>483.9871792387729</v>
+        <v>489.806515046773</v>
       </c>
       <c r="Q31">
-        <v>1114.887179238773</v>
+        <v>1120.706515046773</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1271868024566402</v>
+        <v>0.1271715589064689</v>
       </c>
       <c r="T31">
         <v>1.120110137007776</v>
       </c>
       <c r="U31">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.714263974193662</v>
+        <v>3.839570679358357</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1078597837597055</v>
+        <v>0.1072561887571939</v>
       </c>
       <c r="C32">
-        <v>7174.343175068474</v>
+        <v>7238.534373403847</v>
       </c>
       <c r="D32">
-        <v>9355.903175068474</v>
+        <v>9420.094373403846</v>
       </c>
       <c r="E32">
         <v>-1441.34</v>
@@ -3917,37 +3917,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M32">
-        <v>242.7121064845029</v>
+        <v>234.7910504845028</v>
       </c>
       <c r="N32">
-        <v>628.7348322910073</v>
+        <v>636.6558882910073</v>
       </c>
       <c r="O32">
-        <v>150.8963597498417</v>
+        <v>152.7974131898417</v>
       </c>
       <c r="P32">
-        <v>477.8384725411655</v>
+        <v>483.8584751011655</v>
       </c>
       <c r="Q32">
-        <v>1108.738472541165</v>
+        <v>1114.758475101165</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1281365317568957</v>
+        <v>0.1281211103247363</v>
       </c>
       <c r="T32">
         <v>1.133181069696111</v>
       </c>
       <c r="U32">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V32">
         <v>0.24</v>
       </c>
       <c r="W32">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.590455175053874</v>
+        <v>3.711584990046412</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1078581999629807</v>
+        <v>0.107234872878579</v>
       </c>
       <c r="C33">
-        <v>7072.961393503768</v>
+        <v>7139.305392178868</v>
       </c>
       <c r="D33">
-        <v>9356.073393503768</v>
+        <v>9422.417392178868</v>
       </c>
       <c r="E33">
         <v>-1339.788</v>
@@ -3999,37 +3999,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M33">
-        <v>250.8025100339863</v>
+        <v>242.6174188339863</v>
       </c>
       <c r="N33">
-        <v>620.6444287415238</v>
+        <v>628.8295199415238</v>
       </c>
       <c r="O33">
-        <v>148.9546628979657</v>
+        <v>150.9190847859657</v>
       </c>
       <c r="P33">
-        <v>471.6897658435581</v>
+        <v>477.9104351555581</v>
       </c>
       <c r="Q33">
-        <v>1102.589765843558</v>
+        <v>1108.810435155558</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.129113789442666</v>
+        <v>0.1290981849725186</v>
       </c>
       <c r="T33">
         <v>1.146630869998601</v>
       </c>
       <c r="U33">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.474634040374716</v>
+        <v>3.591856441980398</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1078566161662558</v>
+        <v>0.107213556999964</v>
       </c>
       <c r="C34">
-        <v>6971.579618132982</v>
+        <v>7040.077556960949</v>
       </c>
       <c r="D34">
-        <v>9356.243618132983</v>
+        <v>9424.741556960949</v>
       </c>
       <c r="E34">
         <v>-1238.235999999999</v>
@@ -4081,37 +4081,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M34">
-        <v>258.8929135834697</v>
+        <v>250.4437871834697</v>
       </c>
       <c r="N34">
-        <v>612.5540251920404</v>
+        <v>621.0031515920405</v>
       </c>
       <c r="O34">
-        <v>147.0129660460897</v>
+        <v>149.0407563820897</v>
       </c>
       <c r="P34">
-        <v>465.5410591459507</v>
+        <v>471.9623952099507</v>
       </c>
       <c r="Q34">
-        <v>1096.441059145951</v>
+        <v>1102.862395209951</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1301197900015471</v>
+        <v>0.1301039971099416</v>
       </c>
       <c r="T34">
         <v>1.160476252662929</v>
       </c>
       <c r="U34">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.366051726613006</v>
+        <v>3.479610928168511</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1078550323695309</v>
+        <v>0.1071922411213491</v>
       </c>
       <c r="C35">
-        <v>6870.197848956454</v>
+        <v>6940.850868598332</v>
       </c>
       <c r="D35">
-        <v>9356.413848956454</v>
+        <v>9427.066868598333</v>
       </c>
       <c r="E35">
         <v>-1136.683999999999</v>
@@ -4163,37 +4163,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M35">
-        <v>266.9833171329532</v>
+        <v>258.2701555329531</v>
       </c>
       <c r="N35">
-        <v>604.463621642557</v>
+        <v>613.176783242557</v>
       </c>
       <c r="O35">
-        <v>145.0712691942137</v>
+        <v>147.1624279782137</v>
       </c>
       <c r="P35">
-        <v>459.3923524483433</v>
+        <v>466.0143552643433</v>
       </c>
       <c r="Q35">
-        <v>1090.292352448343</v>
+        <v>1096.914355264343</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1311558204278576</v>
+        <v>0.1311398334902728</v>
       </c>
       <c r="T35">
         <v>1.174734930332163</v>
       </c>
       <c r="U35">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.264050159139885</v>
+        <v>3.374168172769465</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1078534485728061</v>
+        <v>0.1071709252427342</v>
       </c>
       <c r="C36">
-        <v>6768.816085974511</v>
+        <v>6841.625327940099</v>
       </c>
       <c r="D36">
-        <v>9356.584085974511</v>
+        <v>9429.393327940099</v>
       </c>
       <c r="E36">
         <v>-1035.131999999999</v>
@@ -4245,37 +4245,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M36">
-        <v>275.0737206824366</v>
+        <v>266.0965238824366</v>
       </c>
       <c r="N36">
-        <v>596.3732180930735</v>
+        <v>605.3504148930735</v>
       </c>
       <c r="O36">
-        <v>143.1295723423376</v>
+        <v>145.2840995743377</v>
       </c>
       <c r="P36">
-        <v>453.2436457507359</v>
+        <v>460.0663153187359</v>
       </c>
       <c r="Q36">
-        <v>1084.143645750736</v>
+        <v>1090.966315318736</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1322232457155714</v>
+        <v>0.1322070588518261</v>
       </c>
       <c r="T36">
         <v>1.189425689142888</v>
       </c>
       <c r="U36">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.168048683871065</v>
+        <v>3.274927932393893</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1078518647760812</v>
+        <v>0.1071496093641193</v>
       </c>
       <c r="C37">
-        <v>6667.434329187506</v>
+        <v>6742.400935836166</v>
       </c>
       <c r="D37">
-        <v>9356.754329187506</v>
+        <v>9431.720935836167</v>
       </c>
       <c r="E37">
         <v>-933.579999999999</v>
@@ -4327,37 +4327,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M37">
-        <v>283.16412423192</v>
+        <v>273.9228922319201</v>
       </c>
       <c r="N37">
-        <v>588.2828145435901</v>
+        <v>597.5240465435901</v>
       </c>
       <c r="O37">
-        <v>141.1878754904616</v>
+        <v>143.4057711704616</v>
       </c>
       <c r="P37">
-        <v>447.0949390531285</v>
+        <v>454.1182753731285</v>
       </c>
       <c r="Q37">
-        <v>1077.994939053129</v>
+        <v>1085.018275373129</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1333235148582917</v>
+        <v>0.1333071219168118</v>
       </c>
       <c r="T37">
         <v>1.204568471301636</v>
       </c>
       <c r="U37">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V37">
         <v>0.24</v>
       </c>
       <c r="W37">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.077533007189035</v>
+        <v>3.181358562896924</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1085616409793563</v>
+        <v>0.1071282934855043</v>
       </c>
       <c r="C38">
-        <v>6490.203780469593</v>
+        <v>6643.177693137294</v>
       </c>
       <c r="D38">
-        <v>9281.075780469593</v>
+        <v>9434.049693137295</v>
       </c>
       <c r="E38">
         <v>-832.0279999999993</v>
@@ -4409,45 +4409,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M38">
-        <v>300.7597949814035</v>
+        <v>281.7492605814035</v>
       </c>
       <c r="N38">
-        <v>570.6871437941066</v>
+        <v>589.6976781941066</v>
       </c>
       <c r="O38">
-        <v>136.9649145105856</v>
+        <v>141.5274427665856</v>
       </c>
       <c r="P38">
-        <v>433.7222292835211</v>
+        <v>448.170235427521</v>
       </c>
       <c r="Q38">
-        <v>1064.622229283521</v>
+        <v>1079.070235427521</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1344581674117221</v>
+        <v>0.1344415619525784</v>
       </c>
       <c r="T38">
         <v>1.220184465402844</v>
       </c>
       <c r="U38">
-        <v>0.08226759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V38">
         <v>0.24</v>
       </c>
       <c r="W38">
-        <v>0.06252337176626169</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.897484814515827</v>
+        <v>3.092987491705343</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1085798171826315</v>
+        <v>0.1071069776068894</v>
       </c>
       <c r="C39">
-        <v>6386.729849964062</v>
+        <v>6543.955600695077</v>
       </c>
       <c r="D39">
-        <v>9279.153849964063</v>
+        <v>9436.379600695078</v>
       </c>
       <c r="E39">
         <v>-730.4759999999992</v>
@@ -4491,45 +4491,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M39">
-        <v>309.1142337308869</v>
+        <v>289.5756289308869</v>
       </c>
       <c r="N39">
-        <v>562.3327050446233</v>
+        <v>581.8713098446233</v>
       </c>
       <c r="O39">
-        <v>134.9598492107096</v>
+        <v>139.6491143627096</v>
       </c>
       <c r="P39">
-        <v>427.3728558339137</v>
+        <v>442.2221954819137</v>
       </c>
       <c r="Q39">
-        <v>1058.272855833914</v>
+        <v>1073.122195481914</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1356288406811343</v>
+        <v>0.1356120159577343</v>
       </c>
       <c r="T39">
         <v>1.236296205348535</v>
       </c>
       <c r="U39">
-        <v>0.08226759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.06252337176626169</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.819174414123508</v>
+        <v>3.009393235172766</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1085979933859066</v>
+        <v>0.1078076617282745</v>
       </c>
       <c r="C40">
-        <v>6283.256715282678</v>
+        <v>6366.414112898809</v>
       </c>
       <c r="D40">
-        <v>9277.232715282678</v>
+        <v>9360.390112898809</v>
       </c>
       <c r="E40">
         <v>-628.9239999999995</v>
@@ -4573,37 +4573,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M40">
-        <v>317.4686724803703</v>
+        <v>307.0494372803703</v>
       </c>
       <c r="N40">
-        <v>553.9782662951397</v>
+        <v>564.3975014951399</v>
       </c>
       <c r="O40">
-        <v>132.9547839108335</v>
+        <v>135.4554003588336</v>
       </c>
       <c r="P40">
-        <v>421.0234823843062</v>
+        <v>428.9421011363063</v>
       </c>
       <c r="Q40">
-        <v>1051.923482384306</v>
+        <v>1059.842101136306</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1368372776043986</v>
+        <v>0.1368202265437017</v>
       </c>
       <c r="T40">
         <v>1.252927678840862</v>
       </c>
       <c r="U40">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.06252337176626169</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.744985613751836</v>
+        <v>2.838132342772484</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1086161695891817</v>
+        <v>0.1078053458496596</v>
       </c>
       <c r="C41">
-        <v>6179.784375931247</v>
+        <v>6265.111255009397</v>
       </c>
       <c r="D41">
-        <v>9275.312375931248</v>
+        <v>9360.639255009397</v>
       </c>
       <c r="E41">
         <v>-527.3719999999994</v>
@@ -4655,37 +4655,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M41">
-        <v>325.8231112298537</v>
+        <v>315.1296856298537</v>
       </c>
       <c r="N41">
-        <v>545.6238275456565</v>
+        <v>556.3172531456564</v>
       </c>
       <c r="O41">
-        <v>130.9497186109575</v>
+        <v>133.5161407549575</v>
       </c>
       <c r="P41">
-        <v>414.6741089346989</v>
+        <v>422.8011123906989</v>
       </c>
       <c r="Q41">
-        <v>1045.574108934699</v>
+        <v>1053.701112390699</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1380853354103929</v>
+        <v>0.1380680505915041</v>
       </c>
       <c r="T41">
         <v>1.270104446546051</v>
       </c>
       <c r="U41">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V41">
         <v>0.24</v>
       </c>
       <c r="W41">
-        <v>0.06252337176626169</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.67460136724538</v>
+        <v>2.76535971859883</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1086343457924569</v>
+        <v>0.1078030299710447</v>
       </c>
       <c r="C42">
-        <v>6076.312831415986</v>
+        <v>6163.808410382991</v>
       </c>
       <c r="D42">
-        <v>9273.392831415986</v>
+        <v>9360.888410382991</v>
       </c>
       <c r="E42">
         <v>-425.8199999999993</v>
@@ -4737,37 +4737,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M42">
-        <v>334.1775499793372</v>
+        <v>323.2099339793372</v>
       </c>
       <c r="N42">
-        <v>537.269388796173</v>
+        <v>548.237004796173</v>
       </c>
       <c r="O42">
-        <v>128.9446533110815</v>
+        <v>131.5768811510815</v>
       </c>
       <c r="P42">
-        <v>408.3247354850914</v>
+        <v>416.6601236450915</v>
       </c>
       <c r="Q42">
-        <v>1039.224735485092</v>
+        <v>1047.560123645091</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1393749951432537</v>
+        <v>0.1393574687742333</v>
       </c>
       <c r="T42">
         <v>1.287853773174747</v>
       </c>
       <c r="U42">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.06252337176626169</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.607736333064245</v>
+        <v>2.69622572563386</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.108652521995732</v>
+        <v>0.1078007140924297</v>
       </c>
       <c r="C43">
-        <v>5972.842081243512</v>
+        <v>6062.505579020645</v>
       </c>
       <c r="D43">
-        <v>9271.474081243512</v>
+        <v>9361.137579020646</v>
       </c>
       <c r="E43">
         <v>-324.2679999999991</v>
@@ -4819,37 +4819,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M43">
-        <v>342.5319887288206</v>
+        <v>331.2901823288206</v>
       </c>
       <c r="N43">
-        <v>528.9149500466895</v>
+        <v>540.1567564466895</v>
       </c>
       <c r="O43">
-        <v>126.9395880112055</v>
+        <v>129.6376215472055</v>
       </c>
       <c r="P43">
-        <v>401.975362035484</v>
+        <v>410.519134899484</v>
       </c>
       <c r="Q43">
-        <v>1032.875362035484</v>
+        <v>1041.419134899484</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1407083721551944</v>
+        <v>0.1406905960479025</v>
       </c>
       <c r="T43">
         <v>1.306204771892551</v>
       </c>
       <c r="U43">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.06252337176626169</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.544133007867555</v>
+        <v>2.630464122569619</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1095325381990071</v>
+        <v>0.1077983982138148</v>
       </c>
       <c r="C44">
-        <v>5779.332596559137</v>
+        <v>5961.202760923422</v>
       </c>
       <c r="D44">
-        <v>9179.516596559137</v>
+        <v>9361.386760923422</v>
       </c>
       <c r="E44">
         <v>-222.7159999999994</v>
@@ -4901,45 +4901,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M44">
-        <v>362.402424278304</v>
+        <v>339.370430678304</v>
       </c>
       <c r="N44">
-        <v>509.0445144972061</v>
+        <v>532.0765080972062</v>
       </c>
       <c r="O44">
-        <v>122.1706834793295</v>
+        <v>127.6983619433295</v>
       </c>
       <c r="P44">
-        <v>386.8738310178767</v>
+        <v>404.3781461538767</v>
       </c>
       <c r="Q44">
-        <v>1017.773831017877</v>
+        <v>1035.278146153877</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1420877276847883</v>
+        <v>0.1420696932275602</v>
       </c>
       <c r="T44">
         <v>1.32518856366959</v>
       </c>
       <c r="U44">
-        <v>0.08496759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V44">
         <v>0.24</v>
       </c>
       <c r="W44">
-        <v>0.06457537176626167</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.404638822466291</v>
+        <v>2.5678340244132</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1095712344022823</v>
+        <v>0.1077960823351999</v>
       </c>
       <c r="C45">
-        <v>5673.778879065047</v>
+        <v>5859.899956092378</v>
       </c>
       <c r="D45">
-        <v>9175.514879065047</v>
+        <v>9361.635956092377</v>
       </c>
       <c r="E45">
         <v>-121.1639999999998</v>
@@ -4983,45 +4983,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M45">
-        <v>371.0310534277874</v>
+        <v>347.4506790277874</v>
       </c>
       <c r="N45">
-        <v>500.4158853477227</v>
+        <v>523.9962597477227</v>
       </c>
       <c r="O45">
-        <v>120.0998124834534</v>
+        <v>125.7591023394534</v>
       </c>
       <c r="P45">
-        <v>380.3160728642693</v>
+        <v>398.2371574082692</v>
       </c>
       <c r="Q45">
-        <v>1011.216072864269</v>
+        <v>1029.137157408269</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1435154816540171</v>
+        <v>0.1434971797819428</v>
       </c>
       <c r="T45">
         <v>1.344838453403718</v>
       </c>
       <c r="U45">
-        <v>0.08496759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.06457537176626167</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.34871698938568</v>
+        <v>2.508116954078009</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1096099306055574</v>
+        <v>0.108964166456585</v>
       </c>
       <c r="C46">
-        <v>5568.228649067225</v>
+        <v>5634.320648069483</v>
       </c>
       <c r="D46">
-        <v>9171.516649067225</v>
+        <v>9237.608648069483</v>
       </c>
       <c r="E46">
         <v>-19.61199999999917</v>
@@ -5065,37 +5065,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M46">
-        <v>379.6596825772709</v>
+        <v>371.1699353772709</v>
       </c>
       <c r="N46">
-        <v>491.7872561982393</v>
+        <v>500.2770033982392</v>
       </c>
       <c r="O46">
-        <v>118.0289414875774</v>
+        <v>120.0664808155774</v>
       </c>
       <c r="P46">
-        <v>373.7583147106619</v>
+        <v>380.2105225826618</v>
       </c>
       <c r="Q46">
-        <v>1004.658314710662</v>
+        <v>1011.110522582662</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1449942268364326</v>
+        <v>0.1449756479989819</v>
       </c>
       <c r="T46">
         <v>1.365190124914065</v>
       </c>
       <c r="U46">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V46">
         <v>0.24</v>
       </c>
       <c r="W46">
-        <v>0.06457537176626167</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.295337057808732</v>
+        <v>2.34783816175666</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1112560268088325</v>
+        <v>0.10898845057797</v>
       </c>
       <c r="C47">
-        <v>5299.764167765255</v>
+        <v>5530.225018875179</v>
       </c>
       <c r="D47">
-        <v>9004.604167765256</v>
+        <v>9235.065018875179</v>
       </c>
       <c r="E47">
         <v>81.94000000000051</v>
@@ -5147,45 +5147,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M47">
-        <v>409.7665597267543</v>
+        <v>379.6056157267543</v>
       </c>
       <c r="N47">
-        <v>461.6803790487559</v>
+        <v>491.8413230487558</v>
       </c>
       <c r="O47">
-        <v>110.8032909717014</v>
+        <v>118.0419175317014</v>
       </c>
       <c r="P47">
-        <v>350.8770880770545</v>
+        <v>373.7994055170544</v>
       </c>
       <c r="Q47">
-        <v>981.7770880770545</v>
+        <v>1004.699405517054</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.146526744570936</v>
+        <v>0.1465078786966405</v>
       </c>
       <c r="T47">
         <v>1.386281857206606</v>
       </c>
       <c r="U47">
-        <v>0.08966759442929167</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V47">
         <v>0.24</v>
       </c>
       <c r="W47">
-        <v>0.06814737176626168</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.126691205247738</v>
+        <v>2.29566398038429</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1113304430121076</v>
+        <v>0.1099916146993551</v>
       </c>
       <c r="C48">
-        <v>5190.809855291925</v>
+        <v>5324.807435227282</v>
       </c>
       <c r="D48">
-        <v>8997.201855291925</v>
+        <v>9131.199435227283</v>
       </c>
       <c r="E48">
         <v>183.4920000000011</v>
@@ -5229,37 +5229,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M48">
-        <v>418.8724832762377</v>
+        <v>401.1211936762378</v>
       </c>
       <c r="N48">
-        <v>452.5744554992724</v>
+        <v>470.3257450992724</v>
       </c>
       <c r="O48">
-        <v>108.6178693198254</v>
+        <v>112.8781788238254</v>
       </c>
       <c r="P48">
-        <v>343.956586179447</v>
+        <v>357.447566275447</v>
       </c>
       <c r="Q48">
-        <v>974.856586179447</v>
+        <v>988.347566275447</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.148116022221532</v>
+        <v>0.1480968586793977</v>
       </c>
       <c r="T48">
         <v>1.408154764769242</v>
       </c>
       <c r="U48">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.06814737176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.080458787742352</v>
+        <v>2.172527785901267</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1114048592153828</v>
+        <v>0.1100371788207402</v>
       </c>
       <c r="C49">
-        <v>5081.867703091685</v>
+        <v>5218.593258321981</v>
       </c>
       <c r="D49">
-        <v>8989.811703091686</v>
+        <v>9126.537258321981</v>
       </c>
       <c r="E49">
         <v>285.0440000000008</v>
@@ -5311,37 +5311,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M49">
-        <v>427.9784068257212</v>
+        <v>409.8412196257212</v>
       </c>
       <c r="N49">
-        <v>443.468531949789</v>
+        <v>461.605719149789</v>
       </c>
       <c r="O49">
-        <v>106.4324476679494</v>
+        <v>110.7853725959494</v>
       </c>
       <c r="P49">
-        <v>337.0360842818396</v>
+        <v>350.8203465538396</v>
       </c>
       <c r="Q49">
-        <v>967.9360842818396</v>
+        <v>981.7203465538396</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.14976527261366</v>
+        <v>0.1497458001709381</v>
       </c>
       <c r="T49">
         <v>1.43085306507009</v>
       </c>
       <c r="U49">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V49">
         <v>0.24</v>
       </c>
       <c r="W49">
-        <v>0.06814737176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.036193707152089</v>
+        <v>2.126303790456559</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1148719154186579</v>
+        <v>0.1100827429421253</v>
       </c>
       <c r="C50">
-        <v>4648.970804659167</v>
+        <v>5112.383839784176</v>
       </c>
       <c r="D50">
-        <v>8658.466804659167</v>
+        <v>9121.879839784177</v>
       </c>
       <c r="E50">
         <v>386.5960000000005</v>
@@ -5393,45 +5393,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M50">
-        <v>482.4171431752046</v>
+        <v>418.5612455752046</v>
       </c>
       <c r="N50">
-        <v>389.0297956003056</v>
+        <v>452.8856932003056</v>
       </c>
       <c r="O50">
-        <v>93.36715094407334</v>
+        <v>108.6925663680733</v>
       </c>
       <c r="P50">
-        <v>295.6626446562323</v>
+        <v>344.1931268322322</v>
       </c>
       <c r="Q50">
-        <v>926.5626446562322</v>
+        <v>975.0931268322322</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1514779557131775</v>
+        <v>0.1514581624890763</v>
       </c>
       <c r="T50">
         <v>1.45442437692097</v>
       </c>
       <c r="U50">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.07521537176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.80641785041005</v>
+        <v>2.082005794822048</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1150170116219331</v>
+        <v>0.1101283070635103</v>
       </c>
       <c r="C51">
-        <v>4534.083698628638</v>
+        <v>5006.179172332777</v>
       </c>
       <c r="D51">
-        <v>8645.131698628638</v>
+        <v>9117.227172332778</v>
       </c>
       <c r="E51">
         <v>488.148000000001</v>
@@ -5475,45 +5475,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M51">
-        <v>492.467500324688</v>
+        <v>427.2812715246881</v>
       </c>
       <c r="N51">
-        <v>378.9794384508221</v>
+        <v>444.1656672508221</v>
       </c>
       <c r="O51">
-        <v>90.9550652281973</v>
+        <v>106.5997601401973</v>
       </c>
       <c r="P51">
-        <v>288.0243732226248</v>
+        <v>337.5659071106248</v>
       </c>
       <c r="Q51">
-        <v>918.9243732226248</v>
+        <v>968.4659071106248</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1532578028558134</v>
+        <v>0.1532376762706708</v>
       </c>
       <c r="T51">
         <v>1.478920053942474</v>
       </c>
       <c r="U51">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.07521537176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.769552179993518</v>
+        <v>2.039515880642006</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1169481078252082</v>
+        <v>0.1131378711848954</v>
       </c>
       <c r="C52">
-        <v>4258.886428598549</v>
+        <v>4607.480537146441</v>
       </c>
       <c r="D52">
-        <v>8471.48642859855</v>
+        <v>8820.080537146441</v>
       </c>
       <c r="E52">
         <v>589.7000000000007</v>
@@ -5557,45 +5557,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M52">
-        <v>526.3825774741715</v>
+        <v>475.6065774741714</v>
       </c>
       <c r="N52">
-        <v>345.0643613013386</v>
+        <v>395.8403613013387</v>
       </c>
       <c r="O52">
-        <v>82.81544671232128</v>
+        <v>95.00168671232129</v>
       </c>
       <c r="P52">
-        <v>262.2489145890174</v>
+        <v>300.8386745890174</v>
       </c>
       <c r="Q52">
-        <v>893.1489145890173</v>
+        <v>931.7386745890174</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1551088438841547</v>
+        <v>0.1550883706035292</v>
       </c>
       <c r="T52">
         <v>1.504395558044837</v>
       </c>
       <c r="U52">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V52">
         <v>0.24</v>
       </c>
       <c r="W52">
-        <v>0.07878737176626169</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.655539100395606</v>
+        <v>1.832285296396759</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1171289240284833</v>
+        <v>0.1132427153062805</v>
       </c>
       <c r="C53">
-        <v>4141.431819665844</v>
+        <v>4495.92558347641</v>
       </c>
       <c r="D53">
-        <v>8455.583819665844</v>
+        <v>8810.07758347641</v>
       </c>
       <c r="E53">
         <v>691.2520000000004</v>
@@ -5639,45 +5639,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M53">
-        <v>536.9102290236549</v>
+        <v>485.1187090236548</v>
       </c>
       <c r="N53">
-        <v>334.5367097518553</v>
+        <v>386.3282297518553</v>
       </c>
       <c r="O53">
-        <v>80.28881034044525</v>
+        <v>92.71877514044527</v>
       </c>
       <c r="P53">
-        <v>254.24789941141</v>
+        <v>293.60945461141</v>
       </c>
       <c r="Q53">
-        <v>885.14789941141</v>
+        <v>924.50945461141</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1570354376075304</v>
+        <v>0.1570146034805859</v>
       </c>
       <c r="T53">
         <v>1.530910878641175</v>
       </c>
       <c r="U53">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V53">
         <v>0.24</v>
       </c>
       <c r="W53">
-        <v>0.07878737176626169</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.623077549407457</v>
+        <v>1.796358133722312</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1173097402317585</v>
+        <v>0.1133475594276656</v>
       </c>
       <c r="C54">
-        <v>4024.036803375765</v>
+        <v>4384.39329303085</v>
       </c>
       <c r="D54">
-        <v>8439.740803375766</v>
+        <v>8800.097293030851</v>
       </c>
       <c r="E54">
         <v>792.804000000001</v>
@@ -5721,45 +5721,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M54">
-        <v>547.4378805731384</v>
+        <v>494.6308405731384</v>
       </c>
       <c r="N54">
-        <v>324.0090582023718</v>
+        <v>376.8160982023718</v>
       </c>
       <c r="O54">
-        <v>77.76217396856921</v>
+        <v>90.43586356856923</v>
       </c>
       <c r="P54">
-        <v>246.2468842338025</v>
+        <v>286.3802346338026</v>
       </c>
       <c r="Q54">
-        <v>877.1468842338026</v>
+        <v>917.2802346338026</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.15904230606938</v>
+        <v>0.1590210960608532</v>
       </c>
       <c r="T54">
         <v>1.55853100426236</v>
       </c>
       <c r="U54">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.07878737176626169</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.591864519611159</v>
+        <v>1.761812784996883</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1174905564350336</v>
+        <v>0.1150233235490507</v>
       </c>
       <c r="C55">
-        <v>3906.701045383025</v>
+        <v>4126.336892175083</v>
       </c>
       <c r="D55">
-        <v>8423.957045383026</v>
+        <v>8643.592892175084</v>
       </c>
       <c r="E55">
         <v>894.3560000000007</v>
@@ -5803,37 +5803,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M55">
-        <v>557.9655321226218</v>
+        <v>525.1337705226217</v>
       </c>
       <c r="N55">
-        <v>313.4814066528884</v>
+        <v>346.3131682528884</v>
       </c>
       <c r="O55">
-        <v>75.23553759669321</v>
+        <v>83.11516038069323</v>
       </c>
       <c r="P55">
-        <v>238.2458690561952</v>
+        <v>263.1980078721952</v>
       </c>
       <c r="Q55">
-        <v>869.1458690561951</v>
+        <v>894.0980078721952</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1611345731891806</v>
+        <v>0.1611129713041106</v>
       </c>
       <c r="T55">
         <v>1.587326454378063</v>
       </c>
       <c r="U55">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.561829339995854</v>
+        <v>1.659476094840048</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1176713726383087</v>
+        <v>0.1151578076704357</v>
       </c>
       <c r="C56">
-        <v>3789.424213838804</v>
+        <v>4012.465987187838</v>
       </c>
       <c r="D56">
-        <v>8408.232213838804</v>
+        <v>8631.273987187838</v>
       </c>
       <c r="E56">
         <v>995.9080000000013</v>
@@ -5885,37 +5885,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M56">
-        <v>568.4931836721053</v>
+        <v>535.0419548721052</v>
       </c>
       <c r="N56">
-        <v>302.9537551034049</v>
+        <v>336.404983903405</v>
       </c>
       <c r="O56">
-        <v>72.70890122481717</v>
+        <v>80.73719613681719</v>
       </c>
       <c r="P56">
-        <v>230.2448538785877</v>
+        <v>255.6677877665878</v>
       </c>
       <c r="Q56">
-        <v>861.1448538785877</v>
+        <v>886.5677877665878</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1633178084446248</v>
+        <v>0.163295797644901</v>
       </c>
       <c r="T56">
         <v>1.617373880585754</v>
       </c>
       <c r="U56">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V56">
         <v>0.24</v>
       </c>
       <c r="W56">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.532906574440376</v>
+        <v>1.628745056046714</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1178521888415839</v>
+        <v>0.1152922917918208</v>
       </c>
       <c r="C57">
-        <v>3672.20597936748</v>
+        <v>3898.630146194691</v>
       </c>
       <c r="D57">
-        <v>8392.56597936748</v>
+        <v>8618.990146194692</v>
       </c>
       <c r="E57">
         <v>1097.460000000001</v>
@@ -5967,37 +5967,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M57">
-        <v>579.0208352215886</v>
+        <v>544.9501392215886</v>
       </c>
       <c r="N57">
-        <v>292.4261035539215</v>
+        <v>326.4967995539215</v>
       </c>
       <c r="O57">
-        <v>70.18226485294116</v>
+        <v>78.35923189294115</v>
       </c>
       <c r="P57">
-        <v>222.2438387009803</v>
+        <v>248.1375676609804</v>
       </c>
       <c r="Q57">
-        <v>853.1438387009803</v>
+        <v>879.0375676609804</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1655980763780888</v>
+        <v>0.1655756384897265</v>
       </c>
       <c r="T57">
         <v>1.648756747958231</v>
       </c>
       <c r="U57">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.505035545814187</v>
+        <v>1.599131509573137</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.124970285044859</v>
+        <v>0.1154267759132059</v>
       </c>
       <c r="C58">
-        <v>2997.144274693964</v>
+        <v>3784.829219701464</v>
       </c>
       <c r="D58">
-        <v>7819.056274693966</v>
+        <v>8606.741219701466</v>
       </c>
       <c r="E58">
         <v>1199.012000000002</v>
@@ -6049,45 +6049,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M58">
-        <v>682.2451523710722</v>
+        <v>554.8583235710721</v>
       </c>
       <c r="N58">
-        <v>189.2017864044379</v>
+        <v>316.588615204438</v>
       </c>
       <c r="O58">
-        <v>45.4084287370651</v>
+        <v>75.98126764906513</v>
       </c>
       <c r="P58">
-        <v>143.7933576673728</v>
+        <v>240.6073475553729</v>
       </c>
       <c r="Q58">
-        <v>774.6933576673728</v>
+        <v>871.5073475553729</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1679819928539829</v>
+        <v>0.1679591084638622</v>
       </c>
       <c r="T58">
         <v>1.681566109302184</v>
       </c>
       <c r="U58">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V58">
         <v>0.24</v>
       </c>
       <c r="W58">
-        <v>0.09117537176626168</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.277322287665785</v>
+        <v>1.570575589759331</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1252749812481341</v>
+        <v>0.115561260034591</v>
       </c>
       <c r="C59">
-        <v>2872.787015637011</v>
+        <v>3671.063059062587</v>
       </c>
       <c r="D59">
-        <v>7796.251015637012</v>
+        <v>8594.527059062588</v>
       </c>
       <c r="E59">
         <v>1300.564000000001</v>
@@ -6131,45 +6131,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M59">
-        <v>694.4281015205556</v>
+        <v>564.7665079205556</v>
       </c>
       <c r="N59">
-        <v>177.0188372549545</v>
+        <v>306.6804308549546</v>
       </c>
       <c r="O59">
-        <v>42.48452094118908</v>
+        <v>73.6033034051891</v>
       </c>
       <c r="P59">
-        <v>134.5343163137654</v>
+        <v>233.0771274497655</v>
       </c>
       <c r="Q59">
-        <v>765.4343163137654</v>
+        <v>863.9771274497655</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1704767891659651</v>
+        <v>0.1704534375065624</v>
       </c>
       <c r="T59">
         <v>1.715901487452833</v>
       </c>
       <c r="U59">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V59">
         <v>0.24</v>
       </c>
       <c r="W59">
-        <v>0.09117537176626168</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.25491312472428</v>
+        <v>1.543021632044255</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1409170427772619</v>
+        <v>0.1156957441559761</v>
       </c>
       <c r="C60">
-        <v>1755.927208823593</v>
+        <v>3557.331516475093</v>
       </c>
       <c r="D60">
-        <v>6780.943208823593</v>
+        <v>8582.347516475093</v>
       </c>
       <c r="E60">
         <v>1402.116</v>
@@ -6213,45 +6213,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M60">
-        <v>899.2145738700387</v>
+        <v>574.6746922700388</v>
       </c>
       <c r="N60">
-        <v>-27.7676350945286</v>
+        <v>296.7722465054713</v>
       </c>
       <c r="O60">
-        <v>-6.664232422686863</v>
+        <v>71.22533916131312</v>
       </c>
       <c r="P60">
-        <v>-21.10340267184174</v>
+        <v>225.5469073441582</v>
       </c>
       <c r="Q60">
-        <v>609.7965973281582</v>
+        <v>856.4469073441583</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1737260207877863</v>
+        <v>0.1730665441227245</v>
       </c>
       <c r="T60">
-        <v>1.760620006515271</v>
+        <v>1.751871883610655</v>
       </c>
       <c r="U60">
-        <v>0.1526675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V60">
-        <v>0.2325888296115961</v>
+        <v>0.24</v>
       </c>
       <c r="W60">
-        <v>0.1171588173213649</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.9691201233816504</v>
+        <v>1.516417810802113</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1419857187215548</v>
+        <v>0.1221975082773611</v>
       </c>
       <c r="C61">
-        <v>1594.574400753855</v>
+        <v>2905.4843181223</v>
       </c>
       <c r="D61">
-        <v>6721.142400753855</v>
+        <v>8032.052318122299</v>
       </c>
       <c r="E61">
         <v>1503.668000000001</v>
@@ -6295,45 +6295,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M61">
-        <v>914.7182734195223</v>
+        <v>669.6631422195223</v>
       </c>
       <c r="N61">
-        <v>-43.2713346440122</v>
+        <v>201.7837965559878</v>
       </c>
       <c r="O61">
-        <v>-10.38512031456293</v>
+        <v>48.42811117343707</v>
       </c>
       <c r="P61">
-        <v>-32.88621432944927</v>
+        <v>153.3556853825507</v>
       </c>
       <c r="Q61">
-        <v>598.0137856705508</v>
+        <v>784.2556853825507</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1768461676362689</v>
+        <v>0.1758071193543091</v>
       </c>
       <c r="T61">
-        <v>1.803561957893692</v>
+        <v>1.78959693323959</v>
       </c>
       <c r="U61">
-        <v>0.1526675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V61">
-        <v>0.2286466460588571</v>
+        <v>0.24</v>
       </c>
       <c r="W61">
-        <v>0.1177606610011603</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.9526943585785714</v>
+        <v>1.301321341782673</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1430543946658477</v>
+        <v>0.1224399123987462</v>
       </c>
       <c r="C62">
-        <v>1434.2671329461</v>
+        <v>2784.777061226613</v>
       </c>
       <c r="D62">
-        <v>6662.3871329461</v>
+        <v>8012.897061226614</v>
       </c>
       <c r="E62">
         <v>1605.22</v>
@@ -6377,45 +6377,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M62">
-        <v>930.2219729690057</v>
+        <v>681.0133649690057</v>
       </c>
       <c r="N62">
-        <v>-58.77503419349557</v>
+        <v>190.4335738065045</v>
       </c>
       <c r="O62">
-        <v>-14.10600820643894</v>
+        <v>45.70405771356107</v>
       </c>
       <c r="P62">
-        <v>-44.66902598705664</v>
+        <v>144.7295160929434</v>
       </c>
       <c r="Q62">
-        <v>586.2309740129433</v>
+        <v>775.6295160929434</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1801223218271756</v>
+        <v>0.178684723347473</v>
       </c>
       <c r="T62">
-        <v>1.848651006841035</v>
+        <v>1.829208235349972</v>
       </c>
       <c r="U62">
-        <v>0.1526675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V62">
-        <v>0.2248358686245429</v>
+        <v>0.24</v>
       </c>
       <c r="W62">
-        <v>0.1183424432249625</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.9368161192689286</v>
+        <v>1.279632652752962</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1441230706101406</v>
+        <v>0.1226823165201313</v>
       </c>
       <c r="C63">
-        <v>1274.9782231325</v>
+        <v>2664.160951867076</v>
       </c>
       <c r="D63">
-        <v>6604.6502231325</v>
+        <v>7993.832951867075</v>
       </c>
       <c r="E63">
         <v>1706.772000000001</v>
@@ -6459,45 +6459,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M63">
-        <v>945.7256725184892</v>
+        <v>692.3635877184893</v>
       </c>
       <c r="N63">
-        <v>-74.27873374297906</v>
+        <v>179.0833510570209</v>
       </c>
       <c r="O63">
-        <v>-17.82689609831497</v>
+        <v>42.98000425368501</v>
       </c>
       <c r="P63">
-        <v>-56.45183764466408</v>
+        <v>136.1033468033359</v>
       </c>
       <c r="Q63">
-        <v>574.4481623553359</v>
+        <v>767.0033468033358</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1835664839253083</v>
+        <v>0.1817098967761838</v>
       </c>
       <c r="T63">
-        <v>1.896052314708753</v>
+        <v>1.870850886286529</v>
       </c>
       <c r="U63">
-        <v>0.1526675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V63">
-        <v>0.2211500347126651</v>
+        <v>0.24</v>
       </c>
       <c r="W63">
-        <v>0.1189051506217547</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.9214584779694379</v>
+        <v>1.258655068281602</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1451917465544336</v>
+        <v>0.1368216489056354</v>
       </c>
       <c r="C64">
-        <v>1116.681423206636</v>
+        <v>1588.44413146804</v>
       </c>
       <c r="D64">
-        <v>6547.905423206636</v>
+        <v>7019.66813146804</v>
       </c>
       <c r="E64">
         <v>1808.324000000001</v>
@@ -6541,37 +6541,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M64">
-        <v>961.2293720679726</v>
+        <v>883.7858168679727</v>
       </c>
       <c r="N64">
-        <v>-89.78243329246243</v>
+        <v>-12.33887809246255</v>
       </c>
       <c r="O64">
-        <v>-21.54778399019098</v>
+        <v>-2.961330742191012</v>
       </c>
       <c r="P64">
-        <v>-68.23464930227145</v>
+        <v>-9.377547350271538</v>
       </c>
       <c r="Q64">
-        <v>562.6653506977285</v>
+        <v>621.5224526497284</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1871919177128164</v>
+        <v>0.1852337660054528</v>
       </c>
       <c r="T64">
-        <v>1.945948428253721</v>
+        <v>1.919358272629354</v>
       </c>
       <c r="U64">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V64">
-        <v>0.2175830986689125</v>
+        <v>0.2366492665013729</v>
       </c>
       <c r="W64">
-        <v>0.1194497061670376</v>
+        <v>0.1071497061670376</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9065962444538018</v>
+        <v>0.9860386104223872</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1462604224987265</v>
+        <v>0.1377673248499283</v>
       </c>
       <c r="C65">
-        <v>959.3513794354476</v>
+        <v>1430.140027208924</v>
       </c>
       <c r="D65">
-        <v>6492.127379435448</v>
+        <v>6962.916027208925</v>
       </c>
       <c r="E65">
         <v>1909.876000000001</v>
@@ -6623,37 +6623,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M65">
-        <v>976.7330716174561</v>
+        <v>898.0404268174563</v>
       </c>
       <c r="N65">
-        <v>-105.2861328419459</v>
+        <v>-26.5934880419461</v>
       </c>
       <c r="O65">
-        <v>-25.26867188206702</v>
+        <v>-6.382437130067064</v>
       </c>
       <c r="P65">
-        <v>-80.01746095987889</v>
+        <v>-20.21105091187904</v>
       </c>
       <c r="Q65">
-        <v>550.8825390401211</v>
+        <v>610.6889490881209</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1910133208942439</v>
+        <v>0.1890022461677624</v>
       </c>
       <c r="T65">
-        <v>1.998541629017335</v>
+        <v>1.971232820538255</v>
       </c>
       <c r="U65">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V65">
-        <v>0.2141293986900408</v>
+        <v>0.232892928937859</v>
       </c>
       <c r="W65">
-        <v>0.1199769742346924</v>
+        <v>0.1076769742346924</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8922058278751701</v>
+        <v>0.970387203907746</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1473290984430194</v>
+        <v>0.1387130007942212</v>
       </c>
       <c r="C66">
-        <v>802.9635946875742</v>
+        <v>1272.746214094354</v>
       </c>
       <c r="D66">
-        <v>6437.291594687575</v>
+        <v>6907.074214094355</v>
       </c>
       <c r="E66">
         <v>2011.428000000001</v>
@@ -6705,37 +6705,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M66">
-        <v>992.2367711669394</v>
+        <v>912.2950367669396</v>
       </c>
       <c r="N66">
-        <v>-120.7898323914293</v>
+        <v>-40.84809799142943</v>
       </c>
       <c r="O66">
-        <v>-28.98955977394303</v>
+        <v>-9.803543517943062</v>
       </c>
       <c r="P66">
-        <v>-91.80027261748626</v>
+        <v>-31.04455447348636</v>
       </c>
       <c r="Q66">
-        <v>539.0997273825137</v>
+        <v>599.8554455265136</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1950470242524174</v>
+        <v>0.1929800863390891</v>
       </c>
       <c r="T66">
-        <v>2.054056674267816</v>
+        <v>2.02598928777543</v>
       </c>
       <c r="U66">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V66">
-        <v>0.2107836268355089</v>
+        <v>0.229253976923205</v>
       </c>
       <c r="W66">
-        <v>0.120487765175233</v>
+        <v>0.1081877651752331</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8782651118146205</v>
+        <v>0.9552249038466876</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1483977743873123</v>
+        <v>0.1396586767385142</v>
       </c>
       <c r="C67">
-        <v>647.4943925599173</v>
+        <v>1116.240965071285</v>
       </c>
       <c r="D67">
-        <v>6383.374392559918</v>
+        <v>6852.120965071286</v>
       </c>
       <c r="E67">
         <v>2112.980000000001</v>
@@ -6787,37 +6787,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M67">
-        <v>1007.740470716423</v>
+        <v>926.5496467164231</v>
       </c>
       <c r="N67">
-        <v>-136.2935319409129</v>
+        <v>-55.10270794091298</v>
       </c>
       <c r="O67">
-        <v>-32.71044766581909</v>
+        <v>-13.22464990581912</v>
       </c>
       <c r="P67">
-        <v>-103.5830842750938</v>
+        <v>-41.87805803509386</v>
       </c>
       <c r="Q67">
-        <v>527.3169157249062</v>
+        <v>589.0219419649061</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1993112249453436</v>
+        <v>0.1971852316630631</v>
       </c>
       <c r="T67">
-        <v>2.112744007818326</v>
+        <v>2.083874695997585</v>
       </c>
       <c r="U67">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V67">
-        <v>0.2075408018072703</v>
+        <v>0.225726992662848</v>
       </c>
       <c r="W67">
-        <v>0.1209828394714493</v>
+        <v>0.1086828394714493</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8647533408636263</v>
+        <v>0.9405291360951999</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1494664503316052</v>
+        <v>0.1406043526828071</v>
       </c>
       <c r="C68">
-        <v>492.9208832920285</v>
+        <v>960.6032390777355</v>
       </c>
       <c r="D68">
-        <v>6330.352883292029</v>
+        <v>6798.035239077736</v>
       </c>
       <c r="E68">
         <v>2214.532000000001</v>
@@ -6869,37 +6869,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M68">
-        <v>1023.244170265906</v>
+        <v>940.8042566659066</v>
       </c>
       <c r="N68">
-        <v>-151.7972314903963</v>
+        <v>-69.35731789039642</v>
       </c>
       <c r="O68">
-        <v>-36.4313355576951</v>
+        <v>-16.64575629369514</v>
       </c>
       <c r="P68">
-        <v>-115.3658959327012</v>
+        <v>-52.71156159670127</v>
       </c>
       <c r="Q68">
-        <v>515.5341040672988</v>
+        <v>578.1884384032987</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2038262609731478</v>
+        <v>0.2016377384766826</v>
       </c>
       <c r="T68">
-        <v>2.174883537460041</v>
+        <v>2.145165128232807</v>
       </c>
       <c r="U68">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V68">
-        <v>0.2043962442041299</v>
+        <v>0.2223068867134109</v>
       </c>
       <c r="W68">
-        <v>0.1214629115162651</v>
+        <v>0.1091629115162651</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8516510175172077</v>
+        <v>0.9262786946392121</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1505351262758982</v>
+        <v>0.1415500286271</v>
       </c>
       <c r="C69">
-        <v>339.2209313652093</v>
+        <v>805.8126541811989</v>
       </c>
       <c r="D69">
-        <v>6278.204931365211</v>
+        <v>6744.7966541812</v>
       </c>
       <c r="E69">
         <v>2316.084000000002</v>
@@ -6951,37 +6951,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M69">
-        <v>1038.74786981539</v>
+        <v>955.05886661539</v>
       </c>
       <c r="N69">
-        <v>-167.3009310398796</v>
+        <v>-83.61192783987985</v>
       </c>
       <c r="O69">
-        <v>-40.15222344957111</v>
+        <v>-20.06686268157116</v>
       </c>
       <c r="P69">
-        <v>-127.1487075903085</v>
+        <v>-63.54506515830869</v>
       </c>
       <c r="Q69">
-        <v>503.7512924096915</v>
+        <v>567.3549348416913</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2086149355480917</v>
+        <v>0.2063600941880973</v>
       </c>
       <c r="T69">
-        <v>2.240789099201254</v>
+        <v>2.210170132118651</v>
       </c>
       <c r="U69">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V69">
-        <v>0.2013455539921279</v>
+        <v>0.2189888734788824</v>
       </c>
       <c r="W69">
-        <v>0.1219286530522804</v>
+        <v>0.1096286530522805</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8389398083005331</v>
+        <v>0.9124536394953432</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.151603802220191</v>
+        <v>0.1424957045713929</v>
       </c>
       <c r="C70">
-        <v>186.3731246900334</v>
+        <v>651.8494619694739</v>
       </c>
       <c r="D70">
-        <v>6226.909124690034</v>
+        <v>6692.385461969475</v>
       </c>
       <c r="E70">
         <v>2417.636000000001</v>
@@ -7033,37 +7033,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M70">
-        <v>1054.251569364873</v>
+        <v>969.3134765648734</v>
       </c>
       <c r="N70">
-        <v>-182.8046305893632</v>
+        <v>-97.86653778936329</v>
       </c>
       <c r="O70">
-        <v>-43.87311134144717</v>
+        <v>-23.48796906944719</v>
       </c>
       <c r="P70">
-        <v>-138.9315192479161</v>
+        <v>-74.3785687199161</v>
       </c>
       <c r="Q70">
-        <v>491.9684807520839</v>
+        <v>556.5214312800839</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2137029022839695</v>
+        <v>0.2113775971314752</v>
       </c>
       <c r="T70">
-        <v>2.310813758551294</v>
+        <v>2.279237948747358</v>
       </c>
       <c r="U70">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V70">
-        <v>0.1983845899628319</v>
+        <v>0.2157684488688988</v>
       </c>
       <c r="W70">
-        <v>0.1223806963078247</v>
+        <v>0.1100806963078247</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8266024581784662</v>
+        <v>0.8990352036204117</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.152672478164484</v>
+        <v>0.1434413805156858</v>
       </c>
       <c r="C71">
-        <v>34.35674529209518</v>
+        <v>498.6945231262271</v>
       </c>
       <c r="D71">
-        <v>6176.444745292096</v>
+        <v>6640.782523126228</v>
       </c>
       <c r="E71">
         <v>2519.188000000001</v>
@@ -7115,37 +7115,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M71">
-        <v>1069.755268914357</v>
+        <v>983.5680865143568</v>
       </c>
       <c r="N71">
-        <v>-198.3083301388466</v>
+        <v>-112.1211477388466</v>
       </c>
       <c r="O71">
-        <v>-47.59399923332318</v>
+        <v>-26.90907545732319</v>
       </c>
       <c r="P71">
-        <v>-150.7143309055234</v>
+        <v>-85.21207228152343</v>
       </c>
       <c r="Q71">
-        <v>480.1856690944766</v>
+        <v>545.6879277184765</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2191191249382911</v>
+        <v>0.2167188099421681</v>
       </c>
       <c r="T71">
-        <v>2.3853561378594</v>
+        <v>2.352761753545661</v>
       </c>
       <c r="U71">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V71">
-        <v>0.1955094509778633</v>
+        <v>0.2126413698997844</v>
       </c>
       <c r="W71">
-        <v>0.1228196368603097</v>
+        <v>0.1105196368603098</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8146227124077638</v>
+        <v>0.8860057079157682</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1537411541087769</v>
+        <v>0.1443870564599787</v>
       </c>
       <c r="C72">
-        <v>-116.8482585882457</v>
+        <v>346.329284127939</v>
       </c>
       <c r="D72">
-        <v>6126.791741411756</v>
+        <v>6589.96928412794</v>
       </c>
       <c r="E72">
         <v>2620.740000000002</v>
@@ -7197,37 +7197,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M72">
-        <v>1085.25896846384</v>
+        <v>997.8226964638403</v>
       </c>
       <c r="N72">
-        <v>-213.81202968833</v>
+        <v>-126.3757576883302</v>
       </c>
       <c r="O72">
-        <v>-51.31488712519919</v>
+        <v>-30.33018184519924</v>
       </c>
       <c r="P72">
-        <v>-162.4971425631308</v>
+        <v>-96.04557584313093</v>
       </c>
       <c r="Q72">
-        <v>468.4028574368692</v>
+        <v>534.8544241568691</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2248964291029009</v>
+        <v>0.2224161036069069</v>
       </c>
       <c r="T72">
-        <v>2.46486800912138</v>
+        <v>2.431187145330516</v>
       </c>
       <c r="U72">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V72">
-        <v>0.1927164588210367</v>
+        <v>0.2096036360440731</v>
       </c>
       <c r="W72">
-        <v>0.1232460362541524</v>
+        <v>0.1109460362541524</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.802985245087653</v>
+        <v>0.8733484835169714</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1795048265975765</v>
+        <v>0.1453327324042717</v>
       </c>
       <c r="C73">
-        <v>-1213.044615062467</v>
+        <v>194.7357550025372</v>
       </c>
       <c r="D73">
-        <v>5132.147384937533</v>
+        <v>6539.927755002537</v>
       </c>
       <c r="E73">
         <v>2722.292</v>
@@ -7279,45 +7279,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M73">
-        <v>1336.535946413323</v>
+        <v>1012.077306413324</v>
       </c>
       <c r="N73">
-        <v>-465.0890076378133</v>
+        <v>-140.6303676378134</v>
       </c>
       <c r="O73">
-        <v>-111.6213618330752</v>
+        <v>-33.75128823307521</v>
       </c>
       <c r="P73">
-        <v>-353.4676458047381</v>
+        <v>-106.8790794047382</v>
       </c>
       <c r="Q73">
-        <v>277.4323541952618</v>
+        <v>524.0209205952618</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2361687078461273</v>
+        <v>0.2285063140761106</v>
       </c>
       <c r="T73">
-        <v>2.6200061065321</v>
+        <v>2.515021184824671</v>
       </c>
       <c r="U73">
-        <v>0.1853675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V73">
-        <v>0.1564845793092075</v>
+        <v>0.2066514721561285</v>
       </c>
       <c r="W73">
-        <v>0.1563604243974642</v>
+        <v>0.1113604243974642</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.6520190804550313</v>
+        <v>0.8610478006505353</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2200007002346499</v>
+        <v>0.1462784083485646</v>
       </c>
       <c r="C74">
-        <v>-2357.952887807409</v>
+        <v>43.89648809376104</v>
       </c>
       <c r="D74">
-        <v>4088.791112192592</v>
+        <v>6490.640488093762</v>
       </c>
       <c r="E74">
         <v>2823.844000000001</v>
@@ -7361,45 +7361,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M74">
-        <v>1737.033433162807</v>
+        <v>1026.331916362807</v>
       </c>
       <c r="N74">
-        <v>-865.586494387297</v>
+        <v>-154.8849775872969</v>
       </c>
       <c r="O74">
-        <v>-207.7407586529513</v>
+        <v>-37.17239462095126</v>
       </c>
       <c r="P74">
-        <v>-657.8457357343457</v>
+        <v>-117.7125829663457</v>
       </c>
       <c r="Q74">
-        <v>-26.9457357343457</v>
+        <v>513.1874170336544</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2483825820291335</v>
+        <v>0.2350315395788288</v>
       </c>
       <c r="T74">
-        <v>2.788103191950972</v>
+        <v>2.60484336999698</v>
       </c>
       <c r="U74">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V74">
-        <v>0.1204048588318217</v>
+        <v>0.2037813128206267</v>
       </c>
       <c r="W74">
-        <v>0.2089633017590174</v>
+        <v>0.1117633017590173</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5016869117992573</v>
+        <v>0.8490888034192778</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2219183761789428</v>
+        <v>0.1472240842928575</v>
       </c>
       <c r="C75">
-        <v>-2498.492968865971</v>
+        <v>-106.2054422214287</v>
       </c>
       <c r="D75">
-        <v>4049.803031134029</v>
+        <v>6442.090557778572</v>
       </c>
       <c r="E75">
         <v>2925.396000000001</v>
@@ -7443,45 +7443,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M75">
-        <v>1761.158897512291</v>
+        <v>1040.586526312291</v>
       </c>
       <c r="N75">
-        <v>-889.7119587367805</v>
+        <v>-169.1395875367804</v>
       </c>
       <c r="O75">
-        <v>-213.5308700968273</v>
+        <v>-40.59350100882729</v>
       </c>
       <c r="P75">
-        <v>-676.1810886399533</v>
+        <v>-128.5460865279531</v>
       </c>
       <c r="Q75">
-        <v>-45.28108863995328</v>
+        <v>502.3539134720469</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2558856406228051</v>
+        <v>0.2420401151187855</v>
       </c>
       <c r="T75">
-        <v>2.891366273134342</v>
+        <v>2.701319050367239</v>
       </c>
       <c r="U75">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V75">
-        <v>0.1187554772039885</v>
+        <v>0.2009897879874674</v>
       </c>
       <c r="W75">
-        <v>0.2093551413846376</v>
+        <v>0.1121551413846376</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4948144883499522</v>
+        <v>0.8374574499477808</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2238360521232357</v>
+        <v>0.1481697602371504</v>
       </c>
       <c r="C76">
-        <v>-2638.296542280369</v>
+        <v>-255.5864589119064</v>
       </c>
       <c r="D76">
-        <v>4011.551457719632</v>
+        <v>6394.261541088094</v>
       </c>
       <c r="E76">
         <v>3026.948000000001</v>
@@ -7525,45 +7525,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M76">
-        <v>1785.284361861774</v>
+        <v>1054.841136261774</v>
       </c>
       <c r="N76">
-        <v>-913.837423086264</v>
+        <v>-183.3941974862638</v>
       </c>
       <c r="O76">
-        <v>-219.3209815407034</v>
+        <v>-44.01460739670331</v>
       </c>
       <c r="P76">
-        <v>-694.5164415455606</v>
+        <v>-139.3795900895605</v>
       </c>
       <c r="Q76">
-        <v>-63.61644154556063</v>
+        <v>491.5204099104395</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.263965857569836</v>
+        <v>0.2495878118541233</v>
       </c>
       <c r="T76">
-        <v>3.002572668254893</v>
+        <v>2.805215936919825</v>
       </c>
       <c r="U76">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V76">
-        <v>0.1171506734579887</v>
+        <v>0.1982737097714205</v>
       </c>
       <c r="W76">
-        <v>0.2097363907501059</v>
+        <v>0.1125363907501059</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4881278060749529</v>
+        <v>0.8261404573809189</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2257537280675286</v>
+        <v>0.1491154361814433</v>
       </c>
       <c r="C77">
-        <v>-2777.38428236561</v>
+        <v>-404.262500814536</v>
       </c>
       <c r="D77">
-        <v>3974.015717634391</v>
+        <v>6347.137499185465</v>
       </c>
       <c r="E77">
         <v>3128.500000000001</v>
@@ -7607,45 +7607,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M77">
-        <v>1809.409826211257</v>
+        <v>1069.095746211257</v>
       </c>
       <c r="N77">
-        <v>-937.9628874357473</v>
+        <v>-197.6488074357472</v>
       </c>
       <c r="O77">
-        <v>-225.1110929845794</v>
+        <v>-47.43571378457933</v>
       </c>
       <c r="P77">
-        <v>-712.851794451168</v>
+        <v>-150.2130936511679</v>
       </c>
       <c r="Q77">
-        <v>-81.95179445116798</v>
+        <v>480.6869063488321</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2726924918726295</v>
+        <v>0.2577393243282883</v>
       </c>
       <c r="T77">
-        <v>3.122675574985089</v>
+        <v>2.917424574396618</v>
       </c>
       <c r="U77">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V77">
-        <v>0.1155886644785488</v>
+        <v>0.1956300603078016</v>
       </c>
       <c r="W77">
-        <v>0.2101074734658283</v>
+        <v>0.1129074734658283</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4816194353272869</v>
+        <v>0.8151252512825067</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2276714040118216</v>
+        <v>0.1500611121257363</v>
       </c>
       <c r="C78">
-        <v>-2915.776096818765</v>
+        <v>-552.2490403432957</v>
       </c>
       <c r="D78">
-        <v>3937.175903181235</v>
+        <v>6300.702959656704</v>
       </c>
       <c r="E78">
         <v>3230.052000000001</v>
@@ -7689,45 +7689,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M78">
-        <v>1833.535290560741</v>
+        <v>1083.350356160741</v>
       </c>
       <c r="N78">
-        <v>-962.0883517852307</v>
+        <v>-211.9034173852307</v>
       </c>
       <c r="O78">
-        <v>-230.9012044284553</v>
+        <v>-50.85682017245536</v>
       </c>
       <c r="P78">
-        <v>-731.1871473567753</v>
+        <v>-161.0465972127753</v>
       </c>
       <c r="Q78">
-        <v>-100.2871473567753</v>
+        <v>469.8534027872247</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2821463457006557</v>
+        <v>0.2665701295086337</v>
       </c>
       <c r="T78">
-        <v>3.252787057276135</v>
+        <v>3.038983931663144</v>
       </c>
       <c r="U78">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V78">
-        <v>0.114067760998568</v>
+        <v>0.1930559805669095</v>
       </c>
       <c r="W78">
-        <v>0.2104687908469265</v>
+        <v>0.1132687908469265</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4752823374940331</v>
+        <v>0.8043999190287895</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2295890799561145</v>
+        <v>0.1742449571762949</v>
       </c>
       <c r="C79">
-        <v>-3053.49116192601</v>
+        <v>-1646.80798961673</v>
       </c>
       <c r="D79">
-        <v>3901.012838073991</v>
+        <v>5307.696010383271</v>
       </c>
       <c r="E79">
         <v>3331.604000000001</v>
@@ -7771,45 +7771,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M79">
-        <v>1857.660754910224</v>
+        <v>1318.114978910224</v>
       </c>
       <c r="N79">
-        <v>-986.2138161347142</v>
+        <v>-446.6680401347143</v>
       </c>
       <c r="O79">
-        <v>-236.6913158723314</v>
+        <v>-107.2003296323314</v>
       </c>
       <c r="P79">
-        <v>-749.5225002623828</v>
+        <v>-339.4677105023828</v>
       </c>
       <c r="Q79">
-        <v>-118.6225002623828</v>
+        <v>291.4322894976171</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2924222737745973</v>
+        <v>0.2827956529927731</v>
       </c>
       <c r="T79">
-        <v>3.394212581505532</v>
+        <v>3.262334369790212</v>
       </c>
       <c r="U79">
-        <v>0.2375675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V79">
-        <v>0.11258636150508</v>
+        <v>0.1586714881876532</v>
       </c>
       <c r="W79">
-        <v>0.2108207233609832</v>
+        <v>0.1418207233609832</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4691098396045003</v>
+        <v>0.6611312007818884</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2315067559004074</v>
+        <v>0.1754726331205878</v>
       </c>
       <c r="C80">
-        <v>-3190.547955847036</v>
+        <v>-1790.487610590975</v>
       </c>
       <c r="D80">
-        <v>3865.508044152965</v>
+        <v>5265.568389409025</v>
       </c>
       <c r="E80">
         <v>3433.156000000001</v>
@@ -7853,45 +7853,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M80">
-        <v>1881.786219259708</v>
+        <v>1335.233355259708</v>
       </c>
       <c r="N80">
-        <v>-1010.339280484198</v>
+        <v>-463.7864164841975</v>
       </c>
       <c r="O80">
-        <v>-242.4814273162075</v>
+        <v>-111.3087399562074</v>
       </c>
       <c r="P80">
-        <v>-767.8578531679902</v>
+        <v>-352.4776765279901</v>
       </c>
       <c r="Q80">
-        <v>-136.9578531679903</v>
+        <v>278.4223234720099</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3036323771279881</v>
+        <v>0.2935681826742629</v>
       </c>
       <c r="T80">
-        <v>3.548494971573966</v>
+        <v>3.410622295689768</v>
       </c>
       <c r="U80">
-        <v>0.2375675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V80">
-        <v>0.1111429466139893</v>
+        <v>0.1566372383390936</v>
       </c>
       <c r="W80">
-        <v>0.2111636319644231</v>
+        <v>0.1421636319644231</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.463095610891622</v>
+        <v>0.6526551597462232</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2334244318447003</v>
+        <v>0.221201007874269</v>
       </c>
       <c r="C81">
-        <v>-3326.964290098263</v>
+        <v>-3093.539921371917</v>
       </c>
       <c r="D81">
-        <v>3830.643709901738</v>
+        <v>4064.068078628085</v>
       </c>
       <c r="E81">
         <v>3534.708000000001</v>
@@ -7935,37 +7935,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M81">
-        <v>1905.911683609191</v>
+        <v>1785.572563609191</v>
       </c>
       <c r="N81">
-        <v>-1034.464744833681</v>
+        <v>-914.1256248336812</v>
       </c>
       <c r="O81">
-        <v>-248.2715387600835</v>
+        <v>-219.3901499600835</v>
       </c>
       <c r="P81">
-        <v>-786.1932060735978</v>
+        <v>-694.7354748735977</v>
       </c>
       <c r="Q81">
-        <v>-155.2932060735978</v>
+        <v>-63.83547487359772</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.315910109372178</v>
+        <v>0.3141318999891718</v>
       </c>
       <c r="T81">
-        <v>3.717470922601297</v>
+        <v>3.693689604815152</v>
       </c>
       <c r="U81">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V81">
-        <v>0.10973607387204</v>
+        <v>0.1171317646611748</v>
       </c>
       <c r="W81">
-        <v>0.2114978593373961</v>
+        <v>0.1964978593373961</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4572336411335001</v>
+        <v>0.4880490194215619</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2353421077889932</v>
+        <v>0.2229686838185619</v>
       </c>
       <c r="C82">
-        <v>-3462.757339347518</v>
+        <v>-3230.625796394244</v>
       </c>
       <c r="D82">
-        <v>3796.402660652483</v>
+        <v>4028.534203605756</v>
       </c>
       <c r="E82">
         <v>3636.260000000001</v>
@@ -8017,37 +8017,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M82">
-        <v>1930.037147958675</v>
+        <v>1808.174747958675</v>
       </c>
       <c r="N82">
-        <v>-1058.590209183164</v>
+        <v>-936.7278091831644</v>
       </c>
       <c r="O82">
-        <v>-254.0616502039595</v>
+        <v>-224.8146742039594</v>
       </c>
       <c r="P82">
-        <v>-804.5285589792049</v>
+        <v>-711.9131349792049</v>
       </c>
       <c r="Q82">
-        <v>-173.628558979205</v>
+        <v>-81.01313497920489</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3294156148407869</v>
+        <v>0.3275484949886304</v>
       </c>
       <c r="T82">
-        <v>3.903344468731362</v>
+        <v>3.878374085055909</v>
       </c>
       <c r="U82">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V82">
-        <v>0.1083643729486395</v>
+        <v>0.1156676176029102</v>
       </c>
       <c r="W82">
-        <v>0.2118237310260448</v>
+        <v>0.1968237310260448</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4515182206193316</v>
+        <v>0.4819484066787924</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2372597837332862</v>
+        <v>0.2247363597628548</v>
       </c>
       <c r="C83">
-        <v>-3597.943669624927</v>
+        <v>-3367.095681723729</v>
       </c>
       <c r="D83">
-        <v>3762.768330375075</v>
+        <v>3993.616318276272</v>
       </c>
       <c r="E83">
         <v>3737.812000000002</v>
@@ -8099,37 +8099,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M83">
-        <v>1954.162612308158</v>
+        <v>1830.776932308158</v>
       </c>
       <c r="N83">
-        <v>-1082.715673532648</v>
+        <v>-959.329993532648</v>
       </c>
       <c r="O83">
-        <v>-259.8517616478355</v>
+        <v>-230.2391984478355</v>
       </c>
       <c r="P83">
-        <v>-822.8639118848125</v>
+        <v>-729.0907950848125</v>
       </c>
       <c r="Q83">
-        <v>-191.9639118848125</v>
+        <v>-98.19079508481252</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3443427524639863</v>
+        <v>0.3423773631459268</v>
       </c>
       <c r="T83">
-        <v>4.108783651296172</v>
+        <v>4.082499036900957</v>
       </c>
       <c r="U83">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V83">
-        <v>0.1070265411838415</v>
+        <v>0.1142396223238619</v>
       </c>
       <c r="W83">
-        <v>0.212141556500159</v>
+        <v>0.1971415565001589</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4459439215993397</v>
+        <v>0.4759984263494245</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.239177459677579</v>
+        <v>0.2265040357071477</v>
       </c>
       <c r="C84">
-        <v>-3732.53926504735</v>
+        <v>-3502.965457250419</v>
       </c>
       <c r="D84">
-        <v>3729.724734952651</v>
+        <v>3959.298542749582</v>
       </c>
       <c r="E84">
         <v>3839.364000000001</v>
@@ -8181,37 +8181,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M84">
-        <v>1978.288076657642</v>
+        <v>1853.379116657642</v>
       </c>
       <c r="N84">
-        <v>-1106.841137882132</v>
+        <v>-981.9321778821314</v>
       </c>
       <c r="O84">
-        <v>-265.6418730917115</v>
+        <v>-235.6637226917115</v>
       </c>
       <c r="P84">
-        <v>-841.19926479042</v>
+        <v>-746.2684551904199</v>
       </c>
       <c r="Q84">
-        <v>-210.29926479042</v>
+        <v>-115.3684551904199</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3609284609342077</v>
+        <v>0.3588538833207005</v>
       </c>
       <c r="T84">
-        <v>4.337049409701514</v>
+        <v>4.309304538951011</v>
       </c>
       <c r="U84">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V84">
-        <v>0.1057213394620874</v>
+        <v>0.1128464561979611</v>
       </c>
       <c r="W84">
-        <v>0.2124516301334411</v>
+        <v>0.197451630133441</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4405055810920306</v>
+        <v>0.4701935674915046</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.241095135621872</v>
+        <v>0.2282717116514406</v>
       </c>
       <c r="C85">
-        <v>-3866.559553146974</v>
+        <v>-3638.250461681218</v>
       </c>
       <c r="D85">
-        <v>3697.256446853026</v>
+        <v>3925.565538318783</v>
       </c>
       <c r="E85">
         <v>3940.916000000001</v>
@@ -8263,37 +8263,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M85">
-        <v>2002.413541007125</v>
+        <v>1875.981301007125</v>
       </c>
       <c r="N85">
-        <v>-1130.966602231615</v>
+        <v>-1004.534362231615</v>
       </c>
       <c r="O85">
-        <v>-271.4319845355875</v>
+        <v>-241.0882469355875</v>
       </c>
       <c r="P85">
-        <v>-859.5346176960271</v>
+        <v>-763.4461152960271</v>
       </c>
       <c r="Q85">
-        <v>-228.6346176960271</v>
+        <v>-132.5461152960271</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3794654292244553</v>
+        <v>0.3772688176336828</v>
       </c>
       <c r="T85">
-        <v>4.592169963213369</v>
+        <v>4.562793041242246</v>
       </c>
       <c r="U85">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V85">
-        <v>0.1044475883842309</v>
+        <v>0.1114868603401544</v>
       </c>
       <c r="W85">
-        <v>0.2127542321129091</v>
+        <v>0.1977542321129091</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4351982849342955</v>
+        <v>0.4645285847506433</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2430128115661649</v>
+        <v>0.2300393875957336</v>
       </c>
       <c r="C86">
-        <v>-4000.019428888349</v>
+        <v>-3772.965515399392</v>
       </c>
       <c r="D86">
-        <v>3665.348571111652</v>
+        <v>3892.402484600609</v>
       </c>
       <c r="E86">
         <v>4042.468000000001</v>
@@ -8345,37 +8345,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M86">
-        <v>2026.539005356608</v>
+        <v>1898.583485356608</v>
       </c>
       <c r="N86">
-        <v>-1155.092066581098</v>
+        <v>-1027.136546581098</v>
       </c>
       <c r="O86">
-        <v>-277.2220959794635</v>
+        <v>-246.5127711794636</v>
       </c>
       <c r="P86">
-        <v>-877.8699706016346</v>
+        <v>-780.6237754016346</v>
       </c>
       <c r="Q86">
-        <v>-246.9699706016346</v>
+        <v>-149.7237754016346</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4003195185509835</v>
+        <v>0.3979856187357879</v>
       </c>
       <c r="T86">
-        <v>4.879180585914201</v>
+        <v>4.847967606319885</v>
       </c>
       <c r="U86">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V86">
-        <v>0.10320416471299</v>
+        <v>0.1101596358122954</v>
       </c>
       <c r="W86">
-        <v>0.2130496292833423</v>
+        <v>0.1980496292833423</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4300173529707919</v>
+        <v>0.4589984825512308</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2449304875104578</v>
+        <v>0.2318070635400264</v>
       </c>
       <c r="C87">
-        <v>-4132.933277452449</v>
+        <v>-3907.124942175052</v>
       </c>
       <c r="D87">
-        <v>3633.986722547551</v>
+        <v>3859.795057824948</v>
       </c>
       <c r="E87">
         <v>4144.02</v>
@@ -8427,37 +8427,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M87">
-        <v>2050.664469706091</v>
+        <v>1921.185669706092</v>
       </c>
       <c r="N87">
-        <v>-1179.217530930581</v>
+        <v>-1049.738730930581</v>
       </c>
       <c r="O87">
-        <v>-283.0122074233395</v>
+        <v>-251.9372954233395</v>
       </c>
       <c r="P87">
-        <v>-896.2053235072417</v>
+        <v>-797.8014355072419</v>
       </c>
       <c r="Q87">
-        <v>-265.3053235072417</v>
+        <v>-166.9014355072419</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4239541531210491</v>
+        <v>0.4214646599848404</v>
       </c>
       <c r="T87">
-        <v>5.204459291641815</v>
+        <v>5.17116544674121</v>
       </c>
       <c r="U87">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V87">
-        <v>0.1019899980693078</v>
+        <v>0.1088636400968566</v>
       </c>
       <c r="W87">
-        <v>0.2133380759321181</v>
+        <v>0.1983380759321181</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4249583252887826</v>
+        <v>0.4535985004035693</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2468481634547507</v>
+        <v>0.2335747394843194</v>
       </c>
       <c r="C88">
-        <v>-4265.314995860981</v>
+        <v>-4040.742589793495</v>
       </c>
       <c r="D88">
-        <v>3603.157004139018</v>
+        <v>3827.729410206505</v>
       </c>
       <c r="E88">
         <v>4245.572</v>
@@ -8509,37 +8509,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M88">
-        <v>2074.789934055575</v>
+        <v>1943.787854055575</v>
       </c>
       <c r="N88">
-        <v>-1203.342995280065</v>
+        <v>-1072.340915280065</v>
       </c>
       <c r="O88">
-        <v>-288.8023188672155</v>
+        <v>-257.3618196672155</v>
       </c>
       <c r="P88">
-        <v>-914.5406764128493</v>
+        <v>-814.9790956128491</v>
       </c>
       <c r="Q88">
-        <v>-283.6406764128493</v>
+        <v>-184.0790956128491</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4509651640582669</v>
+        <v>0.4482978499837576</v>
       </c>
       <c r="T88">
-        <v>5.576206383901945</v>
+        <v>5.540534407222726</v>
       </c>
       <c r="U88">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V88">
-        <v>0.1008040678591996</v>
+        <v>0.1075977838166606</v>
       </c>
       <c r="W88">
-        <v>0.2136198145192946</v>
+        <v>0.1986198145192946</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4200169494133317</v>
+        <v>0.4483240992360861</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2487658393990436</v>
+        <v>0.2353424154286123</v>
       </c>
       <c r="C89">
-        <v>-4397.178013509212</v>
+        <v>-4173.831849663758</v>
       </c>
       <c r="D89">
-        <v>3572.84598649079</v>
+        <v>3796.192150336242</v>
       </c>
       <c r="E89">
         <v>4347.124000000002</v>
@@ -8591,37 +8591,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M89">
-        <v>2098.915398405059</v>
+        <v>1966.390038405059</v>
       </c>
       <c r="N89">
-        <v>-1227.468459629549</v>
+        <v>-1094.943099629549</v>
       </c>
       <c r="O89">
-        <v>-294.5924303110917</v>
+        <v>-262.7863439110916</v>
       </c>
       <c r="P89">
-        <v>-932.8760293184571</v>
+        <v>-832.156755718457</v>
       </c>
       <c r="Q89">
-        <v>-301.9760293184571</v>
+        <v>-201.256755718457</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4821317151396721</v>
+        <v>0.4792592230594312</v>
       </c>
       <c r="T89">
-        <v>6.005145336509787</v>
+        <v>5.966729361624474</v>
       </c>
       <c r="U89">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V89">
-        <v>0.09964540041254211</v>
+        <v>0.1063610276808369</v>
       </c>
       <c r="W89">
-        <v>0.2138950763573405</v>
+        <v>0.1988950763573405</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4151891683855922</v>
+        <v>0.4431709486701538</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2506835153433365</v>
+        <v>0.2371100913729052</v>
       </c>
       <c r="C90">
-        <v>-4528.535311671063</v>
+        <v>-4306.405675465762</v>
       </c>
       <c r="D90">
-        <v>3543.040688328937</v>
+        <v>3765.170324534239</v>
       </c>
       <c r="E90">
         <v>4448.676000000001</v>
@@ -8673,37 +8673,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M90">
-        <v>2123.040862754542</v>
+        <v>1988.992222754542</v>
       </c>
       <c r="N90">
-        <v>-1251.593923979032</v>
+        <v>-1117.545283979032</v>
       </c>
       <c r="O90">
-        <v>-300.3825417549676</v>
+        <v>-268.2108681549676</v>
       </c>
       <c r="P90">
-        <v>-951.2113822240642</v>
+        <v>-849.3344158240643</v>
       </c>
       <c r="Q90">
-        <v>-320.3113822240642</v>
+        <v>-218.4344158240643</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5184926914013115</v>
+        <v>0.5153808249810505</v>
       </c>
       <c r="T90">
-        <v>6.50557411455227</v>
+        <v>6.463956808426515</v>
       </c>
       <c r="U90">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V90">
-        <v>0.09851306631694504</v>
+        <v>0.1051523796390092</v>
       </c>
       <c r="W90">
-        <v>0.2141640822445218</v>
+        <v>0.1991640822445218</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4104711096539377</v>
+        <v>0.4381349151625386</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2526011912876295</v>
+        <v>0.2388777673171981</v>
       </c>
       <c r="C91">
-        <v>-4659.39944203602</v>
+        <v>-4438.476600890579</v>
       </c>
       <c r="D91">
-        <v>3513.72855796398</v>
+        <v>3734.651399109422</v>
       </c>
       <c r="E91">
         <v>4550.228000000001</v>
@@ -8755,37 +8755,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M91">
-        <v>2147.166327104026</v>
+        <v>2011.594407104025</v>
       </c>
       <c r="N91">
-        <v>-1275.719388328515</v>
+        <v>-1140.147468328515</v>
       </c>
       <c r="O91">
-        <v>-306.1726531988437</v>
+        <v>-273.6353923988436</v>
       </c>
       <c r="P91">
-        <v>-969.5467351296717</v>
+        <v>-866.5120759296715</v>
       </c>
       <c r="Q91">
-        <v>-338.6467351296717</v>
+        <v>-235.6120759296715</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5614647542559761</v>
+        <v>0.5580699908884188</v>
       </c>
       <c r="T91">
-        <v>7.096989943147931</v>
+        <v>7.051589245556198</v>
       </c>
       <c r="U91">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V91">
-        <v>0.09740617793136139</v>
+        <v>0.103970892227335</v>
       </c>
       <c r="W91">
-        <v>0.2144270430555866</v>
+        <v>0.1994270430555866</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4058590747140058</v>
+        <v>0.4332120509472291</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2545188672319224</v>
+        <v>0.2406454432614911</v>
       </c>
       <c r="C92">
-        <v>-4789.782544333405</v>
+        <v>-4570.056756524853</v>
       </c>
       <c r="D92">
-        <v>3484.897455666595</v>
+        <v>3704.623243475147</v>
       </c>
       <c r="E92">
         <v>4651.780000000001</v>
@@ -8837,37 +8837,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M92">
-        <v>2171.291791453509</v>
+        <v>2034.196591453509</v>
       </c>
       <c r="N92">
-        <v>-1299.844852677998</v>
+        <v>-1162.749652677999</v>
       </c>
       <c r="O92">
-        <v>-311.9627646427196</v>
+        <v>-279.0599166427197</v>
       </c>
       <c r="P92">
-        <v>-987.8820880352789</v>
+        <v>-883.6897360352791</v>
       </c>
       <c r="Q92">
-        <v>-356.9820880352789</v>
+        <v>-252.7897360352791</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6130312296815738</v>
+        <v>0.6092969899772608</v>
       </c>
       <c r="T92">
-        <v>7.806688937462725</v>
+        <v>7.756748170111819</v>
       </c>
       <c r="U92">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V92">
-        <v>0.09632388706545739</v>
+        <v>0.1028156600914757</v>
       </c>
       <c r="W92">
-        <v>0.2146841602930722</v>
+        <v>0.1996841602930722</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4013495294394058</v>
+        <v>0.428398583714482</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2564365431762153</v>
+        <v>0.242413119205784</v>
       </c>
       <c r="C93">
-        <v>-4919.696363096058</v>
+        <v>-4701.157885927181</v>
       </c>
       <c r="D93">
-        <v>3456.535636903943</v>
+        <v>3675.074114072821</v>
       </c>
       <c r="E93">
         <v>4753.332000000002</v>
@@ -8919,37 +8919,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M93">
-        <v>2195.417255802993</v>
+        <v>2056.798775802993</v>
       </c>
       <c r="N93">
-        <v>-1323.970317027482</v>
+        <v>-1185.351837027482</v>
       </c>
       <c r="O93">
-        <v>-317.7528760865958</v>
+        <v>-284.4844408865957</v>
       </c>
       <c r="P93">
-        <v>-1006.217440940887</v>
+        <v>-900.8673961408866</v>
       </c>
       <c r="Q93">
-        <v>-375.3174409408867</v>
+        <v>-269.9673961408866</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6760569218684154</v>
+        <v>0.6719077666414009</v>
       </c>
       <c r="T93">
-        <v>8.674098819403028</v>
+        <v>8.618609077902022</v>
       </c>
       <c r="U93">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V93">
-        <v>0.09526538281199079</v>
+        <v>0.101685817672888</v>
       </c>
       <c r="W93">
-        <v>0.2149356266022615</v>
+        <v>0.1999356266022614</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3969390950499617</v>
+        <v>0.4236909069703669</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2583542191205083</v>
+        <v>0.2441807951500769</v>
       </c>
       <c r="C94">
-        <v>-5049.15226361204</v>
+        <v>-4831.791360941199</v>
       </c>
       <c r="D94">
-        <v>3428.631736387962</v>
+        <v>3645.992639058803</v>
       </c>
       <c r="E94">
         <v>4854.884000000002</v>
@@ -9001,37 +9001,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M94">
-        <v>2219.542720152476</v>
+        <v>2079.400960152476</v>
       </c>
       <c r="N94">
-        <v>-1348.095781376966</v>
+        <v>-1207.954021376966</v>
       </c>
       <c r="O94">
-        <v>-323.5429875304718</v>
+        <v>-289.9089651304717</v>
       </c>
       <c r="P94">
-        <v>-1024.552793846494</v>
+        <v>-918.0450562464939</v>
       </c>
       <c r="Q94">
-        <v>-393.6527938464943</v>
+        <v>-287.1450562464939</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7548390371019675</v>
+        <v>0.7501712374715762</v>
       </c>
       <c r="T94">
-        <v>9.75836117182841</v>
+        <v>9.695935212639776</v>
       </c>
       <c r="U94">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V94">
-        <v>0.09422988952055611</v>
+        <v>0.1005805370460088</v>
       </c>
       <c r="W94">
-        <v>0.2151816262525553</v>
+        <v>0.2001816262525552</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3926245396689839</v>
+        <v>0.4190855710250369</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2602718950648011</v>
+        <v>0.2459484710943698</v>
       </c>
       <c r="C95">
-        <v>-5178.161247109863</v>
+        <v>-4961.968196287336</v>
       </c>
       <c r="D95">
-        <v>3401.174752890138</v>
+        <v>3617.367803712664</v>
       </c>
       <c r="E95">
         <v>4956.436000000002</v>
@@ -9083,37 +9083,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M95">
-        <v>2243.668184501959</v>
+        <v>2102.003144501959</v>
       </c>
       <c r="N95">
-        <v>-1372.221245726449</v>
+        <v>-1230.556205726449</v>
       </c>
       <c r="O95">
-        <v>-329.3330989743478</v>
+        <v>-295.3334893743478</v>
       </c>
       <c r="P95">
-        <v>-1042.888146752101</v>
+        <v>-935.2227163521014</v>
       </c>
       <c r="Q95">
-        <v>-411.9881467521014</v>
+        <v>-304.3227163521015</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8561303281165344</v>
+        <v>0.8507956999675158</v>
       </c>
       <c r="T95">
-        <v>11.1524127678039</v>
+        <v>11.08106881444546</v>
       </c>
       <c r="U95">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V95">
-        <v>0.09321666490205552</v>
+        <v>0.09949902589497646</v>
       </c>
       <c r="W95">
-        <v>0.215422335587789</v>
+        <v>0.200422335587789</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3884027704252314</v>
+        <v>0.4145792745624021</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2621895710090941</v>
+        <v>0.2477161470386627</v>
       </c>
       <c r="C96">
-        <v>-5306.733965219903</v>
+        <v>-5091.699063472544</v>
       </c>
       <c r="D96">
-        <v>3374.154034780099</v>
+        <v>3589.188936527457</v>
       </c>
       <c r="E96">
         <v>5057.988000000001</v>
@@ -9165,37 +9165,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M96">
-        <v>2267.793648851443</v>
+        <v>2124.605328851443</v>
       </c>
       <c r="N96">
-        <v>-1396.346710075933</v>
+        <v>-1253.158390075932</v>
       </c>
       <c r="O96">
-        <v>-335.1232104182238</v>
+        <v>-300.7580136182237</v>
       </c>
       <c r="P96">
-        <v>-1061.223499657709</v>
+        <v>-952.4003764577087</v>
       </c>
       <c r="Q96">
-        <v>-430.3234996577088</v>
+        <v>-321.5003764577087</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9911853828026237</v>
+        <v>0.984961649962102</v>
       </c>
       <c r="T96">
-        <v>13.01114822910455</v>
+        <v>12.92791361685304</v>
       </c>
       <c r="U96">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V96">
-        <v>0.09222499825416131</v>
+        <v>0.09844052561949801</v>
       </c>
       <c r="W96">
-        <v>0.215657923447805</v>
+        <v>0.2006579234478049</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3842708260590055</v>
+        <v>0.4101688567479084</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.264107246953387</v>
+        <v>0.2494838229829557</v>
       </c>
       <c r="C97">
-        <v>-5434.880733751885</v>
+        <v>-5220.994304054927</v>
       </c>
       <c r="D97">
-        <v>3347.559266248115</v>
+        <v>3561.445695945074</v>
       </c>
       <c r="E97">
         <v>5159.540000000001</v>
@@ -9247,37 +9247,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M97">
-        <v>2291.919113200926</v>
+        <v>2147.207513200926</v>
       </c>
       <c r="N97">
-        <v>-1420.472174425416</v>
+        <v>-1275.760574425416</v>
       </c>
       <c r="O97">
-        <v>-340.9133218620997</v>
+        <v>-306.1825378620997</v>
       </c>
       <c r="P97">
-        <v>-1079.558852563316</v>
+        <v>-969.5780365633159</v>
       </c>
       <c r="Q97">
-        <v>-448.6588525633159</v>
+        <v>-338.6780365633159</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.180262459363149</v>
+        <v>1.172793979954523</v>
       </c>
       <c r="T97">
-        <v>15.61337787492547</v>
+        <v>15.51349634022366</v>
       </c>
       <c r="U97">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V97">
-        <v>0.09125420879885436</v>
+        <v>0.0974043095603454</v>
       </c>
       <c r="W97">
-        <v>0.2158885515633996</v>
+        <v>0.2008885515633995</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3802258699952266</v>
+        <v>0.4058512898347726</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2660249228976799</v>
+        <v>0.2512514989272486</v>
       </c>
       <c r="C98">
-        <v>-5562.611545825936</v>
+        <v>-5349.863942297909</v>
       </c>
       <c r="D98">
-        <v>3321.380454174064</v>
+        <v>3534.128057702091</v>
       </c>
       <c r="E98">
         <v>5261.092000000001</v>
@@ -9329,37 +9329,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M98">
-        <v>2316.044577550409</v>
+        <v>2169.80969755041</v>
       </c>
       <c r="N98">
-        <v>-1444.597638774899</v>
+        <v>-1298.362758774899</v>
       </c>
       <c r="O98">
-        <v>-346.7034333059758</v>
+        <v>-311.6070621059758</v>
       </c>
       <c r="P98">
-        <v>-1097.894205468923</v>
+        <v>-986.7556966689235</v>
       </c>
       <c r="Q98">
-        <v>-466.9942054689235</v>
+        <v>-355.8556966689235</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.463878074203933</v>
+        <v>1.454542474943151</v>
       </c>
       <c r="T98">
-        <v>19.5167223436568</v>
+        <v>19.39187042527953</v>
       </c>
       <c r="U98">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V98">
-        <v>0.09030364412386629</v>
+        <v>0.09638968133575847</v>
       </c>
       <c r="W98">
-        <v>0.2161143749265859</v>
+        <v>0.2011143749265859</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.376265183849443</v>
+        <v>0.401623672232327</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2679425988419728</v>
+        <v>0.2530191748715415</v>
       </c>
       <c r="C99">
-        <v>-5689.936084392266</v>
+        <v>-5478.317697246463</v>
       </c>
       <c r="D99">
-        <v>3295.607915607734</v>
+        <v>3507.226302753537</v>
       </c>
       <c r="E99">
         <v>5362.644</v>
@@ -9411,37 +9411,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M99">
-        <v>2340.170041899893</v>
+        <v>2192.411881899893</v>
       </c>
       <c r="N99">
-        <v>-1468.723103124383</v>
+        <v>-1320.964943124382</v>
       </c>
       <c r="O99">
-        <v>-352.4935447498518</v>
+        <v>-317.0315863498518</v>
       </c>
       <c r="P99">
-        <v>-1116.229558374531</v>
+        <v>-1003.933356774531</v>
       </c>
       <c r="Q99">
-        <v>-485.3295583745308</v>
+        <v>-373.0333567745307</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.936570765605244</v>
+        <v>1.924123299924201</v>
       </c>
       <c r="T99">
-        <v>26.02229645820906</v>
+        <v>25.85582723370604</v>
       </c>
       <c r="U99">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V99">
-        <v>0.08937267872052745</v>
+        <v>0.09539597328075065</v>
       </c>
       <c r="W99">
-        <v>0.2163355421379541</v>
+        <v>0.201335542137954</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3723861613355312</v>
+        <v>0.3974832220031278</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2698602747862657</v>
+        <v>0.2547868508158344</v>
       </c>
       <c r="C100">
-        <v>-5816.863734172461</v>
+        <v>-5606.364994255948</v>
       </c>
       <c r="D100">
-        <v>3270.232265827541</v>
+        <v>3480.731005744054</v>
       </c>
       <c r="E100">
         <v>5464.196000000002</v>
@@ -9493,37 +9493,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M100">
-        <v>2364.295506249377</v>
+        <v>2215.014066249376</v>
       </c>
       <c r="N100">
-        <v>-1492.848567473866</v>
+        <v>-1343.567127473866</v>
       </c>
       <c r="O100">
-        <v>-358.2836561937279</v>
+        <v>-322.4561105937278</v>
       </c>
       <c r="P100">
-        <v>-1134.564911280138</v>
+        <v>-1021.111016880138</v>
       </c>
       <c r="Q100">
-        <v>-503.6649112801384</v>
+        <v>-390.2110168801383</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.881956148407866</v>
+        <v>2.863284949886301</v>
       </c>
       <c r="T100">
-        <v>39.03344468731358</v>
+        <v>38.78374085055906</v>
       </c>
       <c r="U100">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V100">
-        <v>0.08846071261113432</v>
+        <v>0.09442254498196748</v>
       </c>
       <c r="W100">
-        <v>0.2165521957327636</v>
+        <v>0.2015521957327636</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.368586302546393</v>
+        <v>0.3934272707581978</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2717779507305587</v>
+        <v>0.2565545267601274</v>
       </c>
       <c r="C101">
-        <v>-5943.403593053306</v>
+        <v>-5734.014976002298</v>
       </c>
       <c r="D101">
-        <v>3245.244406946695</v>
+        <v>3454.633023997703</v>
       </c>
       <c r="E101">
         <v>5565.748000000001</v>
@@ -9575,37 +9575,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M101">
-        <v>2388.42097059886</v>
+        <v>2237.61625059886</v>
       </c>
       <c r="N101">
-        <v>-1516.97403182335</v>
+        <v>-1366.16931182335</v>
       </c>
       <c r="O101">
-        <v>-364.073767637604</v>
+        <v>-327.8806348376039</v>
       </c>
       <c r="P101">
-        <v>-1152.900264185746</v>
+        <v>-1038.288676985746</v>
       </c>
       <c r="Q101">
-        <v>-522.000264185746</v>
+        <v>-407.388676985746</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.718112296815733</v>
+        <v>5.680769899772601</v>
       </c>
       <c r="T101">
-        <v>78.06688937462718</v>
+        <v>77.5674817011181</v>
       </c>
       <c r="U101">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V101">
-        <v>0.08756717005950669</v>
+        <v>0.09346878190134153</v>
       </c>
       <c r="W101">
-        <v>0.216764472487274</v>
+        <v>0.201764472487274</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.364863208581278</v>
+        <v>0.3894532579222565</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/italy/italy_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_rubber_tires.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1078956651156416</v>
+        <v>0.1078363492370267</v>
       </c>
       <c r="C2">
-        <v>10215.9325301295</v>
+        <v>10120.75301137926</v>
       </c>
       <c r="D2">
-        <v>9350.932530129496</v>
+        <v>9357.305011379261</v>
       </c>
       <c r="E2">
-        <v>-4487.9</v>
+        <v>-4386.348</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>101.552</v>
       </c>
       <c r="G2">
         <v>865</v>
@@ -1457,28 +1457,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.31860834948343</v>
       </c>
       <c r="N2">
-        <v>871.4469387755101</v>
+        <v>864.1283304260268</v>
       </c>
       <c r="O2">
-        <v>209.1472653061224</v>
+        <v>207.3907993022464</v>
       </c>
       <c r="P2">
-        <v>662.2996734693877</v>
+        <v>656.7375311237804</v>
       </c>
       <c r="Q2">
-        <v>1293.199673469388</v>
+        <v>1287.63753112378</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1078956651156416</v>
+        <v>0.1083723591104687</v>
       </c>
       <c r="T2">
-        <v>0.8547702034345667</v>
+        <v>0.8613320757033573</v>
       </c>
       <c r="U2">
         <v>0.07206759442929168</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>119.0727659087017</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1078363492370267</v>
+        <v>0.1077770333584118</v>
       </c>
       <c r="C3">
-        <v>10120.75301137926</v>
+        <v>10025.58218399964</v>
       </c>
       <c r="D3">
-        <v>9357.305011379261</v>
+        <v>9363.68618399964</v>
       </c>
       <c r="E3">
-        <v>-4386.348</v>
+        <v>-4284.795999999999</v>
       </c>
       <c r="F3">
-        <v>101.552</v>
+        <v>203.104</v>
       </c>
       <c r="G3">
         <v>865</v>
@@ -1539,28 +1539,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M3">
-        <v>7.31860834948343</v>
+        <v>14.63721669896686</v>
       </c>
       <c r="N3">
-        <v>864.1283304260268</v>
+        <v>856.8097220765433</v>
       </c>
       <c r="O3">
-        <v>207.3907993022464</v>
+        <v>205.6343332983704</v>
       </c>
       <c r="P3">
-        <v>656.7375311237804</v>
+        <v>651.1753887781729</v>
       </c>
       <c r="Q3">
-        <v>1287.63753112378</v>
+        <v>1282.075388778173</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1083723591104687</v>
+        <v>0.1088587815541699</v>
       </c>
       <c r="T3">
-        <v>0.8613320757033573</v>
+        <v>0.8680278637327354</v>
       </c>
       <c r="U3">
         <v>0.07206759442929168</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.0727659087017</v>
+        <v>59.53638295435085</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1077770333584118</v>
+        <v>0.1077177174797968</v>
       </c>
       <c r="C4">
-        <v>10025.58218399964</v>
+        <v>9930.420065783888</v>
       </c>
       <c r="D4">
-        <v>9363.68618399964</v>
+        <v>9370.076065783889</v>
       </c>
       <c r="E4">
-        <v>-4284.795999999999</v>
+        <v>-4183.244</v>
       </c>
       <c r="F4">
-        <v>203.104</v>
+        <v>304.656</v>
       </c>
       <c r="G4">
         <v>865</v>
@@ -1621,28 +1621,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M4">
-        <v>14.63721669896686</v>
+        <v>21.95582504845029</v>
       </c>
       <c r="N4">
-        <v>856.8097220765433</v>
+        <v>849.4911137270599</v>
       </c>
       <c r="O4">
-        <v>205.6343332983704</v>
+        <v>203.8778672944944</v>
       </c>
       <c r="P4">
-        <v>651.1753887781729</v>
+        <v>645.6132464325656</v>
       </c>
       <c r="Q4">
-        <v>1282.075388778173</v>
+        <v>1276.513246432566</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1088587815541699</v>
+        <v>0.1093552333266072</v>
       </c>
       <c r="T4">
-        <v>0.8680278637327354</v>
+        <v>0.8748617092472555</v>
       </c>
       <c r="U4">
         <v>0.07206759442929168</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.53638295435085</v>
+        <v>39.69092196956724</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1077177174797968</v>
+        <v>0.1076584016011819</v>
       </c>
       <c r="C5">
-        <v>9930.420065783888</v>
+        <v>9835.266674573861</v>
       </c>
       <c r="D5">
-        <v>9370.076065783889</v>
+        <v>9376.474674573861</v>
       </c>
       <c r="E5">
-        <v>-4183.244</v>
+        <v>-4081.692</v>
       </c>
       <c r="F5">
-        <v>304.656</v>
+        <v>406.208</v>
       </c>
       <c r="G5">
         <v>865</v>
@@ -1703,28 +1703,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M5">
-        <v>21.95582504845029</v>
+        <v>29.27443339793372</v>
       </c>
       <c r="N5">
-        <v>849.4911137270599</v>
+        <v>842.1725053775764</v>
       </c>
       <c r="O5">
-        <v>203.8778672944944</v>
+        <v>202.1214012906183</v>
       </c>
       <c r="P5">
-        <v>645.6132464325656</v>
+        <v>640.051104086958</v>
       </c>
       <c r="Q5">
-        <v>1276.513246432566</v>
+        <v>1270.951104086958</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1093552333266072</v>
+        <v>0.1098620278443036</v>
       </c>
       <c r="T5">
-        <v>0.8748617092472555</v>
+        <v>0.881837926543328</v>
       </c>
       <c r="U5">
         <v>0.07206759442929168</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.69092196956724</v>
+        <v>29.76819147717542</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1076584016011819</v>
+        <v>0.107599085722567</v>
       </c>
       <c r="C6">
-        <v>9835.266674573861</v>
+        <v>9740.122028260192</v>
       </c>
       <c r="D6">
-        <v>9376.474674573861</v>
+        <v>9382.882028260192</v>
       </c>
       <c r="E6">
-        <v>-4081.692</v>
+        <v>-3980.139999999999</v>
       </c>
       <c r="F6">
-        <v>406.208</v>
+        <v>507.76</v>
       </c>
       <c r="G6">
         <v>865</v>
@@ -1785,28 +1785,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M6">
-        <v>29.27443339793372</v>
+        <v>36.59304174741715</v>
       </c>
       <c r="N6">
-        <v>842.1725053775764</v>
+        <v>834.853897028093</v>
       </c>
       <c r="O6">
-        <v>202.1214012906183</v>
+        <v>200.3649352867423</v>
       </c>
       <c r="P6">
-        <v>640.051104086958</v>
+        <v>634.4889617413507</v>
       </c>
       <c r="Q6">
-        <v>1270.951104086958</v>
+        <v>1265.388961741351</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1098620278443036</v>
+        <v>0.1103794917202673</v>
       </c>
       <c r="T6">
-        <v>0.881837926543328</v>
+        <v>0.8889610115719494</v>
       </c>
       <c r="U6">
         <v>0.07206759442929168</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.76819147717542</v>
+        <v>23.81455318174034</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.107599085722567</v>
+        <v>0.1075397698439521</v>
       </c>
       <c r="C7">
-        <v>9740.122028260192</v>
+        <v>9644.986144782446</v>
       </c>
       <c r="D7">
-        <v>9382.882028260192</v>
+        <v>9389.298144782446</v>
       </c>
       <c r="E7">
-        <v>-3980.139999999999</v>
+        <v>-3878.588</v>
       </c>
       <c r="F7">
-        <v>507.76</v>
+        <v>609.3120000000001</v>
       </c>
       <c r="G7">
         <v>865</v>
@@ -1867,28 +1867,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M7">
-        <v>36.59304174741715</v>
+        <v>43.91165009690059</v>
       </c>
       <c r="N7">
-        <v>834.853897028093</v>
+        <v>827.5352886786095</v>
       </c>
       <c r="O7">
-        <v>200.3649352867423</v>
+        <v>198.6084692828663</v>
       </c>
       <c r="P7">
-        <v>634.4889617413507</v>
+        <v>628.9268193957432</v>
       </c>
       <c r="Q7">
-        <v>1265.388961741351</v>
+        <v>1259.826819395743</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1103794917202673</v>
+        <v>0.1109079654659323</v>
       </c>
       <c r="T7">
-        <v>0.8889610115719494</v>
+        <v>0.8962356516011797</v>
       </c>
       <c r="U7">
         <v>0.07206759442929168</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.81455318174034</v>
+        <v>19.84546098478361</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1075397698439521</v>
+        <v>0.1074804539653371</v>
       </c>
       <c r="C8">
-        <v>9644.986144782446</v>
+        <v>9549.859042129292</v>
       </c>
       <c r="D8">
-        <v>9389.298144782446</v>
+        <v>9395.723042129292</v>
       </c>
       <c r="E8">
-        <v>-3878.588</v>
+        <v>-3777.036</v>
       </c>
       <c r="F8">
-        <v>609.312</v>
+        <v>710.864</v>
       </c>
       <c r="G8">
         <v>865</v>
@@ -1949,28 +1949,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M8">
-        <v>43.91165009690057</v>
+        <v>51.23025844638401</v>
       </c>
       <c r="N8">
-        <v>827.5352886786096</v>
+        <v>820.2166803291261</v>
       </c>
       <c r="O8">
-        <v>198.6084692828663</v>
+        <v>196.8520032789903</v>
       </c>
       <c r="P8">
-        <v>628.9268193957433</v>
+        <v>623.3646770501359</v>
       </c>
       <c r="Q8">
-        <v>1259.826819395743</v>
+        <v>1254.264677050136</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1109079654659323</v>
+        <v>0.1114478042383858</v>
       </c>
       <c r="T8">
-        <v>0.8962356516011797</v>
+        <v>0.9036667355020064</v>
       </c>
       <c r="U8">
         <v>0.07206759442929168</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.84546098478362</v>
+        <v>17.01039512981453</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1074804539653371</v>
+        <v>0.1074211380867222</v>
       </c>
       <c r="C9">
-        <v>9549.859042129292</v>
+        <v>9454.740738338669</v>
       </c>
       <c r="D9">
-        <v>9395.723042129292</v>
+        <v>9402.156738338668</v>
       </c>
       <c r="E9">
-        <v>-3777.036</v>
+        <v>-3675.483999999999</v>
       </c>
       <c r="F9">
-        <v>710.8640000000001</v>
+        <v>812.4160000000001</v>
       </c>
       <c r="G9">
         <v>865</v>
@@ -2031,28 +2031,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M9">
-        <v>51.23025844638401</v>
+        <v>58.54886679586744</v>
       </c>
       <c r="N9">
-        <v>820.2166803291261</v>
+        <v>812.8980719796427</v>
       </c>
       <c r="O9">
-        <v>196.8520032789903</v>
+        <v>195.0955372751143</v>
       </c>
       <c r="P9">
-        <v>623.3646770501359</v>
+        <v>617.8025347045285</v>
       </c>
       <c r="Q9">
-        <v>1254.264677050136</v>
+        <v>1248.702534704528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1114478042383858</v>
+        <v>0.1119993786363275</v>
       </c>
       <c r="T9">
-        <v>0.9036667355020064</v>
+        <v>0.9112593647050249</v>
       </c>
       <c r="U9">
         <v>0.07206759442929168</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.01039512981453</v>
+        <v>14.88409573858771</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1074211380867222</v>
+        <v>0.1073618222081073</v>
       </c>
       <c r="C10">
-        <v>9454.740738338669</v>
+        <v>9359.631251497953</v>
       </c>
       <c r="D10">
-        <v>9402.156738338668</v>
+        <v>9408.599251497953</v>
       </c>
       <c r="E10">
-        <v>-3675.483999999999</v>
+        <v>-3573.932</v>
       </c>
       <c r="F10">
-        <v>812.4160000000001</v>
+        <v>913.9680000000001</v>
       </c>
       <c r="G10">
         <v>865</v>
@@ -2113,28 +2113,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M10">
-        <v>58.54886679586744</v>
+        <v>65.86747514535087</v>
       </c>
       <c r="N10">
-        <v>812.8980719796427</v>
+        <v>805.5794636301592</v>
       </c>
       <c r="O10">
-        <v>195.0955372751143</v>
+        <v>193.3390712712382</v>
       </c>
       <c r="P10">
-        <v>617.8025347045285</v>
+        <v>612.2403923589211</v>
       </c>
       <c r="Q10">
-        <v>1248.702534704528</v>
+        <v>1243.140392358921</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1119993786363275</v>
+        <v>0.1125630755485096</v>
       </c>
       <c r="T10">
-        <v>0.9112593647050249</v>
+        <v>0.9190188648795384</v>
       </c>
       <c r="U10">
         <v>0.07206759442929168</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.88409573858771</v>
+        <v>13.23030732318908</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1073618222081073</v>
+        <v>0.1073025063294924</v>
       </c>
       <c r="C11">
-        <v>9359.631251497953</v>
+        <v>9264.53059974413</v>
       </c>
       <c r="D11">
-        <v>9408.599251497953</v>
+        <v>9415.050599744131</v>
       </c>
       <c r="E11">
-        <v>-3573.932</v>
+        <v>-3472.38</v>
       </c>
       <c r="F11">
-        <v>913.9680000000001</v>
+        <v>1015.52</v>
       </c>
       <c r="G11">
         <v>865</v>
@@ -2195,28 +2195,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M11">
-        <v>65.86747514535087</v>
+        <v>73.18608349483429</v>
       </c>
       <c r="N11">
-        <v>805.5794636301592</v>
+        <v>798.2608552806759</v>
       </c>
       <c r="O11">
-        <v>193.3390712712382</v>
+        <v>191.5826052673622</v>
       </c>
       <c r="P11">
-        <v>612.2403923589211</v>
+        <v>606.6782500133137</v>
       </c>
       <c r="Q11">
-        <v>1243.140392358921</v>
+        <v>1237.578250013314</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1125630755485096</v>
+        <v>0.1131392990587402</v>
       </c>
       <c r="T11">
-        <v>0.9190188648795384</v>
+        <v>0.9269507983912635</v>
       </c>
       <c r="U11">
         <v>0.07206759442929168</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.23030732318908</v>
+        <v>11.90727659087017</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1073025063294924</v>
+        <v>0.1072431904508774</v>
       </c>
       <c r="C12">
-        <v>9264.53059974413</v>
+        <v>9169.438801263967</v>
       </c>
       <c r="D12">
-        <v>9415.050599744131</v>
+        <v>9421.510801263967</v>
       </c>
       <c r="E12">
-        <v>-3472.38</v>
+        <v>-3370.828</v>
       </c>
       <c r="F12">
-        <v>1015.52</v>
+        <v>1117.072</v>
       </c>
       <c r="G12">
         <v>865</v>
@@ -2277,28 +2277,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M12">
-        <v>73.18608349483429</v>
+        <v>80.50469184431773</v>
       </c>
       <c r="N12">
-        <v>798.2608552806759</v>
+        <v>790.9422469311924</v>
       </c>
       <c r="O12">
-        <v>191.5826052673622</v>
+        <v>189.8261392634862</v>
       </c>
       <c r="P12">
-        <v>606.6782500133137</v>
+        <v>601.1161076677062</v>
       </c>
       <c r="Q12">
-        <v>1237.578250013314</v>
+        <v>1232.016107667706</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1131392990587402</v>
+        <v>0.1137284714118974</v>
       </c>
       <c r="T12">
-        <v>0.9269507983912635</v>
+        <v>0.935060977599881</v>
       </c>
       <c r="U12">
         <v>0.07206759442929168</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.90727659087017</v>
+        <v>10.82479690079106</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1072431904508774</v>
+        <v>0.1071838745722625</v>
       </c>
       <c r="C13">
-        <v>9169.438801263967</v>
+        <v>9074.355874294186</v>
       </c>
       <c r="D13">
-        <v>9421.510801263967</v>
+        <v>9427.979874294186</v>
       </c>
       <c r="E13">
-        <v>-3370.828</v>
+        <v>-3269.276</v>
       </c>
       <c r="F13">
-        <v>1117.072</v>
+        <v>1218.624</v>
       </c>
       <c r="G13">
         <v>865</v>
@@ -2359,28 +2359,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M13">
-        <v>80.50469184431773</v>
+        <v>87.82330019380115</v>
       </c>
       <c r="N13">
-        <v>790.9422469311924</v>
+        <v>783.623638581709</v>
       </c>
       <c r="O13">
-        <v>189.8261392634862</v>
+        <v>188.0696732596101</v>
       </c>
       <c r="P13">
-        <v>601.1161076677062</v>
+        <v>595.5539653220989</v>
       </c>
       <c r="Q13">
-        <v>1232.016107667706</v>
+        <v>1226.453965322099</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1137284714118974</v>
+        <v>0.1143310340458081</v>
       </c>
       <c r="T13">
-        <v>0.935060977599881</v>
+        <v>0.9433554790632398</v>
       </c>
       <c r="U13">
         <v>0.07206759442929168</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.82479690079106</v>
+        <v>9.922730492391809</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1071838745722625</v>
+        <v>0.1071245586936476</v>
       </c>
       <c r="C14">
-        <v>9074.355874294186</v>
+        <v>8979.281837121614</v>
       </c>
       <c r="D14">
-        <v>9427.979874294186</v>
+        <v>9434.457837121614</v>
       </c>
       <c r="E14">
-        <v>-3269.276</v>
+        <v>-3167.723999999999</v>
       </c>
       <c r="F14">
-        <v>1218.624</v>
+        <v>1320.176</v>
       </c>
       <c r="G14">
         <v>865</v>
@@ -2441,28 +2441,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M14">
-        <v>87.82330019380115</v>
+        <v>95.14190854328459</v>
       </c>
       <c r="N14">
-        <v>783.623638581709</v>
+        <v>776.3050302322256</v>
       </c>
       <c r="O14">
-        <v>188.0696732596101</v>
+        <v>186.3132072557341</v>
       </c>
       <c r="P14">
-        <v>595.5539653220989</v>
+        <v>589.9918229764914</v>
       </c>
       <c r="Q14">
-        <v>1226.453965322099</v>
+        <v>1220.891822976491</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1143310340458081</v>
+        <v>0.1149474486942915</v>
       </c>
       <c r="T14">
-        <v>0.9433554790632398</v>
+        <v>0.9518406587211589</v>
       </c>
       <c r="U14">
         <v>0.07206759442929168</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.922730492391809</v>
+        <v>9.159443531438592</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1071245586936476</v>
+        <v>0.1072248428150327</v>
       </c>
       <c r="C15">
-        <v>8979.281837121614</v>
+        <v>8866.782871685522</v>
       </c>
       <c r="D15">
-        <v>9434.457837121614</v>
+        <v>9423.510871685523</v>
       </c>
       <c r="E15">
-        <v>-3167.723999999999</v>
+        <v>-3066.172</v>
       </c>
       <c r="F15">
-        <v>1320.176</v>
+        <v>1421.728</v>
       </c>
       <c r="G15">
         <v>865</v>
@@ -2523,45 +2523,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M15">
-        <v>95.14190854328459</v>
+        <v>104.593108892768</v>
       </c>
       <c r="N15">
-        <v>776.3050302322256</v>
+        <v>766.8538298827422</v>
       </c>
       <c r="O15">
-        <v>186.3132072557341</v>
+        <v>184.0449191718581</v>
       </c>
       <c r="P15">
-        <v>589.9918229764914</v>
+        <v>582.808910710884</v>
       </c>
       <c r="Q15">
-        <v>1220.891822976491</v>
+        <v>1213.708910710884</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1149474486942915</v>
+        <v>0.1155781985671582</v>
       </c>
       <c r="T15">
-        <v>0.9518406587211589</v>
+        <v>0.9605231681385642</v>
       </c>
       <c r="U15">
-        <v>0.07206759442929168</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.05477137176626168</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.159443531438592</v>
+        <v>8.331781586767285</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1072248428150327</v>
+        <v>0.1071769269364178</v>
       </c>
       <c r="C16">
-        <v>8866.782871685522</v>
+        <v>8770.458174474112</v>
       </c>
       <c r="D16">
-        <v>9423.510871685523</v>
+        <v>9428.738174474112</v>
       </c>
       <c r="E16">
-        <v>-3066.172</v>
+        <v>-2964.619999999999</v>
       </c>
       <c r="F16">
-        <v>1421.728</v>
+        <v>1523.28</v>
       </c>
       <c r="G16">
         <v>865</v>
@@ -2605,28 +2605,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M16">
-        <v>104.593108892768</v>
+        <v>112.0640452422515</v>
       </c>
       <c r="N16">
-        <v>766.8538298827422</v>
+        <v>759.3828935332587</v>
       </c>
       <c r="O16">
-        <v>184.0449191718581</v>
+        <v>182.2518944479821</v>
       </c>
       <c r="P16">
-        <v>582.808910710884</v>
+        <v>577.1309990852766</v>
       </c>
       <c r="Q16">
-        <v>1213.708910710884</v>
+        <v>1208.030999085277</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1155781985671582</v>
+        <v>0.1162237896135041</v>
       </c>
       <c r="T16">
-        <v>0.9605231681385642</v>
+        <v>0.9694099718952028</v>
       </c>
       <c r="U16">
         <v>0.07356759442929167</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.331781586767285</v>
+        <v>7.776329480982799</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1071769269364177</v>
+        <v>0.1071290110578028</v>
       </c>
       <c r="C17">
-        <v>8770.458174474114</v>
+        <v>8674.139279741305</v>
       </c>
       <c r="D17">
-        <v>9428.738174474114</v>
+        <v>9433.971279741305</v>
       </c>
       <c r="E17">
-        <v>-2964.62</v>
+        <v>-2863.067999999999</v>
       </c>
       <c r="F17">
-        <v>1523.28</v>
+        <v>1624.832</v>
       </c>
       <c r="G17">
         <v>865</v>
@@ -2687,28 +2687,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M17">
-        <v>112.0640452422514</v>
+        <v>119.5349815917348</v>
       </c>
       <c r="N17">
-        <v>759.3828935332588</v>
+        <v>751.9119571837753</v>
       </c>
       <c r="O17">
-        <v>182.2518944479821</v>
+        <v>180.4588697241061</v>
       </c>
       <c r="P17">
-        <v>577.1309990852767</v>
+        <v>571.4530874596692</v>
       </c>
       <c r="Q17">
-        <v>1208.030999085277</v>
+        <v>1202.353087459669</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1162237896135041</v>
+        <v>0.1168847518752393</v>
       </c>
       <c r="T17">
-        <v>0.9694099718952026</v>
+        <v>0.9785083662174755</v>
       </c>
       <c r="U17">
         <v>0.07356759442929167</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.776329480982803</v>
+        <v>7.290308888421376</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1071290110578028</v>
+        <v>0.1070810951791879</v>
       </c>
       <c r="C18">
-        <v>8674.139279741305</v>
+        <v>8577.826197153881</v>
       </c>
       <c r="D18">
-        <v>9433.971279741305</v>
+        <v>9439.210197153881</v>
       </c>
       <c r="E18">
-        <v>-2863.067999999999</v>
+        <v>-2761.516</v>
       </c>
       <c r="F18">
-        <v>1624.832</v>
+        <v>1726.384</v>
       </c>
       <c r="G18">
         <v>865</v>
@@ -2769,28 +2769,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M18">
-        <v>119.5349815917348</v>
+        <v>127.0059179412183</v>
       </c>
       <c r="N18">
-        <v>751.9119571837753</v>
+        <v>744.4410208342919</v>
       </c>
       <c r="O18">
-        <v>180.4588697241061</v>
+        <v>178.66584500023</v>
       </c>
       <c r="P18">
-        <v>571.4530874596692</v>
+        <v>565.7751758340619</v>
       </c>
       <c r="Q18">
-        <v>1202.353087459669</v>
+        <v>1196.675175834062</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1168847518752393</v>
+        <v>0.1175616409384619</v>
       </c>
       <c r="T18">
-        <v>0.9785083662174755</v>
+        <v>0.9878259989571523</v>
       </c>
       <c r="U18">
         <v>0.07356759442929167</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.290308888421376</v>
+        <v>6.861467189102471</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1070810951791879</v>
+        <v>0.107265739300573</v>
       </c>
       <c r="C19">
-        <v>8577.826197153881</v>
+        <v>8456.11792030656</v>
       </c>
       <c r="D19">
-        <v>9439.210197153881</v>
+        <v>9419.05392030656</v>
       </c>
       <c r="E19">
-        <v>-2761.516</v>
+        <v>-2659.963999999999</v>
       </c>
       <c r="F19">
-        <v>1726.384</v>
+        <v>1827.936</v>
       </c>
       <c r="G19">
         <v>865</v>
@@ -2851,45 +2851,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M19">
-        <v>127.0059179412183</v>
+        <v>137.5843454907017</v>
       </c>
       <c r="N19">
-        <v>744.4410208342919</v>
+        <v>733.8625932848084</v>
       </c>
       <c r="O19">
-        <v>178.66584500023</v>
+        <v>176.127022388354</v>
       </c>
       <c r="P19">
-        <v>565.7751758340619</v>
+        <v>557.7355708964544</v>
       </c>
       <c r="Q19">
-        <v>1196.675175834062</v>
+        <v>1188.635570896454</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1175616409384619</v>
+        <v>0.1182550394910316</v>
       </c>
       <c r="T19">
-        <v>0.9878259989571523</v>
+        <v>0.9973708910319433</v>
       </c>
       <c r="U19">
-        <v>0.07356759442929167</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.05591137176626167</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.861467189102471</v>
+        <v>6.333910559863837</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.107265739300573</v>
+        <v>0.107230743421958</v>
       </c>
       <c r="C20">
-        <v>8456.11792030656</v>
+        <v>8358.379555620919</v>
       </c>
       <c r="D20">
-        <v>9419.05392030656</v>
+        <v>9422.867555620918</v>
       </c>
       <c r="E20">
-        <v>-2659.963999999999</v>
+        <v>-2558.411999999999</v>
       </c>
       <c r="F20">
-        <v>1827.936</v>
+        <v>1929.488</v>
       </c>
       <c r="G20">
         <v>865</v>
@@ -2933,28 +2933,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M20">
-        <v>137.5843454907017</v>
+        <v>145.2279202401851</v>
       </c>
       <c r="N20">
-        <v>733.8625932848084</v>
+        <v>726.2190185353249</v>
       </c>
       <c r="O20">
-        <v>176.127022388354</v>
+        <v>174.292564448478</v>
       </c>
       <c r="P20">
-        <v>557.7355708964544</v>
+        <v>551.926454086847</v>
       </c>
       <c r="Q20">
-        <v>1188.635570896454</v>
+        <v>1182.826454086847</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1182550394910316</v>
+        <v>0.1189655589955164</v>
       </c>
       <c r="T20">
-        <v>0.9973708910319431</v>
+        <v>1.00715145945426</v>
       </c>
       <c r="U20">
         <v>0.07526759442929168</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.333910559863837</v>
+        <v>6.000546846186793</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.107230743421958</v>
+        <v>0.1071957475433431</v>
       </c>
       <c r="C21">
-        <v>8358.379555620919</v>
+        <v>8260.644280354954</v>
       </c>
       <c r="D21">
-        <v>9422.867555620918</v>
+        <v>9426.684280354955</v>
       </c>
       <c r="E21">
-        <v>-2558.411999999999</v>
+        <v>-2456.86</v>
       </c>
       <c r="F21">
-        <v>1929.488</v>
+        <v>2031.04</v>
       </c>
       <c r="G21">
         <v>865</v>
@@ -3015,28 +3015,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M21">
-        <v>145.2279202401851</v>
+        <v>152.8714949896686</v>
       </c>
       <c r="N21">
-        <v>726.2190185353249</v>
+        <v>718.5754437858416</v>
       </c>
       <c r="O21">
-        <v>174.292564448478</v>
+        <v>172.458106508602</v>
       </c>
       <c r="P21">
-        <v>551.926454086847</v>
+        <v>546.1173372772396</v>
       </c>
       <c r="Q21">
-        <v>1182.826454086847</v>
+        <v>1177.01733727724</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1189655589955164</v>
+        <v>0.1196938414876135</v>
       </c>
       <c r="T21">
-        <v>1.00715145945426</v>
+        <v>1.017176542087134</v>
       </c>
       <c r="U21">
         <v>0.07526759442929168</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.000546846186793</v>
+        <v>5.700519503877453</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1071957475433431</v>
+        <v>0.1072884316647282</v>
       </c>
       <c r="C22">
-        <v>8260.644280354954</v>
+        <v>8148.990695578026</v>
       </c>
       <c r="D22">
-        <v>9426.684280354955</v>
+        <v>9416.582695578027</v>
       </c>
       <c r="E22">
-        <v>-2456.86</v>
+        <v>-2355.307999999999</v>
       </c>
       <c r="F22">
-        <v>2031.04</v>
+        <v>2132.592000000001</v>
       </c>
       <c r="G22">
         <v>865</v>
@@ -3097,45 +3097,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M22">
-        <v>152.8714949896686</v>
+        <v>162.221143339152</v>
       </c>
       <c r="N22">
-        <v>718.5754437858416</v>
+        <v>709.2257954363581</v>
       </c>
       <c r="O22">
-        <v>172.458106508602</v>
+        <v>170.2141909047259</v>
       </c>
       <c r="P22">
-        <v>546.1173372772396</v>
+        <v>539.0116045316322</v>
       </c>
       <c r="Q22">
-        <v>1177.01733727724</v>
+        <v>1169.911604531632</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1196938414876135</v>
+        <v>0.120440561511156</v>
       </c>
       <c r="T22">
-        <v>1.017176542087134</v>
+        <v>1.027455424280335</v>
       </c>
       <c r="U22">
-        <v>0.07526759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.05720337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.700519503877453</v>
+        <v>5.371968911312602</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1072884316647282</v>
+        <v>0.1072595157861133</v>
       </c>
       <c r="C23">
-        <v>8148.990695578026</v>
+        <v>8050.587894896553</v>
       </c>
       <c r="D23">
-        <v>9416.582695578027</v>
+        <v>9419.731894896553</v>
       </c>
       <c r="E23">
-        <v>-2355.308</v>
+        <v>-2253.755999999999</v>
       </c>
       <c r="F23">
-        <v>2132.592</v>
+        <v>2234.144</v>
       </c>
       <c r="G23">
         <v>865</v>
@@ -3179,28 +3179,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M23">
-        <v>162.221143339152</v>
+        <v>169.9459596886354</v>
       </c>
       <c r="N23">
-        <v>709.2257954363581</v>
+        <v>701.5009790868747</v>
       </c>
       <c r="O23">
-        <v>170.2141909047259</v>
+        <v>168.3602349808499</v>
       </c>
       <c r="P23">
-        <v>539.0116045316322</v>
+        <v>533.1407441060248</v>
       </c>
       <c r="Q23">
-        <v>1169.911604531632</v>
+        <v>1164.040744106025</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.120440561511156</v>
+        <v>0.1212064282019689</v>
       </c>
       <c r="T23">
-        <v>1.027455424280335</v>
+        <v>1.037997867555412</v>
       </c>
       <c r="U23">
         <v>0.07606759442929167</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.371968911312603</v>
+        <v>5.12778850625294</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1072595157861133</v>
+        <v>0.1072305999074984</v>
       </c>
       <c r="C24">
-        <v>8050.587894896553</v>
+        <v>7952.187201300945</v>
       </c>
       <c r="D24">
-        <v>9419.731894896553</v>
+        <v>9422.883201300945</v>
       </c>
       <c r="E24">
-        <v>-2253.755999999999</v>
+        <v>-2152.203999999999</v>
       </c>
       <c r="F24">
-        <v>2234.144</v>
+        <v>2335.696</v>
       </c>
       <c r="G24">
         <v>865</v>
@@ -3261,28 +3261,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M24">
-        <v>169.9459596886354</v>
+        <v>177.6707760381189</v>
       </c>
       <c r="N24">
-        <v>701.5009790868747</v>
+        <v>693.7761627373912</v>
       </c>
       <c r="O24">
-        <v>168.3602349808499</v>
+        <v>166.5062790569739</v>
       </c>
       <c r="P24">
-        <v>533.1407441060248</v>
+        <v>527.2698836804174</v>
       </c>
       <c r="Q24">
-        <v>1164.040744106025</v>
+        <v>1158.169883680417</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1212064282019689</v>
+        <v>0.1219921875341015</v>
       </c>
       <c r="T24">
-        <v>1.037997867555412</v>
+        <v>1.048814140525946</v>
       </c>
       <c r="U24">
         <v>0.07606759442929167</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.12778850625294</v>
+        <v>4.904841179894115</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1072305999074984</v>
+        <v>0.1072016840288834</v>
       </c>
       <c r="C25">
-        <v>7952.187201300945</v>
+        <v>7853.788616906652</v>
       </c>
       <c r="D25">
-        <v>9422.883201300945</v>
+        <v>9426.036616906653</v>
       </c>
       <c r="E25">
-        <v>-2152.203999999999</v>
+        <v>-2050.651999999999</v>
       </c>
       <c r="F25">
-        <v>2335.696</v>
+        <v>2437.248000000001</v>
       </c>
       <c r="G25">
         <v>865</v>
@@ -3343,28 +3343,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M25">
-        <v>177.6707760381189</v>
+        <v>185.3955923876023</v>
       </c>
       <c r="N25">
-        <v>693.7761627373912</v>
+        <v>686.0513463879079</v>
       </c>
       <c r="O25">
-        <v>166.5062790569739</v>
+        <v>164.6523231330979</v>
       </c>
       <c r="P25">
-        <v>527.2698836804174</v>
+        <v>521.39902325481</v>
       </c>
       <c r="Q25">
-        <v>1158.169883680417</v>
+        <v>1152.29902325481</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1219921875341015</v>
+        <v>0.1227986247433956</v>
       </c>
       <c r="T25">
-        <v>1.048814140525946</v>
+        <v>1.059915052258863</v>
       </c>
       <c r="U25">
         <v>0.07606759442929167</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.904841179894115</v>
+        <v>4.700472797398527</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1072016840288834</v>
+        <v>0.1071727681502685</v>
       </c>
       <c r="C26">
-        <v>7853.788616906653</v>
+        <v>7755.392143831938</v>
       </c>
       <c r="D26">
-        <v>9426.036616906653</v>
+        <v>9429.192143831939</v>
       </c>
       <c r="E26">
-        <v>-2050.652</v>
+        <v>-1949.099999999999</v>
       </c>
       <c r="F26">
-        <v>2437.248</v>
+        <v>2538.8</v>
       </c>
       <c r="G26">
         <v>865</v>
@@ -3425,28 +3425,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M26">
-        <v>185.3955923876023</v>
+        <v>193.1204087370857</v>
       </c>
       <c r="N26">
-        <v>686.0513463879079</v>
+        <v>678.3265300384244</v>
       </c>
       <c r="O26">
-        <v>164.6523231330979</v>
+        <v>162.7983672092219</v>
       </c>
       <c r="P26">
-        <v>521.39902325481</v>
+        <v>515.5281628292025</v>
       </c>
       <c r="Q26">
-        <v>1152.29902325481</v>
+        <v>1146.428162829202</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1227986247433956</v>
+        <v>0.1236265669449375</v>
       </c>
       <c r="T26">
-        <v>1.059915052258863</v>
+        <v>1.071311988304657</v>
       </c>
       <c r="U26">
         <v>0.07606759442929167</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.700472797398528</v>
+        <v>4.512453885502587</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1071727681502685</v>
+        <v>0.1071438522716536</v>
       </c>
       <c r="C27">
-        <v>7755.392143831938</v>
+        <v>7656.99778419792</v>
       </c>
       <c r="D27">
-        <v>9429.192143831939</v>
+        <v>9432.349784197921</v>
       </c>
       <c r="E27">
-        <v>-1949.099999999999</v>
+        <v>-1847.547999999999</v>
       </c>
       <c r="F27">
-        <v>2538.8</v>
+        <v>2640.352</v>
       </c>
       <c r="G27">
         <v>865</v>
@@ -3507,28 +3507,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M27">
-        <v>193.1204087370857</v>
+        <v>200.8452250865691</v>
       </c>
       <c r="N27">
-        <v>678.3265300384244</v>
+        <v>670.601713688941</v>
       </c>
       <c r="O27">
-        <v>162.7983672092219</v>
+        <v>160.9444112853458</v>
       </c>
       <c r="P27">
-        <v>515.5281628292025</v>
+        <v>509.6573024035952</v>
       </c>
       <c r="Q27">
-        <v>1146.428162829202</v>
+        <v>1140.557302403595</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1236265669449375</v>
+        <v>0.1244768859627372</v>
       </c>
       <c r="T27">
-        <v>1.071311988304657</v>
+        <v>1.083016949648986</v>
       </c>
       <c r="U27">
         <v>0.07606759442929167</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.512453885502587</v>
+        <v>4.338897966829411</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1071438522716536</v>
+        <v>0.1073201363930387</v>
       </c>
       <c r="C28">
-        <v>7656.99778419792</v>
+        <v>7536.228184651249</v>
       </c>
       <c r="D28">
-        <v>9432.349784197921</v>
+        <v>9413.132184651249</v>
       </c>
       <c r="E28">
-        <v>-1847.547999999999</v>
+        <v>-1745.995999999999</v>
       </c>
       <c r="F28">
-        <v>2640.352</v>
+        <v>2741.904</v>
       </c>
       <c r="G28">
         <v>865</v>
@@ -3589,45 +3589,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M28">
-        <v>200.8452250865691</v>
+        <v>211.3119454360526</v>
       </c>
       <c r="N28">
-        <v>670.601713688941</v>
+        <v>660.1349933394575</v>
       </c>
       <c r="O28">
-        <v>160.9444112853458</v>
+        <v>158.4323984014698</v>
       </c>
       <c r="P28">
-        <v>509.6573024035952</v>
+        <v>501.7025949379877</v>
       </c>
       <c r="Q28">
-        <v>1140.557302403595</v>
+        <v>1132.602594937988</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1244768859627372</v>
+        <v>0.1253505013919836</v>
       </c>
       <c r="T28">
-        <v>1.083016949648986</v>
+        <v>1.095042594865763</v>
       </c>
       <c r="U28">
-        <v>0.07606759442929167</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.05781137176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.338897966829411</v>
+        <v>4.123983322273791</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1073201363930387</v>
+        <v>0.1072988205144237</v>
       </c>
       <c r="C29">
-        <v>7536.228184651249</v>
+        <v>7436.99577048619</v>
       </c>
       <c r="D29">
-        <v>9413.132184651249</v>
+        <v>9415.45177048619</v>
       </c>
       <c r="E29">
-        <v>-1745.995999999999</v>
+        <v>-1644.443999999999</v>
       </c>
       <c r="F29">
-        <v>2741.904</v>
+        <v>2843.456000000001</v>
       </c>
       <c r="G29">
         <v>865</v>
@@ -3671,28 +3671,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M29">
-        <v>211.3119454360526</v>
+        <v>219.138313785536</v>
       </c>
       <c r="N29">
-        <v>660.1349933394575</v>
+        <v>652.3086249899741</v>
       </c>
       <c r="O29">
-        <v>158.4323984014698</v>
+        <v>156.5540699975938</v>
       </c>
       <c r="P29">
-        <v>501.7025949379877</v>
+        <v>495.7545549923803</v>
       </c>
       <c r="Q29">
-        <v>1132.602594937988</v>
+        <v>1126.65455499238</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1253505013919836</v>
+        <v>0.1262483839164868</v>
       </c>
       <c r="T29">
-        <v>1.095042594865763</v>
+        <v>1.107402285783005</v>
       </c>
       <c r="U29">
         <v>0.07706759442929167</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.123983322273791</v>
+        <v>3.976698203621155</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1072988205144237</v>
+        <v>0.1072775046358088</v>
       </c>
       <c r="C30">
-        <v>7436.99577048619</v>
+        <v>7337.764499788477</v>
       </c>
       <c r="D30">
-        <v>9415.45177048619</v>
+        <v>9417.772499788478</v>
       </c>
       <c r="E30">
-        <v>-1644.443999999999</v>
+        <v>-1542.891999999999</v>
       </c>
       <c r="F30">
-        <v>2843.456000000001</v>
+        <v>2945.008000000001</v>
       </c>
       <c r="G30">
         <v>865</v>
@@ -3753,28 +3753,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M30">
-        <v>219.138313785536</v>
+        <v>226.9646821350195</v>
       </c>
       <c r="N30">
-        <v>652.3086249899741</v>
+        <v>644.4822566404907</v>
       </c>
       <c r="O30">
-        <v>156.5540699975938</v>
+        <v>154.6757415937178</v>
       </c>
       <c r="P30">
-        <v>495.7545549923803</v>
+        <v>489.806515046773</v>
       </c>
       <c r="Q30">
-        <v>1126.65455499238</v>
+        <v>1120.706515046773</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1262483839164868</v>
+        <v>0.1271715589064689</v>
       </c>
       <c r="T30">
-        <v>1.107402285783005</v>
+        <v>1.120110137007776</v>
       </c>
       <c r="U30">
         <v>0.07706759442929167</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.976698203621155</v>
+        <v>3.839570679358357</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1072775046358088</v>
+        <v>0.1072561887571939</v>
       </c>
       <c r="C31">
-        <v>7337.764499788478</v>
+        <v>7238.534373403847</v>
       </c>
       <c r="D31">
-        <v>9417.772499788478</v>
+        <v>9420.094373403846</v>
       </c>
       <c r="E31">
-        <v>-1542.892</v>
+        <v>-1441.34</v>
       </c>
       <c r="F31">
-        <v>2945.008</v>
+        <v>3046.56</v>
       </c>
       <c r="G31">
         <v>865</v>
@@ -3835,28 +3835,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M31">
-        <v>226.9646821350194</v>
+        <v>234.7910504845028</v>
       </c>
       <c r="N31">
-        <v>644.4822566404907</v>
+        <v>636.6558882910073</v>
       </c>
       <c r="O31">
-        <v>154.6757415937178</v>
+        <v>152.7974131898417</v>
       </c>
       <c r="P31">
-        <v>489.806515046773</v>
+        <v>483.8584751011655</v>
       </c>
       <c r="Q31">
-        <v>1120.706515046773</v>
+        <v>1114.758475101165</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1271715589064689</v>
+        <v>0.1281211103247363</v>
       </c>
       <c r="T31">
-        <v>1.120110137007776</v>
+        <v>1.133181069696111</v>
       </c>
       <c r="U31">
         <v>0.07706759442929167</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.839570679358357</v>
+        <v>3.711584990046412</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1072561887571939</v>
+        <v>0.107234872878579</v>
       </c>
       <c r="C32">
-        <v>7238.534373403847</v>
+        <v>7139.305392178868</v>
       </c>
       <c r="D32">
-        <v>9420.094373403846</v>
+        <v>9422.417392178868</v>
       </c>
       <c r="E32">
-        <v>-1441.34</v>
+        <v>-1339.788</v>
       </c>
       <c r="F32">
-        <v>3046.56</v>
+        <v>3148.112</v>
       </c>
       <c r="G32">
         <v>865</v>
@@ -3917,28 +3917,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M32">
-        <v>234.7910504845028</v>
+        <v>242.6174188339863</v>
       </c>
       <c r="N32">
-        <v>636.6558882910073</v>
+        <v>628.8295199415238</v>
       </c>
       <c r="O32">
-        <v>152.7974131898417</v>
+        <v>150.9190847859657</v>
       </c>
       <c r="P32">
-        <v>483.8584751011655</v>
+        <v>477.9104351555581</v>
       </c>
       <c r="Q32">
-        <v>1114.758475101165</v>
+        <v>1108.810435155558</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1281211103247363</v>
+        <v>0.1290981849725186</v>
       </c>
       <c r="T32">
-        <v>1.133181069696111</v>
+        <v>1.146630869998601</v>
       </c>
       <c r="U32">
         <v>0.07706759442929167</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.711584990046412</v>
+        <v>3.591856441980398</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.107234872878579</v>
+        <v>0.107213556999964</v>
       </c>
       <c r="C33">
-        <v>7139.305392178868</v>
+        <v>7040.077556960949</v>
       </c>
       <c r="D33">
-        <v>9422.417392178868</v>
+        <v>9424.741556960949</v>
       </c>
       <c r="E33">
-        <v>-1339.788</v>
+        <v>-1238.235999999999</v>
       </c>
       <c r="F33">
-        <v>3148.112</v>
+        <v>3249.664</v>
       </c>
       <c r="G33">
         <v>865</v>
@@ -3999,28 +3999,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M33">
-        <v>242.6174188339863</v>
+        <v>250.4437871834697</v>
       </c>
       <c r="N33">
-        <v>628.8295199415238</v>
+        <v>621.0031515920405</v>
       </c>
       <c r="O33">
-        <v>150.9190847859657</v>
+        <v>149.0407563820897</v>
       </c>
       <c r="P33">
-        <v>477.9104351555581</v>
+        <v>471.9623952099507</v>
       </c>
       <c r="Q33">
-        <v>1108.810435155558</v>
+        <v>1102.862395209951</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1290981849725186</v>
+        <v>0.1301039971099416</v>
       </c>
       <c r="T33">
-        <v>1.146630869998601</v>
+        <v>1.160476252662929</v>
       </c>
       <c r="U33">
         <v>0.07706759442929167</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.591856441980398</v>
+        <v>3.479610928168511</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.107213556999964</v>
+        <v>0.1071922411213491</v>
       </c>
       <c r="C34">
-        <v>7040.077556960949</v>
+        <v>6940.850868598332</v>
       </c>
       <c r="D34">
-        <v>9424.741556960949</v>
+        <v>9427.066868598333</v>
       </c>
       <c r="E34">
-        <v>-1238.235999999999</v>
+        <v>-1136.683999999999</v>
       </c>
       <c r="F34">
-        <v>3249.664</v>
+        <v>3351.216</v>
       </c>
       <c r="G34">
         <v>865</v>
@@ -4081,28 +4081,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M34">
-        <v>250.4437871834697</v>
+        <v>258.2701555329531</v>
       </c>
       <c r="N34">
-        <v>621.0031515920405</v>
+        <v>613.176783242557</v>
       </c>
       <c r="O34">
-        <v>149.0407563820897</v>
+        <v>147.1624279782137</v>
       </c>
       <c r="P34">
-        <v>471.9623952099507</v>
+        <v>466.0143552643433</v>
       </c>
       <c r="Q34">
-        <v>1102.862395209951</v>
+        <v>1096.914355264343</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1301039971099416</v>
+        <v>0.1311398334902728</v>
       </c>
       <c r="T34">
-        <v>1.160476252662929</v>
+        <v>1.174734930332163</v>
       </c>
       <c r="U34">
         <v>0.07706759442929167</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.479610928168511</v>
+        <v>3.374168172769465</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1071922411213491</v>
+        <v>0.1071709252427342</v>
       </c>
       <c r="C35">
-        <v>6940.850868598332</v>
+        <v>6841.625327940099</v>
       </c>
       <c r="D35">
-        <v>9427.066868598333</v>
+        <v>9429.393327940099</v>
       </c>
       <c r="E35">
-        <v>-1136.683999999999</v>
+        <v>-1035.131999999999</v>
       </c>
       <c r="F35">
-        <v>3351.216</v>
+        <v>3452.768</v>
       </c>
       <c r="G35">
         <v>865</v>
@@ -4163,28 +4163,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M35">
-        <v>258.2701555329531</v>
+        <v>266.0965238824366</v>
       </c>
       <c r="N35">
-        <v>613.176783242557</v>
+        <v>605.3504148930735</v>
       </c>
       <c r="O35">
-        <v>147.1624279782137</v>
+        <v>145.2840995743377</v>
       </c>
       <c r="P35">
-        <v>466.0143552643433</v>
+        <v>460.0663153187359</v>
       </c>
       <c r="Q35">
-        <v>1096.914355264343</v>
+        <v>1090.966315318736</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1311398334902728</v>
+        <v>0.1322070588518261</v>
       </c>
       <c r="T35">
-        <v>1.174734930332163</v>
+        <v>1.189425689142888</v>
       </c>
       <c r="U35">
         <v>0.07706759442929167</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.374168172769465</v>
+        <v>3.274927932393893</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1071709252427342</v>
+        <v>0.1071496093641193</v>
       </c>
       <c r="C36">
-        <v>6841.625327940099</v>
+        <v>6742.400935836166</v>
       </c>
       <c r="D36">
-        <v>9429.393327940099</v>
+        <v>9431.720935836167</v>
       </c>
       <c r="E36">
-        <v>-1035.131999999999</v>
+        <v>-933.579999999999</v>
       </c>
       <c r="F36">
-        <v>3452.768</v>
+        <v>3554.320000000001</v>
       </c>
       <c r="G36">
         <v>865</v>
@@ -4245,28 +4245,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M36">
-        <v>266.0965238824366</v>
+        <v>273.9228922319201</v>
       </c>
       <c r="N36">
-        <v>605.3504148930735</v>
+        <v>597.5240465435901</v>
       </c>
       <c r="O36">
-        <v>145.2840995743377</v>
+        <v>143.4057711704616</v>
       </c>
       <c r="P36">
-        <v>460.0663153187359</v>
+        <v>454.1182753731285</v>
       </c>
       <c r="Q36">
-        <v>1090.966315318736</v>
+        <v>1085.018275373129</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1322070588518261</v>
+        <v>0.1333071219168118</v>
       </c>
       <c r="T36">
-        <v>1.189425689142888</v>
+        <v>1.204568471301636</v>
       </c>
       <c r="U36">
         <v>0.07706759442929167</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.274927932393893</v>
+        <v>3.181358562896924</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1071496093641193</v>
+        <v>0.1071282934855044</v>
       </c>
       <c r="C37">
-        <v>6742.400935836166</v>
+        <v>6643.17769313729</v>
       </c>
       <c r="D37">
-        <v>9431.720935836167</v>
+        <v>9434.049693137291</v>
       </c>
       <c r="E37">
-        <v>-933.579999999999</v>
+        <v>-832.0279999999989</v>
       </c>
       <c r="F37">
-        <v>3554.320000000001</v>
+        <v>3655.872000000001</v>
       </c>
       <c r="G37">
         <v>865</v>
@@ -4327,28 +4327,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M37">
-        <v>273.9228922319201</v>
+        <v>281.7492605814035</v>
       </c>
       <c r="N37">
-        <v>597.5240465435901</v>
+        <v>589.6976781941066</v>
       </c>
       <c r="O37">
-        <v>143.4057711704616</v>
+        <v>141.5274427665856</v>
       </c>
       <c r="P37">
-        <v>454.1182753731285</v>
+        <v>448.170235427521</v>
       </c>
       <c r="Q37">
-        <v>1085.018275373129</v>
+        <v>1079.070235427521</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1333071219168118</v>
+        <v>0.1344415619525784</v>
       </c>
       <c r="T37">
-        <v>1.204568471301636</v>
+        <v>1.220184465402844</v>
       </c>
       <c r="U37">
         <v>0.07706759442929167</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.181358562896924</v>
+        <v>3.092987491705343</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1071282934855043</v>
+        <v>0.1071069776068894</v>
       </c>
       <c r="C38">
-        <v>6643.177693137294</v>
+        <v>6543.955600695077</v>
       </c>
       <c r="D38">
-        <v>9434.049693137295</v>
+        <v>9436.379600695078</v>
       </c>
       <c r="E38">
-        <v>-832.0279999999993</v>
+        <v>-730.4759999999992</v>
       </c>
       <c r="F38">
-        <v>3655.872</v>
+        <v>3757.424</v>
       </c>
       <c r="G38">
         <v>865</v>
@@ -4409,28 +4409,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M38">
-        <v>281.7492605814035</v>
+        <v>289.5756289308869</v>
       </c>
       <c r="N38">
-        <v>589.6976781941066</v>
+        <v>581.8713098446233</v>
       </c>
       <c r="O38">
-        <v>141.5274427665856</v>
+        <v>139.6491143627096</v>
       </c>
       <c r="P38">
-        <v>448.170235427521</v>
+        <v>442.2221954819137</v>
       </c>
       <c r="Q38">
-        <v>1079.070235427521</v>
+        <v>1073.122195481914</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1344415619525784</v>
+        <v>0.1356120159577343</v>
       </c>
       <c r="T38">
-        <v>1.220184465402844</v>
+        <v>1.236296205348535</v>
       </c>
       <c r="U38">
         <v>0.07706759442929167</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.092987491705343</v>
+        <v>3.009393235172766</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1071069776068894</v>
+        <v>0.1078076617282745</v>
       </c>
       <c r="C39">
-        <v>6543.955600695077</v>
+        <v>6366.414112898809</v>
       </c>
       <c r="D39">
-        <v>9436.379600695078</v>
+        <v>9360.390112898809</v>
       </c>
       <c r="E39">
-        <v>-730.4759999999992</v>
+        <v>-628.9239999999995</v>
       </c>
       <c r="F39">
-        <v>3757.424</v>
+        <v>3858.976</v>
       </c>
       <c r="G39">
         <v>865</v>
@@ -4491,45 +4491,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M39">
-        <v>289.5756289308869</v>
+        <v>307.0494372803703</v>
       </c>
       <c r="N39">
-        <v>581.8713098446233</v>
+        <v>564.3975014951399</v>
       </c>
       <c r="O39">
-        <v>139.6491143627096</v>
+        <v>135.4554003588336</v>
       </c>
       <c r="P39">
-        <v>442.2221954819137</v>
+        <v>428.9421011363063</v>
       </c>
       <c r="Q39">
-        <v>1073.122195481914</v>
+        <v>1059.842101136306</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1356120159577343</v>
+        <v>0.1368202265437017</v>
       </c>
       <c r="T39">
-        <v>1.236296205348535</v>
+        <v>1.252927678840862</v>
       </c>
       <c r="U39">
-        <v>0.07706759442929167</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.05857137176626168</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.009393235172766</v>
+        <v>2.838132342772484</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1078076617282745</v>
+        <v>0.1078053458496596</v>
       </c>
       <c r="C40">
-        <v>6366.414112898809</v>
+        <v>6265.111255009397</v>
       </c>
       <c r="D40">
-        <v>9360.390112898809</v>
+        <v>9360.639255009397</v>
       </c>
       <c r="E40">
-        <v>-628.9239999999995</v>
+        <v>-527.3719999999994</v>
       </c>
       <c r="F40">
-        <v>3858.976</v>
+        <v>3960.528</v>
       </c>
       <c r="G40">
         <v>865</v>
@@ -4573,28 +4573,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M40">
-        <v>307.0494372803703</v>
+        <v>315.1296856298537</v>
       </c>
       <c r="N40">
-        <v>564.3975014951399</v>
+        <v>556.3172531456564</v>
       </c>
       <c r="O40">
-        <v>135.4554003588336</v>
+        <v>133.5161407549575</v>
       </c>
       <c r="P40">
-        <v>428.9421011363063</v>
+        <v>422.8011123906989</v>
       </c>
       <c r="Q40">
-        <v>1059.842101136306</v>
+        <v>1053.701112390699</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1368202265437017</v>
+        <v>0.1380680505915041</v>
       </c>
       <c r="T40">
-        <v>1.252927678840862</v>
+        <v>1.270104446546051</v>
       </c>
       <c r="U40">
         <v>0.07956759442929168</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.838132342772484</v>
+        <v>2.76535971859883</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1078053458496596</v>
+        <v>0.1078030299710447</v>
       </c>
       <c r="C41">
-        <v>6265.111255009397</v>
+        <v>6163.808410382991</v>
       </c>
       <c r="D41">
-        <v>9360.639255009397</v>
+        <v>9360.888410382991</v>
       </c>
       <c r="E41">
-        <v>-527.3719999999994</v>
+        <v>-425.8199999999993</v>
       </c>
       <c r="F41">
-        <v>3960.528</v>
+        <v>4062.08</v>
       </c>
       <c r="G41">
         <v>865</v>
@@ -4655,28 +4655,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M41">
-        <v>315.1296856298537</v>
+        <v>323.2099339793372</v>
       </c>
       <c r="N41">
-        <v>556.3172531456564</v>
+        <v>548.237004796173</v>
       </c>
       <c r="O41">
-        <v>133.5161407549575</v>
+        <v>131.5768811510815</v>
       </c>
       <c r="P41">
-        <v>422.8011123906989</v>
+        <v>416.6601236450915</v>
       </c>
       <c r="Q41">
-        <v>1053.701112390699</v>
+        <v>1047.560123645091</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1380680505915041</v>
+        <v>0.1393574687742333</v>
       </c>
       <c r="T41">
-        <v>1.270104446546051</v>
+        <v>1.287853773174747</v>
       </c>
       <c r="U41">
         <v>0.07956759442929168</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.76535971859883</v>
+        <v>2.69622572563386</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1078030299710447</v>
+        <v>0.1078007140924297</v>
       </c>
       <c r="C42">
-        <v>6163.808410382991</v>
+        <v>6062.505579020645</v>
       </c>
       <c r="D42">
-        <v>9360.888410382991</v>
+        <v>9361.137579020646</v>
       </c>
       <c r="E42">
-        <v>-425.8199999999993</v>
+        <v>-324.2679999999991</v>
       </c>
       <c r="F42">
-        <v>4062.08</v>
+        <v>4163.632000000001</v>
       </c>
       <c r="G42">
         <v>865</v>
@@ -4737,28 +4737,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M42">
-        <v>323.2099339793372</v>
+        <v>331.2901823288206</v>
       </c>
       <c r="N42">
-        <v>548.237004796173</v>
+        <v>540.1567564466895</v>
       </c>
       <c r="O42">
-        <v>131.5768811510815</v>
+        <v>129.6376215472055</v>
       </c>
       <c r="P42">
-        <v>416.6601236450915</v>
+        <v>410.519134899484</v>
       </c>
       <c r="Q42">
-        <v>1047.560123645091</v>
+        <v>1041.419134899484</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1393574687742333</v>
+        <v>0.1406905960479025</v>
       </c>
       <c r="T42">
-        <v>1.287853773174747</v>
+        <v>1.306204771892551</v>
       </c>
       <c r="U42">
         <v>0.07956759442929168</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.69622572563386</v>
+        <v>2.630464122569619</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1078007140924297</v>
+        <v>0.1077983982138148</v>
       </c>
       <c r="C43">
-        <v>6062.505579020645</v>
+        <v>5961.202760923421</v>
       </c>
       <c r="D43">
-        <v>9361.137579020646</v>
+        <v>9361.386760923422</v>
       </c>
       <c r="E43">
-        <v>-324.2679999999991</v>
+        <v>-222.7159999999985</v>
       </c>
       <c r="F43">
-        <v>4163.632000000001</v>
+        <v>4265.184000000001</v>
       </c>
       <c r="G43">
         <v>865</v>
@@ -4819,28 +4819,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M43">
-        <v>331.2901823288206</v>
+        <v>339.3704306783041</v>
       </c>
       <c r="N43">
-        <v>540.1567564466895</v>
+        <v>532.076508097206</v>
       </c>
       <c r="O43">
-        <v>129.6376215472055</v>
+        <v>127.6983619433294</v>
       </c>
       <c r="P43">
-        <v>410.519134899484</v>
+        <v>404.3781461538766</v>
       </c>
       <c r="Q43">
-        <v>1041.419134899484</v>
+        <v>1035.278146153877</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1406905960479025</v>
+        <v>0.1420696932275602</v>
       </c>
       <c r="T43">
-        <v>1.306204771892551</v>
+        <v>1.32518856366959</v>
       </c>
       <c r="U43">
         <v>0.07956759442929168</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.630464122569619</v>
+        <v>2.567834024413199</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1077983982138148</v>
+        <v>0.1077960823351999</v>
       </c>
       <c r="C44">
-        <v>5961.202760923422</v>
+        <v>5859.899956092378</v>
       </c>
       <c r="D44">
-        <v>9361.386760923422</v>
+        <v>9361.635956092377</v>
       </c>
       <c r="E44">
-        <v>-222.7159999999994</v>
+        <v>-121.1639999999998</v>
       </c>
       <c r="F44">
-        <v>4265.184</v>
+        <v>4366.736</v>
       </c>
       <c r="G44">
         <v>865</v>
@@ -4901,28 +4901,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M44">
-        <v>339.370430678304</v>
+        <v>347.4506790277874</v>
       </c>
       <c r="N44">
-        <v>532.0765080972062</v>
+        <v>523.9962597477227</v>
       </c>
       <c r="O44">
-        <v>127.6983619433295</v>
+        <v>125.7591023394534</v>
       </c>
       <c r="P44">
-        <v>404.3781461538767</v>
+        <v>398.2371574082692</v>
       </c>
       <c r="Q44">
-        <v>1035.278146153877</v>
+        <v>1029.137157408269</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1420696932275602</v>
+        <v>0.1434971797819428</v>
       </c>
       <c r="T44">
-        <v>1.32518856366959</v>
+        <v>1.344838453403718</v>
       </c>
       <c r="U44">
         <v>0.07956759442929168</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.5678340244132</v>
+        <v>2.508116954078009</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1077960823351999</v>
+        <v>0.108964166456585</v>
       </c>
       <c r="C45">
-        <v>5859.899956092378</v>
+        <v>5634.320648069483</v>
       </c>
       <c r="D45">
-        <v>9361.635956092377</v>
+        <v>9237.608648069483</v>
       </c>
       <c r="E45">
-        <v>-121.1639999999998</v>
+        <v>-19.61199999999917</v>
       </c>
       <c r="F45">
-        <v>4366.736</v>
+        <v>4468.288</v>
       </c>
       <c r="G45">
         <v>865</v>
@@ -4983,45 +4983,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M45">
-        <v>347.4506790277874</v>
+        <v>371.1699353772709</v>
       </c>
       <c r="N45">
-        <v>523.9962597477227</v>
+        <v>500.2770033982392</v>
       </c>
       <c r="O45">
-        <v>125.7591023394534</v>
+        <v>120.0664808155774</v>
       </c>
       <c r="P45">
-        <v>398.2371574082692</v>
+        <v>380.2105225826618</v>
       </c>
       <c r="Q45">
-        <v>1029.137157408269</v>
+        <v>1011.110522582662</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1434971797819428</v>
+        <v>0.1449756479989819</v>
       </c>
       <c r="T45">
-        <v>1.344838453403718</v>
+        <v>1.365190124914065</v>
       </c>
       <c r="U45">
-        <v>0.07956759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.06047137176626168</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.508116954078009</v>
+        <v>2.34783816175666</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.108964166456585</v>
+        <v>0.10898845057797</v>
       </c>
       <c r="C46">
-        <v>5634.320648069483</v>
+        <v>5530.225018875179</v>
       </c>
       <c r="D46">
-        <v>9237.608648069483</v>
+        <v>9235.065018875179</v>
       </c>
       <c r="E46">
-        <v>-19.61199999999917</v>
+        <v>81.94000000000051</v>
       </c>
       <c r="F46">
-        <v>4468.288</v>
+        <v>4569.84</v>
       </c>
       <c r="G46">
         <v>865</v>
@@ -5065,28 +5065,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M46">
-        <v>371.1699353772709</v>
+        <v>379.6056157267543</v>
       </c>
       <c r="N46">
-        <v>500.2770033982392</v>
+        <v>491.8413230487558</v>
       </c>
       <c r="O46">
-        <v>120.0664808155774</v>
+        <v>118.0419175317014</v>
       </c>
       <c r="P46">
-        <v>380.2105225826618</v>
+        <v>373.7994055170544</v>
       </c>
       <c r="Q46">
-        <v>1011.110522582662</v>
+        <v>1004.699405517054</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1449756479989819</v>
+        <v>0.1465078786966405</v>
       </c>
       <c r="T46">
-        <v>1.365190124914065</v>
+        <v>1.386281857206606</v>
       </c>
       <c r="U46">
         <v>0.08306759442929168</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.34783816175666</v>
+        <v>2.29566398038429</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.10898845057797</v>
+        <v>0.1099916146993551</v>
       </c>
       <c r="C47">
-        <v>5530.225018875179</v>
+        <v>5324.807435227282</v>
       </c>
       <c r="D47">
-        <v>9235.065018875179</v>
+        <v>9131.199435227283</v>
       </c>
       <c r="E47">
-        <v>81.94000000000051</v>
+        <v>183.4920000000011</v>
       </c>
       <c r="F47">
-        <v>4569.84</v>
+        <v>4671.392000000001</v>
       </c>
       <c r="G47">
         <v>865</v>
@@ -5147,45 +5147,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M47">
-        <v>379.6056157267543</v>
+        <v>401.1211936762378</v>
       </c>
       <c r="N47">
-        <v>491.8413230487558</v>
+        <v>470.3257450992724</v>
       </c>
       <c r="O47">
-        <v>118.0419175317014</v>
+        <v>112.8781788238254</v>
       </c>
       <c r="P47">
-        <v>373.7994055170544</v>
+        <v>357.447566275447</v>
       </c>
       <c r="Q47">
-        <v>1004.699405517054</v>
+        <v>988.347566275447</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1465078786966405</v>
+        <v>0.1480968586793977</v>
       </c>
       <c r="T47">
-        <v>1.386281857206606</v>
+        <v>1.408154764769242</v>
       </c>
       <c r="U47">
-        <v>0.08306759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V47">
         <v>0.24</v>
       </c>
       <c r="W47">
-        <v>0.06313137176626167</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.29566398038429</v>
+        <v>2.172527785901267</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1099916146993551</v>
+        <v>0.1100371788207402</v>
       </c>
       <c r="C48">
-        <v>5324.807435227282</v>
+        <v>5218.593258321981</v>
       </c>
       <c r="D48">
-        <v>9131.199435227283</v>
+        <v>9126.537258321981</v>
       </c>
       <c r="E48">
-        <v>183.4920000000011</v>
+        <v>285.0440000000008</v>
       </c>
       <c r="F48">
-        <v>4671.392000000001</v>
+        <v>4772.944</v>
       </c>
       <c r="G48">
         <v>865</v>
@@ -5229,28 +5229,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M48">
-        <v>401.1211936762378</v>
+        <v>409.8412196257212</v>
       </c>
       <c r="N48">
-        <v>470.3257450992724</v>
+        <v>461.605719149789</v>
       </c>
       <c r="O48">
-        <v>112.8781788238254</v>
+        <v>110.7853725959494</v>
       </c>
       <c r="P48">
-        <v>357.447566275447</v>
+        <v>350.8203465538396</v>
       </c>
       <c r="Q48">
-        <v>988.347566275447</v>
+        <v>981.7203465538396</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1480968586793977</v>
+        <v>0.1497458001709381</v>
       </c>
       <c r="T48">
-        <v>1.408154764769242</v>
+        <v>1.43085306507009</v>
       </c>
       <c r="U48">
         <v>0.08586759442929168</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.172527785901267</v>
+        <v>2.126303790456559</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1100371788207402</v>
+        <v>0.1100827429421253</v>
       </c>
       <c r="C49">
-        <v>5218.593258321981</v>
+        <v>5112.383839784176</v>
       </c>
       <c r="D49">
-        <v>9126.537258321981</v>
+        <v>9121.879839784177</v>
       </c>
       <c r="E49">
-        <v>285.0440000000008</v>
+        <v>386.5960000000014</v>
       </c>
       <c r="F49">
-        <v>4772.944</v>
+        <v>4874.496000000001</v>
       </c>
       <c r="G49">
         <v>865</v>
@@ -5311,28 +5311,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M49">
-        <v>409.8412196257212</v>
+        <v>418.5612455752046</v>
       </c>
       <c r="N49">
-        <v>461.605719149789</v>
+        <v>452.8856932003055</v>
       </c>
       <c r="O49">
-        <v>110.7853725959494</v>
+        <v>108.6925663680733</v>
       </c>
       <c r="P49">
-        <v>350.8203465538396</v>
+        <v>344.1931268322322</v>
       </c>
       <c r="Q49">
-        <v>981.7203465538396</v>
+        <v>975.0931268322322</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1497458001709381</v>
+        <v>0.1514581624890763</v>
       </c>
       <c r="T49">
-        <v>1.43085306507009</v>
+        <v>1.45442437692097</v>
       </c>
       <c r="U49">
         <v>0.08586759442929168</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.126303790456559</v>
+        <v>2.082005794822048</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1100827429421253</v>
+        <v>0.1101283070635103</v>
       </c>
       <c r="C50">
-        <v>5112.383839784176</v>
+        <v>5006.179172332777</v>
       </c>
       <c r="D50">
-        <v>9121.879839784177</v>
+        <v>9117.227172332778</v>
       </c>
       <c r="E50">
-        <v>386.5960000000005</v>
+        <v>488.148000000001</v>
       </c>
       <c r="F50">
-        <v>4874.496</v>
+        <v>4976.048000000001</v>
       </c>
       <c r="G50">
         <v>865</v>
@@ -5393,28 +5393,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M50">
-        <v>418.5612455752046</v>
+        <v>427.2812715246881</v>
       </c>
       <c r="N50">
-        <v>452.8856932003056</v>
+        <v>444.1656672508221</v>
       </c>
       <c r="O50">
-        <v>108.6925663680733</v>
+        <v>106.5997601401973</v>
       </c>
       <c r="P50">
-        <v>344.1931268322322</v>
+        <v>337.5659071106248</v>
       </c>
       <c r="Q50">
-        <v>975.0931268322322</v>
+        <v>968.4659071106248</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1514581624890763</v>
+        <v>0.1532376762706708</v>
       </c>
       <c r="T50">
-        <v>1.45442437692097</v>
+        <v>1.478920053942474</v>
       </c>
       <c r="U50">
         <v>0.08586759442929168</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.082005794822048</v>
+        <v>2.039515880642006</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1101283070635103</v>
+        <v>0.1131378711848954</v>
       </c>
       <c r="C51">
-        <v>5006.179172332777</v>
+        <v>4607.480537146441</v>
       </c>
       <c r="D51">
-        <v>9117.227172332778</v>
+        <v>8820.080537146441</v>
       </c>
       <c r="E51">
-        <v>488.148000000001</v>
+        <v>589.7000000000007</v>
       </c>
       <c r="F51">
-        <v>4976.048000000001</v>
+        <v>5077.6</v>
       </c>
       <c r="G51">
         <v>865</v>
@@ -5475,45 +5475,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M51">
-        <v>427.2812715246881</v>
+        <v>475.6065774741714</v>
       </c>
       <c r="N51">
-        <v>444.1656672508221</v>
+        <v>395.8403613013387</v>
       </c>
       <c r="O51">
-        <v>106.5997601401973</v>
+        <v>95.00168671232129</v>
       </c>
       <c r="P51">
-        <v>337.5659071106248</v>
+        <v>300.8386745890174</v>
       </c>
       <c r="Q51">
-        <v>968.4659071106248</v>
+        <v>931.7386745890174</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1532376762706708</v>
+        <v>0.1550883706035292</v>
       </c>
       <c r="T51">
-        <v>1.478920053942474</v>
+        <v>1.504395558044837</v>
       </c>
       <c r="U51">
-        <v>0.08586759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.06525937176626168</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.039515880642006</v>
+        <v>1.832285296396759</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1131378711848954</v>
+        <v>0.1132427153062805</v>
       </c>
       <c r="C52">
-        <v>4607.480537146441</v>
+        <v>4495.92558347641</v>
       </c>
       <c r="D52">
-        <v>8820.080537146441</v>
+        <v>8810.07758347641</v>
       </c>
       <c r="E52">
-        <v>589.7000000000007</v>
+        <v>691.2520000000004</v>
       </c>
       <c r="F52">
-        <v>5077.6</v>
+        <v>5179.152</v>
       </c>
       <c r="G52">
         <v>865</v>
@@ -5557,28 +5557,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M52">
-        <v>475.6065774741714</v>
+        <v>485.1187090236548</v>
       </c>
       <c r="N52">
-        <v>395.8403613013387</v>
+        <v>386.3282297518553</v>
       </c>
       <c r="O52">
-        <v>95.00168671232129</v>
+        <v>92.71877514044527</v>
       </c>
       <c r="P52">
-        <v>300.8386745890174</v>
+        <v>293.60945461141</v>
       </c>
       <c r="Q52">
-        <v>931.7386745890174</v>
+        <v>924.50945461141</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1550883706035292</v>
+        <v>0.1570146034805859</v>
       </c>
       <c r="T52">
-        <v>1.504395558044837</v>
+        <v>1.530910878641175</v>
       </c>
       <c r="U52">
         <v>0.09366759442929168</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.832285296396759</v>
+        <v>1.796358133722312</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1132427153062805</v>
+        <v>0.1133475594276656</v>
       </c>
       <c r="C53">
-        <v>4495.92558347641</v>
+        <v>4384.39329303085</v>
       </c>
       <c r="D53">
-        <v>8810.07758347641</v>
+        <v>8800.097293030851</v>
       </c>
       <c r="E53">
-        <v>691.2520000000004</v>
+        <v>792.804000000001</v>
       </c>
       <c r="F53">
-        <v>5179.152</v>
+        <v>5280.704000000001</v>
       </c>
       <c r="G53">
         <v>865</v>
@@ -5639,28 +5639,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M53">
-        <v>485.1187090236548</v>
+        <v>494.6308405731384</v>
       </c>
       <c r="N53">
-        <v>386.3282297518553</v>
+        <v>376.8160982023718</v>
       </c>
       <c r="O53">
-        <v>92.71877514044527</v>
+        <v>90.43586356856923</v>
       </c>
       <c r="P53">
-        <v>293.60945461141</v>
+        <v>286.3802346338026</v>
       </c>
       <c r="Q53">
-        <v>924.50945461141</v>
+        <v>917.2802346338026</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1570146034805859</v>
+        <v>0.1590210960608532</v>
       </c>
       <c r="T53">
-        <v>1.530910878641175</v>
+        <v>1.55853100426236</v>
       </c>
       <c r="U53">
         <v>0.09366759442929168</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.796358133722312</v>
+        <v>1.761812784996883</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1133475594276656</v>
+        <v>0.1150233235490507</v>
       </c>
       <c r="C54">
-        <v>4384.39329303085</v>
+        <v>4126.336892175083</v>
       </c>
       <c r="D54">
-        <v>8800.097293030851</v>
+        <v>8643.592892175084</v>
       </c>
       <c r="E54">
-        <v>792.804000000001</v>
+        <v>894.3560000000007</v>
       </c>
       <c r="F54">
-        <v>5280.704000000001</v>
+        <v>5382.256</v>
       </c>
       <c r="G54">
         <v>865</v>
@@ -5721,45 +5721,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M54">
-        <v>494.6308405731384</v>
+        <v>525.1337705226217</v>
       </c>
       <c r="N54">
-        <v>376.8160982023718</v>
+        <v>346.3131682528884</v>
       </c>
       <c r="O54">
-        <v>90.43586356856923</v>
+        <v>83.11516038069323</v>
       </c>
       <c r="P54">
-        <v>286.3802346338026</v>
+        <v>263.1980078721952</v>
       </c>
       <c r="Q54">
-        <v>917.2802346338026</v>
+        <v>894.0980078721952</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1590210960608532</v>
+        <v>0.1611129713041106</v>
       </c>
       <c r="T54">
-        <v>1.55853100426236</v>
+        <v>1.587326454378063</v>
       </c>
       <c r="U54">
-        <v>0.09366759442929168</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.07118737176626168</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.761812784996883</v>
+        <v>1.659476094840048</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1150233235490507</v>
+        <v>0.1151578076704357</v>
       </c>
       <c r="C55">
-        <v>4126.336892175083</v>
+        <v>4012.465987187838</v>
       </c>
       <c r="D55">
-        <v>8643.592892175084</v>
+        <v>8631.273987187838</v>
       </c>
       <c r="E55">
-        <v>894.3560000000007</v>
+        <v>995.9080000000013</v>
       </c>
       <c r="F55">
-        <v>5382.256</v>
+        <v>5483.808000000001</v>
       </c>
       <c r="G55">
         <v>865</v>
@@ -5803,28 +5803,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M55">
-        <v>525.1337705226217</v>
+        <v>535.0419548721052</v>
       </c>
       <c r="N55">
-        <v>346.3131682528884</v>
+        <v>336.404983903405</v>
       </c>
       <c r="O55">
-        <v>83.11516038069323</v>
+        <v>80.73719613681719</v>
       </c>
       <c r="P55">
-        <v>263.1980078721952</v>
+        <v>255.6677877665878</v>
       </c>
       <c r="Q55">
-        <v>894.0980078721952</v>
+        <v>886.5677877665878</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1611129713041106</v>
+        <v>0.163295797644901</v>
       </c>
       <c r="T55">
-        <v>1.587326454378063</v>
+        <v>1.617373880585754</v>
       </c>
       <c r="U55">
         <v>0.09756759442929168</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.659476094840048</v>
+        <v>1.628745056046714</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1151578076704357</v>
+        <v>0.1152922917918208</v>
       </c>
       <c r="C56">
-        <v>4012.465987187838</v>
+        <v>3898.630146194691</v>
       </c>
       <c r="D56">
-        <v>8631.273987187838</v>
+        <v>8618.990146194692</v>
       </c>
       <c r="E56">
-        <v>995.9080000000013</v>
+        <v>1097.460000000001</v>
       </c>
       <c r="F56">
-        <v>5483.808000000001</v>
+        <v>5585.360000000001</v>
       </c>
       <c r="G56">
         <v>865</v>
@@ -5885,28 +5885,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M56">
-        <v>535.0419548721052</v>
+        <v>544.9501392215886</v>
       </c>
       <c r="N56">
-        <v>336.404983903405</v>
+        <v>326.4967995539215</v>
       </c>
       <c r="O56">
-        <v>80.73719613681719</v>
+        <v>78.35923189294115</v>
       </c>
       <c r="P56">
-        <v>255.6677877665878</v>
+        <v>248.1375676609804</v>
       </c>
       <c r="Q56">
-        <v>886.5677877665878</v>
+        <v>879.0375676609804</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.163295797644901</v>
+        <v>0.1655756384897265</v>
       </c>
       <c r="T56">
-        <v>1.617373880585754</v>
+        <v>1.648756747958231</v>
       </c>
       <c r="U56">
         <v>0.09756759442929168</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.628745056046714</v>
+        <v>1.599131509573137</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1152922917918208</v>
+        <v>0.1154267759132059</v>
       </c>
       <c r="C57">
-        <v>3898.630146194691</v>
+        <v>3784.829219701464</v>
       </c>
       <c r="D57">
-        <v>8618.990146194692</v>
+        <v>8606.741219701466</v>
       </c>
       <c r="E57">
-        <v>1097.460000000001</v>
+        <v>1199.012000000002</v>
       </c>
       <c r="F57">
-        <v>5585.360000000001</v>
+        <v>5686.912000000001</v>
       </c>
       <c r="G57">
         <v>865</v>
@@ -5967,28 +5967,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M57">
-        <v>544.9501392215886</v>
+        <v>554.8583235710721</v>
       </c>
       <c r="N57">
-        <v>326.4967995539215</v>
+        <v>316.588615204438</v>
       </c>
       <c r="O57">
-        <v>78.35923189294115</v>
+        <v>75.98126764906513</v>
       </c>
       <c r="P57">
-        <v>248.1375676609804</v>
+        <v>240.6073475553729</v>
       </c>
       <c r="Q57">
-        <v>879.0375676609804</v>
+        <v>871.5073475553729</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1655756384897265</v>
+        <v>0.1679591084638622</v>
       </c>
       <c r="T57">
-        <v>1.648756747958231</v>
+        <v>1.681566109302184</v>
       </c>
       <c r="U57">
         <v>0.09756759442929168</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.599131509573137</v>
+        <v>1.570575589759331</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1154267759132059</v>
+        <v>0.115561260034591</v>
       </c>
       <c r="C58">
-        <v>3784.829219701464</v>
+        <v>3671.063059062587</v>
       </c>
       <c r="D58">
-        <v>8606.741219701466</v>
+        <v>8594.527059062588</v>
       </c>
       <c r="E58">
-        <v>1199.012000000002</v>
+        <v>1300.564000000001</v>
       </c>
       <c r="F58">
-        <v>5686.912000000001</v>
+        <v>5788.464000000001</v>
       </c>
       <c r="G58">
         <v>865</v>
@@ -6049,28 +6049,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M58">
-        <v>554.8583235710721</v>
+        <v>564.7665079205556</v>
       </c>
       <c r="N58">
-        <v>316.588615204438</v>
+        <v>306.6804308549546</v>
       </c>
       <c r="O58">
-        <v>75.98126764906513</v>
+        <v>73.6033034051891</v>
       </c>
       <c r="P58">
-        <v>240.6073475553729</v>
+        <v>233.0771274497655</v>
       </c>
       <c r="Q58">
-        <v>871.5073475553729</v>
+        <v>863.9771274497655</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1679591084638622</v>
+        <v>0.1704534375065624</v>
       </c>
       <c r="T58">
-        <v>1.681566109302184</v>
+        <v>1.715901487452833</v>
       </c>
       <c r="U58">
         <v>0.09756759442929168</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.570575589759331</v>
+        <v>1.543021632044255</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.115561260034591</v>
+        <v>0.1156957441559761</v>
       </c>
       <c r="C59">
-        <v>3671.063059062587</v>
+        <v>3557.331516475091</v>
       </c>
       <c r="D59">
-        <v>8594.527059062588</v>
+        <v>8582.347516475093</v>
       </c>
       <c r="E59">
-        <v>1300.564000000001</v>
+        <v>1402.116000000002</v>
       </c>
       <c r="F59">
-        <v>5788.464000000001</v>
+        <v>5890.016000000001</v>
       </c>
       <c r="G59">
         <v>865</v>
@@ -6131,28 +6131,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M59">
-        <v>564.7665079205556</v>
+        <v>574.674692270039</v>
       </c>
       <c r="N59">
-        <v>306.6804308549546</v>
+        <v>296.7722465054711</v>
       </c>
       <c r="O59">
-        <v>73.6033034051891</v>
+        <v>71.22533916131306</v>
       </c>
       <c r="P59">
-        <v>233.0771274497655</v>
+        <v>225.5469073441581</v>
       </c>
       <c r="Q59">
-        <v>863.9771274497655</v>
+        <v>856.446907344158</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1704534375065624</v>
+        <v>0.1730665441227245</v>
       </c>
       <c r="T59">
-        <v>1.715901487452833</v>
+        <v>1.751871883610655</v>
       </c>
       <c r="U59">
         <v>0.09756759442929168</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.543021632044255</v>
+        <v>1.516417810802112</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1156957441559761</v>
+        <v>0.1221975082773611</v>
       </c>
       <c r="C60">
-        <v>3557.331516475093</v>
+        <v>2905.4843181223</v>
       </c>
       <c r="D60">
-        <v>8582.347516475093</v>
+        <v>8032.052318122299</v>
       </c>
       <c r="E60">
-        <v>1402.116</v>
+        <v>1503.668000000001</v>
       </c>
       <c r="F60">
-        <v>5890.016</v>
+        <v>5991.568</v>
       </c>
       <c r="G60">
         <v>865</v>
@@ -6213,45 +6213,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M60">
-        <v>574.6746922700388</v>
+        <v>669.6631422195223</v>
       </c>
       <c r="N60">
-        <v>296.7722465054713</v>
+        <v>201.7837965559878</v>
       </c>
       <c r="O60">
-        <v>71.22533916131312</v>
+        <v>48.42811117343707</v>
       </c>
       <c r="P60">
-        <v>225.5469073441582</v>
+        <v>153.3556853825507</v>
       </c>
       <c r="Q60">
-        <v>856.4469073441583</v>
+        <v>784.2556853825507</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1730665441227245</v>
+        <v>0.1758071193543091</v>
       </c>
       <c r="T60">
-        <v>1.751871883610655</v>
+        <v>1.78959693323959</v>
       </c>
       <c r="U60">
-        <v>0.09756759442929168</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V60">
         <v>0.24</v>
       </c>
       <c r="W60">
-        <v>0.07415137176626167</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.516417810802113</v>
+        <v>1.301321341782673</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1221975082773611</v>
+        <v>0.1224399123987462</v>
       </c>
       <c r="C61">
-        <v>2905.4843181223</v>
+        <v>2784.777061226613</v>
       </c>
       <c r="D61">
-        <v>8032.052318122299</v>
+        <v>8012.897061226614</v>
       </c>
       <c r="E61">
-        <v>1503.668000000001</v>
+        <v>1605.22</v>
       </c>
       <c r="F61">
-        <v>5991.568</v>
+        <v>6093.12</v>
       </c>
       <c r="G61">
         <v>865</v>
@@ -6295,28 +6295,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M61">
-        <v>669.6631422195223</v>
+        <v>681.0133649690057</v>
       </c>
       <c r="N61">
-        <v>201.7837965559878</v>
+        <v>190.4335738065045</v>
       </c>
       <c r="O61">
-        <v>48.42811117343707</v>
+        <v>45.70405771356107</v>
       </c>
       <c r="P61">
-        <v>153.3556853825507</v>
+        <v>144.7295160929434</v>
       </c>
       <c r="Q61">
-        <v>784.2556853825507</v>
+        <v>775.6295160929434</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1758071193543091</v>
+        <v>0.178684723347473</v>
       </c>
       <c r="T61">
-        <v>1.78959693323959</v>
+        <v>1.829208235349972</v>
       </c>
       <c r="U61">
         <v>0.1117675944292917</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.301321341782673</v>
+        <v>1.279632652752962</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1224399123987462</v>
+        <v>0.1226823165201313</v>
       </c>
       <c r="C62">
-        <v>2784.777061226613</v>
+        <v>2664.160951867076</v>
       </c>
       <c r="D62">
-        <v>8012.897061226614</v>
+        <v>7993.832951867075</v>
       </c>
       <c r="E62">
-        <v>1605.22</v>
+        <v>1706.772000000001</v>
       </c>
       <c r="F62">
-        <v>6093.12</v>
+        <v>6194.672</v>
       </c>
       <c r="G62">
         <v>865</v>
@@ -6377,28 +6377,28 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M62">
-        <v>681.0133649690057</v>
+        <v>692.3635877184893</v>
       </c>
       <c r="N62">
-        <v>190.4335738065045</v>
+        <v>179.0833510570209</v>
       </c>
       <c r="O62">
-        <v>45.70405771356107</v>
+        <v>42.98000425368501</v>
       </c>
       <c r="P62">
-        <v>144.7295160929434</v>
+        <v>136.1033468033359</v>
       </c>
       <c r="Q62">
-        <v>775.6295160929434</v>
+        <v>767.0033468033358</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.178684723347473</v>
+        <v>0.1817098967761838</v>
       </c>
       <c r="T62">
-        <v>1.829208235349972</v>
+        <v>1.870850886286529</v>
       </c>
       <c r="U62">
         <v>0.1117675944292917</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.279632652752962</v>
+        <v>1.258655068281602</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1226823165201313</v>
+        <v>0.1368216489056354</v>
       </c>
       <c r="C63">
-        <v>2664.160951867076</v>
+        <v>1588.44413146804</v>
       </c>
       <c r="D63">
-        <v>7993.832951867075</v>
+        <v>7019.66813146804</v>
       </c>
       <c r="E63">
-        <v>1706.772000000001</v>
+        <v>1808.324000000001</v>
       </c>
       <c r="F63">
-        <v>6194.672</v>
+        <v>6296.224</v>
       </c>
       <c r="G63">
         <v>865</v>
@@ -6459,45 +6459,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M63">
-        <v>692.3635877184893</v>
+        <v>883.7858168679727</v>
       </c>
       <c r="N63">
-        <v>179.0833510570209</v>
+        <v>-12.33887809246255</v>
       </c>
       <c r="O63">
-        <v>42.98000425368501</v>
+        <v>-2.961330742191012</v>
       </c>
       <c r="P63">
-        <v>136.1033468033359</v>
+        <v>-9.377547350271538</v>
       </c>
       <c r="Q63">
-        <v>767.0033468033358</v>
+        <v>621.5224526497284</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1817098967761838</v>
+        <v>0.1852337660054528</v>
       </c>
       <c r="T63">
-        <v>1.870850886286529</v>
+        <v>1.919358272629354</v>
       </c>
       <c r="U63">
-        <v>0.1117675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V63">
-        <v>0.24</v>
+        <v>0.2366492665013729</v>
       </c>
       <c r="W63">
-        <v>0.08494337176626168</v>
+        <v>0.1071497061670376</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.258655068281602</v>
+        <v>0.9860386104223872</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1368216489056354</v>
+        <v>0.1377673248499283</v>
       </c>
       <c r="C64">
-        <v>1588.44413146804</v>
+        <v>1430.140027208924</v>
       </c>
       <c r="D64">
-        <v>7019.66813146804</v>
+        <v>6962.916027208925</v>
       </c>
       <c r="E64">
-        <v>1808.324000000001</v>
+        <v>1909.876000000001</v>
       </c>
       <c r="F64">
-        <v>6296.224</v>
+        <v>6397.776000000001</v>
       </c>
       <c r="G64">
         <v>865</v>
@@ -6541,37 +6541,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M64">
-        <v>883.7858168679727</v>
+        <v>898.0404268174563</v>
       </c>
       <c r="N64">
-        <v>-12.33887809246255</v>
+        <v>-26.5934880419461</v>
       </c>
       <c r="O64">
-        <v>-2.961330742191012</v>
+        <v>-6.382437130067064</v>
       </c>
       <c r="P64">
-        <v>-9.377547350271538</v>
+        <v>-20.21105091187904</v>
       </c>
       <c r="Q64">
-        <v>621.5224526497284</v>
+        <v>610.6889490881209</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1852337660054528</v>
+        <v>0.1890022461677624</v>
       </c>
       <c r="T64">
-        <v>1.919358272629354</v>
+        <v>1.971232820538255</v>
       </c>
       <c r="U64">
         <v>0.1403675944292917</v>
       </c>
       <c r="V64">
-        <v>0.2366492665013729</v>
+        <v>0.232892928937859</v>
       </c>
       <c r="W64">
-        <v>0.1071497061670376</v>
+        <v>0.1076769742346924</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9860386104223872</v>
+        <v>0.970387203907746</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1377673248499283</v>
+        <v>0.1387130007942212</v>
       </c>
       <c r="C65">
-        <v>1430.140027208924</v>
+        <v>1272.746214094354</v>
       </c>
       <c r="D65">
-        <v>6962.916027208925</v>
+        <v>6907.074214094355</v>
       </c>
       <c r="E65">
-        <v>1909.876000000001</v>
+        <v>2011.428000000001</v>
       </c>
       <c r="F65">
-        <v>6397.776000000001</v>
+        <v>6499.328</v>
       </c>
       <c r="G65">
         <v>865</v>
@@ -6623,37 +6623,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M65">
-        <v>898.0404268174563</v>
+        <v>912.2950367669396</v>
       </c>
       <c r="N65">
-        <v>-26.5934880419461</v>
+        <v>-40.84809799142943</v>
       </c>
       <c r="O65">
-        <v>-6.382437130067064</v>
+        <v>-9.803543517943062</v>
       </c>
       <c r="P65">
-        <v>-20.21105091187904</v>
+        <v>-31.04455447348636</v>
       </c>
       <c r="Q65">
-        <v>610.6889490881209</v>
+        <v>599.8554455265136</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1890022461677624</v>
+        <v>0.1929800863390891</v>
       </c>
       <c r="T65">
-        <v>1.971232820538255</v>
+        <v>2.02598928777543</v>
       </c>
       <c r="U65">
         <v>0.1403675944292917</v>
       </c>
       <c r="V65">
-        <v>0.232892928937859</v>
+        <v>0.229253976923205</v>
       </c>
       <c r="W65">
-        <v>0.1076769742346924</v>
+        <v>0.1081877651752331</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.970387203907746</v>
+        <v>0.9552249038466876</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1387130007942212</v>
+        <v>0.1396586767385142</v>
       </c>
       <c r="C66">
-        <v>1272.746214094354</v>
+        <v>1116.240965071285</v>
       </c>
       <c r="D66">
-        <v>6907.074214094355</v>
+        <v>6852.120965071286</v>
       </c>
       <c r="E66">
-        <v>2011.428000000001</v>
+        <v>2112.980000000001</v>
       </c>
       <c r="F66">
-        <v>6499.328</v>
+        <v>6600.880000000001</v>
       </c>
       <c r="G66">
         <v>865</v>
@@ -6705,37 +6705,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M66">
-        <v>912.2950367669396</v>
+        <v>926.5496467164231</v>
       </c>
       <c r="N66">
-        <v>-40.84809799142943</v>
+        <v>-55.10270794091298</v>
       </c>
       <c r="O66">
-        <v>-9.803543517943062</v>
+        <v>-13.22464990581912</v>
       </c>
       <c r="P66">
-        <v>-31.04455447348636</v>
+        <v>-41.87805803509386</v>
       </c>
       <c r="Q66">
-        <v>599.8554455265136</v>
+        <v>589.0219419649061</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1929800863390891</v>
+        <v>0.1971852316630631</v>
       </c>
       <c r="T66">
-        <v>2.02598928777543</v>
+        <v>2.083874695997585</v>
       </c>
       <c r="U66">
         <v>0.1403675944292917</v>
       </c>
       <c r="V66">
-        <v>0.229253976923205</v>
+        <v>0.225726992662848</v>
       </c>
       <c r="W66">
-        <v>0.1081877651752331</v>
+        <v>0.1086828394714493</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9552249038466876</v>
+        <v>0.9405291360951999</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1396586767385142</v>
+        <v>0.1406043526828071</v>
       </c>
       <c r="C67">
-        <v>1116.240965071285</v>
+        <v>960.6032390777355</v>
       </c>
       <c r="D67">
-        <v>6852.120965071286</v>
+        <v>6798.035239077736</v>
       </c>
       <c r="E67">
-        <v>2112.980000000001</v>
+        <v>2214.532000000001</v>
       </c>
       <c r="F67">
-        <v>6600.880000000001</v>
+        <v>6702.432000000001</v>
       </c>
       <c r="G67">
         <v>865</v>
@@ -6787,37 +6787,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M67">
-        <v>926.5496467164231</v>
+        <v>940.8042566659066</v>
       </c>
       <c r="N67">
-        <v>-55.10270794091298</v>
+        <v>-69.35731789039642</v>
       </c>
       <c r="O67">
-        <v>-13.22464990581912</v>
+        <v>-16.64575629369514</v>
       </c>
       <c r="P67">
-        <v>-41.87805803509386</v>
+        <v>-52.71156159670127</v>
       </c>
       <c r="Q67">
-        <v>589.0219419649061</v>
+        <v>578.1884384032987</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1971852316630631</v>
+        <v>0.2016377384766826</v>
       </c>
       <c r="T67">
-        <v>2.083874695997585</v>
+        <v>2.145165128232807</v>
       </c>
       <c r="U67">
         <v>0.1403675944292917</v>
       </c>
       <c r="V67">
-        <v>0.225726992662848</v>
+        <v>0.2223068867134109</v>
       </c>
       <c r="W67">
-        <v>0.1086828394714493</v>
+        <v>0.1091629115162651</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9405291360951999</v>
+        <v>0.9262786946392121</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1406043526828071</v>
+        <v>0.1415500286271</v>
       </c>
       <c r="C68">
-        <v>960.6032390777355</v>
+        <v>805.8126541811989</v>
       </c>
       <c r="D68">
-        <v>6798.035239077736</v>
+        <v>6744.7966541812</v>
       </c>
       <c r="E68">
-        <v>2214.532000000001</v>
+        <v>2316.084000000002</v>
       </c>
       <c r="F68">
-        <v>6702.432000000001</v>
+        <v>6803.984000000001</v>
       </c>
       <c r="G68">
         <v>865</v>
@@ -6869,37 +6869,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M68">
-        <v>940.8042566659066</v>
+        <v>955.05886661539</v>
       </c>
       <c r="N68">
-        <v>-69.35731789039642</v>
+        <v>-83.61192783987985</v>
       </c>
       <c r="O68">
-        <v>-16.64575629369514</v>
+        <v>-20.06686268157116</v>
       </c>
       <c r="P68">
-        <v>-52.71156159670127</v>
+        <v>-63.54506515830869</v>
       </c>
       <c r="Q68">
-        <v>578.1884384032987</v>
+        <v>567.3549348416913</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2016377384766826</v>
+        <v>0.2063600941880973</v>
       </c>
       <c r="T68">
-        <v>2.145165128232807</v>
+        <v>2.210170132118651</v>
       </c>
       <c r="U68">
         <v>0.1403675944292917</v>
       </c>
       <c r="V68">
-        <v>0.2223068867134109</v>
+        <v>0.2189888734788824</v>
       </c>
       <c r="W68">
-        <v>0.1091629115162651</v>
+        <v>0.1096286530522805</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9262786946392121</v>
+        <v>0.9124536394953432</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1415500286271</v>
+        <v>0.1424957045713929</v>
       </c>
       <c r="C69">
-        <v>805.8126541811989</v>
+        <v>651.8494619694739</v>
       </c>
       <c r="D69">
-        <v>6744.7966541812</v>
+        <v>6692.385461969475</v>
       </c>
       <c r="E69">
-        <v>2316.084000000002</v>
+        <v>2417.636000000001</v>
       </c>
       <c r="F69">
-        <v>6803.984000000001</v>
+        <v>6905.536000000001</v>
       </c>
       <c r="G69">
         <v>865</v>
@@ -6951,37 +6951,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M69">
-        <v>955.05886661539</v>
+        <v>969.3134765648734</v>
       </c>
       <c r="N69">
-        <v>-83.61192783987985</v>
+        <v>-97.86653778936329</v>
       </c>
       <c r="O69">
-        <v>-20.06686268157116</v>
+        <v>-23.48796906944719</v>
       </c>
       <c r="P69">
-        <v>-63.54506515830869</v>
+        <v>-74.3785687199161</v>
       </c>
       <c r="Q69">
-        <v>567.3549348416913</v>
+        <v>556.5214312800839</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2063600941880973</v>
+        <v>0.2113775971314752</v>
       </c>
       <c r="T69">
-        <v>2.210170132118651</v>
+        <v>2.279237948747358</v>
       </c>
       <c r="U69">
         <v>0.1403675944292917</v>
       </c>
       <c r="V69">
-        <v>0.2189888734788824</v>
+        <v>0.2157684488688988</v>
       </c>
       <c r="W69">
-        <v>0.1096286530522805</v>
+        <v>0.1100806963078247</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9124536394953432</v>
+        <v>0.8990352036204117</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1424957045713929</v>
+        <v>0.1434413805156858</v>
       </c>
       <c r="C70">
-        <v>651.8494619694739</v>
+        <v>498.6945231262271</v>
       </c>
       <c r="D70">
-        <v>6692.385461969475</v>
+        <v>6640.782523126228</v>
       </c>
       <c r="E70">
-        <v>2417.636000000001</v>
+        <v>2519.188000000001</v>
       </c>
       <c r="F70">
-        <v>6905.536000000001</v>
+        <v>7007.088000000001</v>
       </c>
       <c r="G70">
         <v>865</v>
@@ -7033,37 +7033,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M70">
-        <v>969.3134765648734</v>
+        <v>983.5680865143568</v>
       </c>
       <c r="N70">
-        <v>-97.86653778936329</v>
+        <v>-112.1211477388466</v>
       </c>
       <c r="O70">
-        <v>-23.48796906944719</v>
+        <v>-26.90907545732319</v>
       </c>
       <c r="P70">
-        <v>-74.3785687199161</v>
+        <v>-85.21207228152343</v>
       </c>
       <c r="Q70">
-        <v>556.5214312800839</v>
+        <v>545.6879277184765</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2113775971314752</v>
+        <v>0.2167188099421681</v>
       </c>
       <c r="T70">
-        <v>2.279237948747358</v>
+        <v>2.352761753545661</v>
       </c>
       <c r="U70">
         <v>0.1403675944292917</v>
       </c>
       <c r="V70">
-        <v>0.2157684488688988</v>
+        <v>0.2126413698997844</v>
       </c>
       <c r="W70">
-        <v>0.1100806963078247</v>
+        <v>0.1105196368603098</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8990352036204117</v>
+        <v>0.8860057079157682</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1434413805156858</v>
+        <v>0.1443870564599787</v>
       </c>
       <c r="C71">
-        <v>498.6945231262271</v>
+        <v>346.329284127939</v>
       </c>
       <c r="D71">
-        <v>6640.782523126228</v>
+        <v>6589.96928412794</v>
       </c>
       <c r="E71">
-        <v>2519.188000000001</v>
+        <v>2620.740000000002</v>
       </c>
       <c r="F71">
-        <v>7007.088000000001</v>
+        <v>7108.640000000001</v>
       </c>
       <c r="G71">
         <v>865</v>
@@ -7115,37 +7115,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M71">
-        <v>983.5680865143568</v>
+        <v>997.8226964638403</v>
       </c>
       <c r="N71">
-        <v>-112.1211477388466</v>
+        <v>-126.3757576883302</v>
       </c>
       <c r="O71">
-        <v>-26.90907545732319</v>
+        <v>-30.33018184519924</v>
       </c>
       <c r="P71">
-        <v>-85.21207228152343</v>
+        <v>-96.04557584313093</v>
       </c>
       <c r="Q71">
-        <v>545.6879277184765</v>
+        <v>534.8544241568691</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2167188099421681</v>
+        <v>0.2224161036069069</v>
       </c>
       <c r="T71">
-        <v>2.352761753545661</v>
+        <v>2.431187145330516</v>
       </c>
       <c r="U71">
         <v>0.1403675944292917</v>
       </c>
       <c r="V71">
-        <v>0.2126413698997844</v>
+        <v>0.2096036360440731</v>
       </c>
       <c r="W71">
-        <v>0.1105196368603098</v>
+        <v>0.1109460362541524</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8860057079157682</v>
+        <v>0.8733484835169714</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1443870564599787</v>
+        <v>0.1453327324042717</v>
       </c>
       <c r="C72">
-        <v>346.329284127939</v>
+        <v>194.7357550025363</v>
       </c>
       <c r="D72">
-        <v>6589.96928412794</v>
+        <v>6539.927755002537</v>
       </c>
       <c r="E72">
-        <v>2620.740000000002</v>
+        <v>2722.292000000001</v>
       </c>
       <c r="F72">
-        <v>7108.640000000001</v>
+        <v>7210.192000000001</v>
       </c>
       <c r="G72">
         <v>865</v>
@@ -7197,37 +7197,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M72">
-        <v>997.8226964638403</v>
+        <v>1012.077306413324</v>
       </c>
       <c r="N72">
-        <v>-126.3757576883302</v>
+        <v>-140.6303676378135</v>
       </c>
       <c r="O72">
-        <v>-30.33018184519924</v>
+        <v>-33.75128823307524</v>
       </c>
       <c r="P72">
-        <v>-96.04557584313093</v>
+        <v>-106.8790794047383</v>
       </c>
       <c r="Q72">
-        <v>534.8544241568691</v>
+        <v>524.0209205952617</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2224161036069069</v>
+        <v>0.2285063140761107</v>
       </c>
       <c r="T72">
-        <v>2.431187145330516</v>
+        <v>2.515021184824672</v>
       </c>
       <c r="U72">
         <v>0.1403675944292917</v>
       </c>
       <c r="V72">
-        <v>0.2096036360440731</v>
+        <v>0.2066514721561284</v>
       </c>
       <c r="W72">
-        <v>0.1109460362541524</v>
+        <v>0.1113604243974642</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8733484835169714</v>
+        <v>0.8610478006505352</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1453327324042717</v>
+        <v>0.1462784083485646</v>
       </c>
       <c r="C73">
-        <v>194.7357550025372</v>
+        <v>43.89648809376104</v>
       </c>
       <c r="D73">
-        <v>6539.927755002537</v>
+        <v>6490.640488093762</v>
       </c>
       <c r="E73">
-        <v>2722.292</v>
+        <v>2823.844000000001</v>
       </c>
       <c r="F73">
-        <v>7210.192</v>
+        <v>7311.744000000001</v>
       </c>
       <c r="G73">
         <v>865</v>
@@ -7279,37 +7279,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M73">
-        <v>1012.077306413324</v>
+        <v>1026.331916362807</v>
       </c>
       <c r="N73">
-        <v>-140.6303676378134</v>
+        <v>-154.8849775872969</v>
       </c>
       <c r="O73">
-        <v>-33.75128823307521</v>
+        <v>-37.17239462095126</v>
       </c>
       <c r="P73">
-        <v>-106.8790794047382</v>
+        <v>-117.7125829663457</v>
       </c>
       <c r="Q73">
-        <v>524.0209205952618</v>
+        <v>513.1874170336544</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2285063140761106</v>
+        <v>0.2350315395788288</v>
       </c>
       <c r="T73">
-        <v>2.515021184824671</v>
+        <v>2.60484336999698</v>
       </c>
       <c r="U73">
         <v>0.1403675944292917</v>
       </c>
       <c r="V73">
-        <v>0.2066514721561285</v>
+        <v>0.2037813128206267</v>
       </c>
       <c r="W73">
-        <v>0.1113604243974642</v>
+        <v>0.1117633017590173</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8610478006505353</v>
+        <v>0.8490888034192778</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1462784083485646</v>
+        <v>0.1472240842928575</v>
       </c>
       <c r="C74">
-        <v>43.89648809376104</v>
+        <v>-106.2054422214287</v>
       </c>
       <c r="D74">
-        <v>6490.640488093762</v>
+        <v>6442.090557778572</v>
       </c>
       <c r="E74">
-        <v>2823.844000000001</v>
+        <v>2925.396000000001</v>
       </c>
       <c r="F74">
-        <v>7311.744000000001</v>
+        <v>7413.296</v>
       </c>
       <c r="G74">
         <v>865</v>
@@ -7361,37 +7361,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M74">
-        <v>1026.331916362807</v>
+        <v>1040.586526312291</v>
       </c>
       <c r="N74">
-        <v>-154.8849775872969</v>
+        <v>-169.1395875367804</v>
       </c>
       <c r="O74">
-        <v>-37.17239462095126</v>
+        <v>-40.59350100882729</v>
       </c>
       <c r="P74">
-        <v>-117.7125829663457</v>
+        <v>-128.5460865279531</v>
       </c>
       <c r="Q74">
-        <v>513.1874170336544</v>
+        <v>502.3539134720469</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2350315395788288</v>
+        <v>0.2420401151187855</v>
       </c>
       <c r="T74">
-        <v>2.60484336999698</v>
+        <v>2.701319050367239</v>
       </c>
       <c r="U74">
         <v>0.1403675944292917</v>
       </c>
       <c r="V74">
-        <v>0.2037813128206267</v>
+        <v>0.2009897879874674</v>
       </c>
       <c r="W74">
-        <v>0.1117633017590173</v>
+        <v>0.1121551413846376</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8490888034192778</v>
+        <v>0.8374574499477808</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1472240842928575</v>
+        <v>0.1481697602371504</v>
       </c>
       <c r="C75">
-        <v>-106.2054422214287</v>
+        <v>-255.5864589119064</v>
       </c>
       <c r="D75">
-        <v>6442.090557778572</v>
+        <v>6394.261541088094</v>
       </c>
       <c r="E75">
-        <v>2925.396000000001</v>
+        <v>3026.948000000001</v>
       </c>
       <c r="F75">
-        <v>7413.296</v>
+        <v>7514.848000000001</v>
       </c>
       <c r="G75">
         <v>865</v>
@@ -7443,37 +7443,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M75">
-        <v>1040.586526312291</v>
+        <v>1054.841136261774</v>
       </c>
       <c r="N75">
-        <v>-169.1395875367804</v>
+        <v>-183.3941974862638</v>
       </c>
       <c r="O75">
-        <v>-40.59350100882729</v>
+        <v>-44.01460739670331</v>
       </c>
       <c r="P75">
-        <v>-128.5460865279531</v>
+        <v>-139.3795900895605</v>
       </c>
       <c r="Q75">
-        <v>502.3539134720469</v>
+        <v>491.5204099104395</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2420401151187855</v>
+        <v>0.2495878118541233</v>
       </c>
       <c r="T75">
-        <v>2.701319050367239</v>
+        <v>2.805215936919825</v>
       </c>
       <c r="U75">
         <v>0.1403675944292917</v>
       </c>
       <c r="V75">
-        <v>0.2009897879874674</v>
+        <v>0.1982737097714205</v>
       </c>
       <c r="W75">
-        <v>0.1121551413846376</v>
+        <v>0.1125363907501059</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8374574499477808</v>
+        <v>0.8261404573809189</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1481697602371504</v>
+        <v>0.1491154361814433</v>
       </c>
       <c r="C76">
-        <v>-255.5864589119064</v>
+        <v>-404.262500814536</v>
       </c>
       <c r="D76">
-        <v>6394.261541088094</v>
+        <v>6347.137499185465</v>
       </c>
       <c r="E76">
-        <v>3026.948000000001</v>
+        <v>3128.500000000001</v>
       </c>
       <c r="F76">
-        <v>7514.848000000001</v>
+        <v>7616.400000000001</v>
       </c>
       <c r="G76">
         <v>865</v>
@@ -7525,37 +7525,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M76">
-        <v>1054.841136261774</v>
+        <v>1069.095746211257</v>
       </c>
       <c r="N76">
-        <v>-183.3941974862638</v>
+        <v>-197.6488074357472</v>
       </c>
       <c r="O76">
-        <v>-44.01460739670331</v>
+        <v>-47.43571378457933</v>
       </c>
       <c r="P76">
-        <v>-139.3795900895605</v>
+        <v>-150.2130936511679</v>
       </c>
       <c r="Q76">
-        <v>491.5204099104395</v>
+        <v>480.6869063488321</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2495878118541233</v>
+        <v>0.2577393243282883</v>
       </c>
       <c r="T76">
-        <v>2.805215936919825</v>
+        <v>2.917424574396618</v>
       </c>
       <c r="U76">
         <v>0.1403675944292917</v>
       </c>
       <c r="V76">
-        <v>0.1982737097714205</v>
+        <v>0.1956300603078016</v>
       </c>
       <c r="W76">
-        <v>0.1125363907501059</v>
+        <v>0.1129074734658283</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8261404573809189</v>
+        <v>0.8151252512825067</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1491154361814433</v>
+        <v>0.1500611121257363</v>
       </c>
       <c r="C77">
-        <v>-404.262500814536</v>
+        <v>-552.2490403432957</v>
       </c>
       <c r="D77">
-        <v>6347.137499185465</v>
+        <v>6300.702959656704</v>
       </c>
       <c r="E77">
-        <v>3128.500000000001</v>
+        <v>3230.052000000001</v>
       </c>
       <c r="F77">
-        <v>7616.400000000001</v>
+        <v>7717.952</v>
       </c>
       <c r="G77">
         <v>865</v>
@@ -7607,37 +7607,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M77">
-        <v>1069.095746211257</v>
+        <v>1083.350356160741</v>
       </c>
       <c r="N77">
-        <v>-197.6488074357472</v>
+        <v>-211.9034173852307</v>
       </c>
       <c r="O77">
-        <v>-47.43571378457933</v>
+        <v>-50.85682017245536</v>
       </c>
       <c r="P77">
-        <v>-150.2130936511679</v>
+        <v>-161.0465972127753</v>
       </c>
       <c r="Q77">
-        <v>480.6869063488321</v>
+        <v>469.8534027872247</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2577393243282883</v>
+        <v>0.2665701295086337</v>
       </c>
       <c r="T77">
-        <v>2.917424574396618</v>
+        <v>3.038983931663144</v>
       </c>
       <c r="U77">
         <v>0.1403675944292917</v>
       </c>
       <c r="V77">
-        <v>0.1956300603078016</v>
+        <v>0.1930559805669095</v>
       </c>
       <c r="W77">
-        <v>0.1129074734658283</v>
+        <v>0.1132687908469265</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8151252512825067</v>
+        <v>0.8043999190287895</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1500611121257363</v>
+        <v>0.1742449571762949</v>
       </c>
       <c r="C78">
-        <v>-552.2490403432957</v>
+        <v>-1646.80798961673</v>
       </c>
       <c r="D78">
-        <v>6300.702959656704</v>
+        <v>5307.696010383271</v>
       </c>
       <c r="E78">
-        <v>3230.052000000001</v>
+        <v>3331.604000000001</v>
       </c>
       <c r="F78">
-        <v>7717.952</v>
+        <v>7819.504000000001</v>
       </c>
       <c r="G78">
         <v>865</v>
@@ -7689,45 +7689,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M78">
-        <v>1083.350356160741</v>
+        <v>1318.114978910224</v>
       </c>
       <c r="N78">
-        <v>-211.9034173852307</v>
+        <v>-446.6680401347143</v>
       </c>
       <c r="O78">
-        <v>-50.85682017245536</v>
+        <v>-107.2003296323314</v>
       </c>
       <c r="P78">
-        <v>-161.0465972127753</v>
+        <v>-339.4677105023828</v>
       </c>
       <c r="Q78">
-        <v>469.8534027872247</v>
+        <v>291.4322894976171</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2665701295086337</v>
+        <v>0.2827956529927731</v>
       </c>
       <c r="T78">
-        <v>3.038983931663144</v>
+        <v>3.262334369790212</v>
       </c>
       <c r="U78">
-        <v>0.1403675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V78">
-        <v>0.1930559805669095</v>
+        <v>0.1586714881876532</v>
       </c>
       <c r="W78">
-        <v>0.1132687908469265</v>
+        <v>0.1418207233609832</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.8043999190287895</v>
+        <v>0.6611312007818884</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1742449571762949</v>
+        <v>0.1754726331205878</v>
       </c>
       <c r="C79">
-        <v>-1646.80798961673</v>
+        <v>-1790.487610590975</v>
       </c>
       <c r="D79">
-        <v>5307.696010383271</v>
+        <v>5265.568389409025</v>
       </c>
       <c r="E79">
-        <v>3331.604000000001</v>
+        <v>3433.156000000001</v>
       </c>
       <c r="F79">
-        <v>7819.504000000001</v>
+        <v>7921.056</v>
       </c>
       <c r="G79">
         <v>865</v>
@@ -7771,37 +7771,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M79">
-        <v>1318.114978910224</v>
+        <v>1335.233355259708</v>
       </c>
       <c r="N79">
-        <v>-446.6680401347143</v>
+        <v>-463.7864164841975</v>
       </c>
       <c r="O79">
-        <v>-107.2003296323314</v>
+        <v>-111.3087399562074</v>
       </c>
       <c r="P79">
-        <v>-339.4677105023828</v>
+        <v>-352.4776765279901</v>
       </c>
       <c r="Q79">
-        <v>291.4322894976171</v>
+        <v>278.4223234720099</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2827956529927731</v>
+        <v>0.2935681826742629</v>
       </c>
       <c r="T79">
-        <v>3.262334369790212</v>
+        <v>3.410622295689768</v>
       </c>
       <c r="U79">
         <v>0.1685675944292917</v>
       </c>
       <c r="V79">
-        <v>0.1586714881876532</v>
+        <v>0.1566372383390936</v>
       </c>
       <c r="W79">
-        <v>0.1418207233609832</v>
+        <v>0.1421636319644231</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.6611312007818884</v>
+        <v>0.6526551597462232</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1754726331205878</v>
+        <v>0.221201007874269</v>
       </c>
       <c r="C80">
-        <v>-1790.487610590975</v>
+        <v>-3093.539921371917</v>
       </c>
       <c r="D80">
-        <v>5265.568389409025</v>
+        <v>4064.068078628085</v>
       </c>
       <c r="E80">
-        <v>3433.156000000001</v>
+        <v>3534.708000000001</v>
       </c>
       <c r="F80">
-        <v>7921.056</v>
+        <v>8022.608000000001</v>
       </c>
       <c r="G80">
         <v>865</v>
@@ -7853,45 +7853,45 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M80">
-        <v>1335.233355259708</v>
+        <v>1785.572563609191</v>
       </c>
       <c r="N80">
-        <v>-463.7864164841975</v>
+        <v>-914.1256248336812</v>
       </c>
       <c r="O80">
-        <v>-111.3087399562074</v>
+        <v>-219.3901499600835</v>
       </c>
       <c r="P80">
-        <v>-352.4776765279901</v>
+        <v>-694.7354748735977</v>
       </c>
       <c r="Q80">
-        <v>278.4223234720099</v>
+        <v>-63.83547487359772</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2935681826742629</v>
+        <v>0.3141318999891718</v>
       </c>
       <c r="T80">
-        <v>3.410622295689768</v>
+        <v>3.693689604815152</v>
       </c>
       <c r="U80">
-        <v>0.1685675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V80">
-        <v>0.1566372383390936</v>
+        <v>0.1171317646611748</v>
       </c>
       <c r="W80">
-        <v>0.1421636319644231</v>
+        <v>0.1964978593373961</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.6526551597462232</v>
+        <v>0.4880490194215619</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.221201007874269</v>
+        <v>0.2229686838185619</v>
       </c>
       <c r="C81">
-        <v>-3093.539921371917</v>
+        <v>-3230.625796394244</v>
       </c>
       <c r="D81">
-        <v>4064.068078628085</v>
+        <v>4028.534203605756</v>
       </c>
       <c r="E81">
-        <v>3534.708000000001</v>
+        <v>3636.260000000001</v>
       </c>
       <c r="F81">
-        <v>8022.608000000001</v>
+        <v>8124.160000000001</v>
       </c>
       <c r="G81">
         <v>865</v>
@@ -7935,37 +7935,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M81">
-        <v>1785.572563609191</v>
+        <v>1808.174747958675</v>
       </c>
       <c r="N81">
-        <v>-914.1256248336812</v>
+        <v>-936.7278091831644</v>
       </c>
       <c r="O81">
-        <v>-219.3901499600835</v>
+        <v>-224.8146742039594</v>
       </c>
       <c r="P81">
-        <v>-694.7354748735977</v>
+        <v>-711.9131349792049</v>
       </c>
       <c r="Q81">
-        <v>-63.83547487359772</v>
+        <v>-81.01313497920489</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3141318999891718</v>
+        <v>0.3275484949886304</v>
       </c>
       <c r="T81">
-        <v>3.693689604815152</v>
+        <v>3.878374085055909</v>
       </c>
       <c r="U81">
         <v>0.2225675944292917</v>
       </c>
       <c r="V81">
-        <v>0.1171317646611748</v>
+        <v>0.1156676176029102</v>
       </c>
       <c r="W81">
-        <v>0.1964978593373961</v>
+        <v>0.1968237310260448</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4880490194215619</v>
+        <v>0.4819484066787924</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2229686838185619</v>
+        <v>0.2247363597628548</v>
       </c>
       <c r="C82">
-        <v>-3230.625796394244</v>
+        <v>-3367.095681723729</v>
       </c>
       <c r="D82">
-        <v>4028.534203605756</v>
+        <v>3993.616318276272</v>
       </c>
       <c r="E82">
-        <v>3636.260000000001</v>
+        <v>3737.812000000002</v>
       </c>
       <c r="F82">
-        <v>8124.160000000001</v>
+        <v>8225.712000000001</v>
       </c>
       <c r="G82">
         <v>865</v>
@@ -8017,37 +8017,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M82">
-        <v>1808.174747958675</v>
+        <v>1830.776932308158</v>
       </c>
       <c r="N82">
-        <v>-936.7278091831644</v>
+        <v>-959.329993532648</v>
       </c>
       <c r="O82">
-        <v>-224.8146742039594</v>
+        <v>-230.2391984478355</v>
       </c>
       <c r="P82">
-        <v>-711.9131349792049</v>
+        <v>-729.0907950848125</v>
       </c>
       <c r="Q82">
-        <v>-81.01313497920489</v>
+        <v>-98.19079508481252</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3275484949886304</v>
+        <v>0.3423773631459268</v>
       </c>
       <c r="T82">
-        <v>3.878374085055909</v>
+        <v>4.082499036900957</v>
       </c>
       <c r="U82">
         <v>0.2225675944292917</v>
       </c>
       <c r="V82">
-        <v>0.1156676176029102</v>
+        <v>0.1142396223238619</v>
       </c>
       <c r="W82">
-        <v>0.1968237310260448</v>
+        <v>0.1971415565001589</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4819484066787924</v>
+        <v>0.4759984263494245</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2247363597628548</v>
+        <v>0.2265040357071477</v>
       </c>
       <c r="C83">
-        <v>-3367.095681723729</v>
+        <v>-3502.965457250419</v>
       </c>
       <c r="D83">
-        <v>3993.616318276272</v>
+        <v>3959.298542749582</v>
       </c>
       <c r="E83">
-        <v>3737.812000000002</v>
+        <v>3839.364000000001</v>
       </c>
       <c r="F83">
-        <v>8225.712000000001</v>
+        <v>8327.264000000001</v>
       </c>
       <c r="G83">
         <v>865</v>
@@ -8099,37 +8099,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M83">
-        <v>1830.776932308158</v>
+        <v>1853.379116657642</v>
       </c>
       <c r="N83">
-        <v>-959.329993532648</v>
+        <v>-981.9321778821314</v>
       </c>
       <c r="O83">
-        <v>-230.2391984478355</v>
+        <v>-235.6637226917115</v>
       </c>
       <c r="P83">
-        <v>-729.0907950848125</v>
+        <v>-746.2684551904199</v>
       </c>
       <c r="Q83">
-        <v>-98.19079508481252</v>
+        <v>-115.3684551904199</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3423773631459268</v>
+        <v>0.3588538833207005</v>
       </c>
       <c r="T83">
-        <v>4.082499036900957</v>
+        <v>4.309304538951011</v>
       </c>
       <c r="U83">
         <v>0.2225675944292917</v>
       </c>
       <c r="V83">
-        <v>0.1142396223238619</v>
+        <v>0.1128464561979611</v>
       </c>
       <c r="W83">
-        <v>0.1971415565001589</v>
+        <v>0.197451630133441</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4759984263494245</v>
+        <v>0.4701935674915046</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2265040357071477</v>
+        <v>0.2282717116514406</v>
       </c>
       <c r="C84">
-        <v>-3502.965457250419</v>
+        <v>-3638.250461681218</v>
       </c>
       <c r="D84">
-        <v>3959.298542749582</v>
+        <v>3925.565538318783</v>
       </c>
       <c r="E84">
-        <v>3839.364000000001</v>
+        <v>3940.916000000001</v>
       </c>
       <c r="F84">
-        <v>8327.264000000001</v>
+        <v>8428.816000000001</v>
       </c>
       <c r="G84">
         <v>865</v>
@@ -8181,37 +8181,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M84">
-        <v>1853.379116657642</v>
+        <v>1875.981301007125</v>
       </c>
       <c r="N84">
-        <v>-981.9321778821314</v>
+        <v>-1004.534362231615</v>
       </c>
       <c r="O84">
-        <v>-235.6637226917115</v>
+        <v>-241.0882469355875</v>
       </c>
       <c r="P84">
-        <v>-746.2684551904199</v>
+        <v>-763.4461152960271</v>
       </c>
       <c r="Q84">
-        <v>-115.3684551904199</v>
+        <v>-132.5461152960271</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3588538833207005</v>
+        <v>0.3772688176336828</v>
       </c>
       <c r="T84">
-        <v>4.309304538951011</v>
+        <v>4.562793041242246</v>
       </c>
       <c r="U84">
         <v>0.2225675944292917</v>
       </c>
       <c r="V84">
-        <v>0.1128464561979611</v>
+        <v>0.1114868603401544</v>
       </c>
       <c r="W84">
-        <v>0.197451630133441</v>
+        <v>0.1977542321129091</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4701935674915046</v>
+        <v>0.4645285847506433</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2282717116514406</v>
+        <v>0.2300393875957336</v>
       </c>
       <c r="C85">
-        <v>-3638.250461681218</v>
+        <v>-3772.965515399394</v>
       </c>
       <c r="D85">
-        <v>3925.565538318783</v>
+        <v>3892.402484600609</v>
       </c>
       <c r="E85">
-        <v>3940.916000000001</v>
+        <v>4042.468000000003</v>
       </c>
       <c r="F85">
-        <v>8428.816000000001</v>
+        <v>8530.368000000002</v>
       </c>
       <c r="G85">
         <v>865</v>
@@ -8263,37 +8263,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M85">
-        <v>1875.981301007125</v>
+        <v>1898.583485356609</v>
       </c>
       <c r="N85">
-        <v>-1004.534362231615</v>
+        <v>-1027.136546581099</v>
       </c>
       <c r="O85">
-        <v>-241.0882469355875</v>
+        <v>-246.5127711794637</v>
       </c>
       <c r="P85">
-        <v>-763.4461152960271</v>
+        <v>-780.6237754016349</v>
       </c>
       <c r="Q85">
-        <v>-132.5461152960271</v>
+        <v>-149.723775401635</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3772688176336828</v>
+        <v>0.3979856187357882</v>
       </c>
       <c r="T85">
-        <v>4.562793041242246</v>
+        <v>4.847967606319889</v>
       </c>
       <c r="U85">
         <v>0.2225675944292917</v>
       </c>
       <c r="V85">
-        <v>0.1114868603401544</v>
+        <v>0.1101596358122954</v>
       </c>
       <c r="W85">
-        <v>0.1977542321129091</v>
+        <v>0.1980496292833423</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4645285847506433</v>
+        <v>0.4589984825512307</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2300393875957336</v>
+        <v>0.2318070635400264</v>
       </c>
       <c r="C86">
-        <v>-3772.965515399392</v>
+        <v>-3907.124942175052</v>
       </c>
       <c r="D86">
-        <v>3892.402484600609</v>
+        <v>3859.795057824948</v>
       </c>
       <c r="E86">
-        <v>4042.468000000001</v>
+        <v>4144.02</v>
       </c>
       <c r="F86">
-        <v>8530.368</v>
+        <v>8631.92</v>
       </c>
       <c r="G86">
         <v>865</v>
@@ -8345,37 +8345,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M86">
-        <v>1898.583485356608</v>
+        <v>1921.185669706092</v>
       </c>
       <c r="N86">
-        <v>-1027.136546581098</v>
+        <v>-1049.738730930581</v>
       </c>
       <c r="O86">
-        <v>-246.5127711794636</v>
+        <v>-251.9372954233395</v>
       </c>
       <c r="P86">
-        <v>-780.6237754016346</v>
+        <v>-797.8014355072419</v>
       </c>
       <c r="Q86">
-        <v>-149.7237754016346</v>
+        <v>-166.9014355072419</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3979856187357879</v>
+        <v>0.4214646599848404</v>
       </c>
       <c r="T86">
-        <v>4.847967606319885</v>
+        <v>5.17116544674121</v>
       </c>
       <c r="U86">
         <v>0.2225675944292917</v>
       </c>
       <c r="V86">
-        <v>0.1101596358122954</v>
+        <v>0.1088636400968566</v>
       </c>
       <c r="W86">
-        <v>0.1980496292833423</v>
+        <v>0.1983380759321181</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4589984825512308</v>
+        <v>0.4535985004035693</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2318070635400264</v>
+        <v>0.2335747394843194</v>
       </c>
       <c r="C87">
-        <v>-3907.124942175052</v>
+        <v>-4040.742589793495</v>
       </c>
       <c r="D87">
-        <v>3859.795057824948</v>
+        <v>3827.729410206505</v>
       </c>
       <c r="E87">
-        <v>4144.02</v>
+        <v>4245.572</v>
       </c>
       <c r="F87">
-        <v>8631.92</v>
+        <v>8733.472</v>
       </c>
       <c r="G87">
         <v>865</v>
@@ -8427,37 +8427,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M87">
-        <v>1921.185669706092</v>
+        <v>1943.787854055575</v>
       </c>
       <c r="N87">
-        <v>-1049.738730930581</v>
+        <v>-1072.340915280065</v>
       </c>
       <c r="O87">
-        <v>-251.9372954233395</v>
+        <v>-257.3618196672155</v>
       </c>
       <c r="P87">
-        <v>-797.8014355072419</v>
+        <v>-814.9790956128491</v>
       </c>
       <c r="Q87">
-        <v>-166.9014355072419</v>
+        <v>-184.0790956128491</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4214646599848404</v>
+        <v>0.4482978499837576</v>
       </c>
       <c r="T87">
-        <v>5.17116544674121</v>
+        <v>5.540534407222726</v>
       </c>
       <c r="U87">
         <v>0.2225675944292917</v>
       </c>
       <c r="V87">
-        <v>0.1088636400968566</v>
+        <v>0.1075977838166606</v>
       </c>
       <c r="W87">
-        <v>0.1983380759321181</v>
+        <v>0.1986198145192946</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4535985004035693</v>
+        <v>0.4483240992360861</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2335747394843194</v>
+        <v>0.2353424154286123</v>
       </c>
       <c r="C88">
-        <v>-4040.742589793495</v>
+        <v>-4173.831849663758</v>
       </c>
       <c r="D88">
-        <v>3827.729410206505</v>
+        <v>3796.192150336242</v>
       </c>
       <c r="E88">
-        <v>4245.572</v>
+        <v>4347.124000000002</v>
       </c>
       <c r="F88">
-        <v>8733.472</v>
+        <v>8835.024000000001</v>
       </c>
       <c r="G88">
         <v>865</v>
@@ -8509,37 +8509,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M88">
-        <v>1943.787854055575</v>
+        <v>1966.390038405059</v>
       </c>
       <c r="N88">
-        <v>-1072.340915280065</v>
+        <v>-1094.943099629549</v>
       </c>
       <c r="O88">
-        <v>-257.3618196672155</v>
+        <v>-262.7863439110916</v>
       </c>
       <c r="P88">
-        <v>-814.9790956128491</v>
+        <v>-832.156755718457</v>
       </c>
       <c r="Q88">
-        <v>-184.0790956128491</v>
+        <v>-201.256755718457</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4482978499837576</v>
+        <v>0.4792592230594312</v>
       </c>
       <c r="T88">
-        <v>5.540534407222726</v>
+        <v>5.966729361624474</v>
       </c>
       <c r="U88">
         <v>0.2225675944292917</v>
       </c>
       <c r="V88">
-        <v>0.1075977838166606</v>
+        <v>0.1063610276808369</v>
       </c>
       <c r="W88">
-        <v>0.1986198145192946</v>
+        <v>0.1988950763573405</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4483240992360861</v>
+        <v>0.4431709486701538</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2353424154286123</v>
+        <v>0.2371100913729052</v>
       </c>
       <c r="C89">
-        <v>-4173.831849663758</v>
+        <v>-4306.405675465762</v>
       </c>
       <c r="D89">
-        <v>3796.192150336242</v>
+        <v>3765.170324534239</v>
       </c>
       <c r="E89">
-        <v>4347.124000000002</v>
+        <v>4448.676000000001</v>
       </c>
       <c r="F89">
-        <v>8835.024000000001</v>
+        <v>8936.576000000001</v>
       </c>
       <c r="G89">
         <v>865</v>
@@ -8591,37 +8591,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M89">
-        <v>1966.390038405059</v>
+        <v>1988.992222754542</v>
       </c>
       <c r="N89">
-        <v>-1094.943099629549</v>
+        <v>-1117.545283979032</v>
       </c>
       <c r="O89">
-        <v>-262.7863439110916</v>
+        <v>-268.2108681549676</v>
       </c>
       <c r="P89">
-        <v>-832.156755718457</v>
+        <v>-849.3344158240643</v>
       </c>
       <c r="Q89">
-        <v>-201.256755718457</v>
+        <v>-218.4344158240643</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4792592230594312</v>
+        <v>0.5153808249810505</v>
       </c>
       <c r="T89">
-        <v>5.966729361624474</v>
+        <v>6.463956808426515</v>
       </c>
       <c r="U89">
         <v>0.2225675944292917</v>
       </c>
       <c r="V89">
-        <v>0.1063610276808369</v>
+        <v>0.1051523796390092</v>
       </c>
       <c r="W89">
-        <v>0.1988950763573405</v>
+        <v>0.1991640822445218</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4431709486701538</v>
+        <v>0.4381349151625386</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2371100913729052</v>
+        <v>0.2388777673171981</v>
       </c>
       <c r="C90">
-        <v>-4306.405675465762</v>
+        <v>-4438.476600890579</v>
       </c>
       <c r="D90">
-        <v>3765.170324534239</v>
+        <v>3734.651399109422</v>
       </c>
       <c r="E90">
-        <v>4448.676000000001</v>
+        <v>4550.228000000001</v>
       </c>
       <c r="F90">
-        <v>8936.576000000001</v>
+        <v>9038.128000000001</v>
       </c>
       <c r="G90">
         <v>865</v>
@@ -8673,37 +8673,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M90">
-        <v>1988.992222754542</v>
+        <v>2011.594407104025</v>
       </c>
       <c r="N90">
-        <v>-1117.545283979032</v>
+        <v>-1140.147468328515</v>
       </c>
       <c r="O90">
-        <v>-268.2108681549676</v>
+        <v>-273.6353923988436</v>
       </c>
       <c r="P90">
-        <v>-849.3344158240643</v>
+        <v>-866.5120759296715</v>
       </c>
       <c r="Q90">
-        <v>-218.4344158240643</v>
+        <v>-235.6120759296715</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5153808249810505</v>
+        <v>0.5580699908884188</v>
       </c>
       <c r="T90">
-        <v>6.463956808426515</v>
+        <v>7.051589245556198</v>
       </c>
       <c r="U90">
         <v>0.2225675944292917</v>
       </c>
       <c r="V90">
-        <v>0.1051523796390092</v>
+        <v>0.103970892227335</v>
       </c>
       <c r="W90">
-        <v>0.1991640822445218</v>
+        <v>0.1994270430555866</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4381349151625386</v>
+        <v>0.4332120509472291</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2388777673171981</v>
+        <v>0.2406454432614911</v>
       </c>
       <c r="C91">
-        <v>-4438.476600890579</v>
+        <v>-4570.056756524853</v>
       </c>
       <c r="D91">
-        <v>3734.651399109422</v>
+        <v>3704.623243475147</v>
       </c>
       <c r="E91">
-        <v>4550.228000000001</v>
+        <v>4651.780000000001</v>
       </c>
       <c r="F91">
-        <v>9038.128000000001</v>
+        <v>9139.68</v>
       </c>
       <c r="G91">
         <v>865</v>
@@ -8755,37 +8755,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M91">
-        <v>2011.594407104025</v>
+        <v>2034.196591453509</v>
       </c>
       <c r="N91">
-        <v>-1140.147468328515</v>
+        <v>-1162.749652677999</v>
       </c>
       <c r="O91">
-        <v>-273.6353923988436</v>
+        <v>-279.0599166427197</v>
       </c>
       <c r="P91">
-        <v>-866.5120759296715</v>
+        <v>-883.6897360352791</v>
       </c>
       <c r="Q91">
-        <v>-235.6120759296715</v>
+        <v>-252.7897360352791</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5580699908884188</v>
+        <v>0.6092969899772608</v>
       </c>
       <c r="T91">
-        <v>7.051589245556198</v>
+        <v>7.756748170111819</v>
       </c>
       <c r="U91">
         <v>0.2225675944292917</v>
       </c>
       <c r="V91">
-        <v>0.103970892227335</v>
+        <v>0.1028156600914757</v>
       </c>
       <c r="W91">
-        <v>0.1994270430555866</v>
+        <v>0.1996841602930722</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4332120509472291</v>
+        <v>0.428398583714482</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2406454432614911</v>
+        <v>0.242413119205784</v>
       </c>
       <c r="C92">
-        <v>-4570.056756524853</v>
+        <v>-4701.157885927181</v>
       </c>
       <c r="D92">
-        <v>3704.623243475147</v>
+        <v>3675.074114072821</v>
       </c>
       <c r="E92">
-        <v>4651.780000000001</v>
+        <v>4753.332000000002</v>
       </c>
       <c r="F92">
-        <v>9139.68</v>
+        <v>9241.232000000002</v>
       </c>
       <c r="G92">
         <v>865</v>
@@ -8837,37 +8837,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M92">
-        <v>2034.196591453509</v>
+        <v>2056.798775802993</v>
       </c>
       <c r="N92">
-        <v>-1162.749652677999</v>
+        <v>-1185.351837027482</v>
       </c>
       <c r="O92">
-        <v>-279.0599166427197</v>
+        <v>-284.4844408865957</v>
       </c>
       <c r="P92">
-        <v>-883.6897360352791</v>
+        <v>-900.8673961408866</v>
       </c>
       <c r="Q92">
-        <v>-252.7897360352791</v>
+        <v>-269.9673961408866</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6092969899772608</v>
+        <v>0.6719077666414009</v>
       </c>
       <c r="T92">
-        <v>7.756748170111819</v>
+        <v>8.618609077902022</v>
       </c>
       <c r="U92">
         <v>0.2225675944292917</v>
       </c>
       <c r="V92">
-        <v>0.1028156600914757</v>
+        <v>0.101685817672888</v>
       </c>
       <c r="W92">
-        <v>0.1996841602930722</v>
+        <v>0.1999356266022614</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.428398583714482</v>
+        <v>0.4236909069703669</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.242413119205784</v>
+        <v>0.2441807951500769</v>
       </c>
       <c r="C93">
-        <v>-4701.157885927181</v>
+        <v>-4831.791360941199</v>
       </c>
       <c r="D93">
-        <v>3675.074114072821</v>
+        <v>3645.992639058803</v>
       </c>
       <c r="E93">
-        <v>4753.332000000002</v>
+        <v>4854.884000000002</v>
       </c>
       <c r="F93">
-        <v>9241.232000000002</v>
+        <v>9342.784000000001</v>
       </c>
       <c r="G93">
         <v>865</v>
@@ -8919,37 +8919,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M93">
-        <v>2056.798775802993</v>
+        <v>2079.400960152476</v>
       </c>
       <c r="N93">
-        <v>-1185.351837027482</v>
+        <v>-1207.954021376966</v>
       </c>
       <c r="O93">
-        <v>-284.4844408865957</v>
+        <v>-289.9089651304717</v>
       </c>
       <c r="P93">
-        <v>-900.8673961408866</v>
+        <v>-918.0450562464939</v>
       </c>
       <c r="Q93">
-        <v>-269.9673961408866</v>
+        <v>-287.1450562464939</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6719077666414009</v>
+        <v>0.7501712374715762</v>
       </c>
       <c r="T93">
-        <v>8.618609077902022</v>
+        <v>9.695935212639776</v>
       </c>
       <c r="U93">
         <v>0.2225675944292917</v>
       </c>
       <c r="V93">
-        <v>0.101685817672888</v>
+        <v>0.1005805370460088</v>
       </c>
       <c r="W93">
-        <v>0.1999356266022614</v>
+        <v>0.2001816262525552</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4236909069703669</v>
+        <v>0.4190855710250369</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2441807951500769</v>
+        <v>0.2459484710943698</v>
       </c>
       <c r="C94">
-        <v>-4831.791360941199</v>
+        <v>-4961.968196287336</v>
       </c>
       <c r="D94">
-        <v>3645.992639058803</v>
+        <v>3617.367803712664</v>
       </c>
       <c r="E94">
-        <v>4854.884000000002</v>
+        <v>4956.436000000002</v>
       </c>
       <c r="F94">
-        <v>9342.784000000001</v>
+        <v>9444.336000000001</v>
       </c>
       <c r="G94">
         <v>865</v>
@@ -9001,37 +9001,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M94">
-        <v>2079.400960152476</v>
+        <v>2102.003144501959</v>
       </c>
       <c r="N94">
-        <v>-1207.954021376966</v>
+        <v>-1230.556205726449</v>
       </c>
       <c r="O94">
-        <v>-289.9089651304717</v>
+        <v>-295.3334893743478</v>
       </c>
       <c r="P94">
-        <v>-918.0450562464939</v>
+        <v>-935.2227163521014</v>
       </c>
       <c r="Q94">
-        <v>-287.1450562464939</v>
+        <v>-304.3227163521015</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7501712374715762</v>
+        <v>0.8507956999675158</v>
       </c>
       <c r="T94">
-        <v>9.695935212639776</v>
+        <v>11.08106881444546</v>
       </c>
       <c r="U94">
         <v>0.2225675944292917</v>
       </c>
       <c r="V94">
-        <v>0.1005805370460088</v>
+        <v>0.09949902589497646</v>
       </c>
       <c r="W94">
-        <v>0.2001816262525552</v>
+        <v>0.200422335587789</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4190855710250369</v>
+        <v>0.4145792745624021</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2459484710943698</v>
+        <v>0.2477161470386627</v>
       </c>
       <c r="C95">
-        <v>-4961.968196287336</v>
+        <v>-5091.699063472544</v>
       </c>
       <c r="D95">
-        <v>3617.367803712664</v>
+        <v>3589.188936527457</v>
       </c>
       <c r="E95">
-        <v>4956.436000000002</v>
+        <v>5057.988000000001</v>
       </c>
       <c r="F95">
-        <v>9444.336000000001</v>
+        <v>9545.888000000001</v>
       </c>
       <c r="G95">
         <v>865</v>
@@ -9083,37 +9083,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M95">
-        <v>2102.003144501959</v>
+        <v>2124.605328851443</v>
       </c>
       <c r="N95">
-        <v>-1230.556205726449</v>
+        <v>-1253.158390075932</v>
       </c>
       <c r="O95">
-        <v>-295.3334893743478</v>
+        <v>-300.7580136182237</v>
       </c>
       <c r="P95">
-        <v>-935.2227163521014</v>
+        <v>-952.4003764577087</v>
       </c>
       <c r="Q95">
-        <v>-304.3227163521015</v>
+        <v>-321.5003764577087</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8507956999675158</v>
+        <v>0.984961649962102</v>
       </c>
       <c r="T95">
-        <v>11.08106881444546</v>
+        <v>12.92791361685304</v>
       </c>
       <c r="U95">
         <v>0.2225675944292917</v>
       </c>
       <c r="V95">
-        <v>0.09949902589497646</v>
+        <v>0.09844052561949801</v>
       </c>
       <c r="W95">
-        <v>0.200422335587789</v>
+        <v>0.2006579234478049</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4145792745624021</v>
+        <v>0.4101688567479084</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2477161470386627</v>
+        <v>0.2494838229829557</v>
       </c>
       <c r="C96">
-        <v>-5091.699063472544</v>
+        <v>-5220.994304054927</v>
       </c>
       <c r="D96">
-        <v>3589.188936527457</v>
+        <v>3561.445695945074</v>
       </c>
       <c r="E96">
-        <v>5057.988000000001</v>
+        <v>5159.540000000001</v>
       </c>
       <c r="F96">
-        <v>9545.888000000001</v>
+        <v>9647.440000000001</v>
       </c>
       <c r="G96">
         <v>865</v>
@@ -9165,37 +9165,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M96">
-        <v>2124.605328851443</v>
+        <v>2147.207513200926</v>
       </c>
       <c r="N96">
-        <v>-1253.158390075932</v>
+        <v>-1275.760574425416</v>
       </c>
       <c r="O96">
-        <v>-300.7580136182237</v>
+        <v>-306.1825378620997</v>
       </c>
       <c r="P96">
-        <v>-952.4003764577087</v>
+        <v>-969.5780365633159</v>
       </c>
       <c r="Q96">
-        <v>-321.5003764577087</v>
+        <v>-338.6780365633159</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.984961649962102</v>
+        <v>1.172793979954523</v>
       </c>
       <c r="T96">
-        <v>12.92791361685304</v>
+        <v>15.51349634022366</v>
       </c>
       <c r="U96">
         <v>0.2225675944292917</v>
       </c>
       <c r="V96">
-        <v>0.09844052561949801</v>
+        <v>0.0974043095603454</v>
       </c>
       <c r="W96">
-        <v>0.2006579234478049</v>
+        <v>0.2008885515633995</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4101688567479084</v>
+        <v>0.4058512898347726</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2494838229829557</v>
+        <v>0.2512514989272486</v>
       </c>
       <c r="C97">
-        <v>-5220.994304054927</v>
+        <v>-5349.863942297911</v>
       </c>
       <c r="D97">
-        <v>3561.445695945074</v>
+        <v>3534.128057702091</v>
       </c>
       <c r="E97">
-        <v>5159.540000000001</v>
+        <v>5261.092000000002</v>
       </c>
       <c r="F97">
-        <v>9647.440000000001</v>
+        <v>9748.992000000002</v>
       </c>
       <c r="G97">
         <v>865</v>
@@ -9247,37 +9247,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M97">
-        <v>2147.207513200926</v>
+        <v>2169.80969755041</v>
       </c>
       <c r="N97">
-        <v>-1275.760574425416</v>
+        <v>-1298.362758774899</v>
       </c>
       <c r="O97">
-        <v>-306.1825378620997</v>
+        <v>-311.6070621059758</v>
       </c>
       <c r="P97">
-        <v>-969.5780365633159</v>
+        <v>-986.7556966689235</v>
       </c>
       <c r="Q97">
-        <v>-338.6780365633159</v>
+        <v>-355.8556966689235</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.172793979954523</v>
+        <v>1.454542474943155</v>
       </c>
       <c r="T97">
-        <v>15.51349634022366</v>
+        <v>19.39187042527958</v>
       </c>
       <c r="U97">
         <v>0.2225675944292917</v>
       </c>
       <c r="V97">
-        <v>0.0974043095603454</v>
+        <v>0.09638968133575847</v>
       </c>
       <c r="W97">
-        <v>0.2008885515633995</v>
+        <v>0.2011143749265859</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4058512898347726</v>
+        <v>0.401623672232327</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2512514989272486</v>
+        <v>0.2530191748715415</v>
       </c>
       <c r="C98">
-        <v>-5349.863942297909</v>
+        <v>-5478.317697246463</v>
       </c>
       <c r="D98">
-        <v>3534.128057702091</v>
+        <v>3507.226302753537</v>
       </c>
       <c r="E98">
-        <v>5261.092000000001</v>
+        <v>5362.644</v>
       </c>
       <c r="F98">
-        <v>9748.992</v>
+        <v>9850.544</v>
       </c>
       <c r="G98">
         <v>865</v>
@@ -9329,37 +9329,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M98">
-        <v>2169.80969755041</v>
+        <v>2192.411881899893</v>
       </c>
       <c r="N98">
-        <v>-1298.362758774899</v>
+        <v>-1320.964943124382</v>
       </c>
       <c r="O98">
-        <v>-311.6070621059758</v>
+        <v>-317.0315863498518</v>
       </c>
       <c r="P98">
-        <v>-986.7556966689235</v>
+        <v>-1003.933356774531</v>
       </c>
       <c r="Q98">
-        <v>-355.8556966689235</v>
+        <v>-373.0333567745307</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.454542474943151</v>
+        <v>1.924123299924201</v>
       </c>
       <c r="T98">
-        <v>19.39187042527953</v>
+        <v>25.85582723370604</v>
       </c>
       <c r="U98">
         <v>0.2225675944292917</v>
       </c>
       <c r="V98">
-        <v>0.09638968133575847</v>
+        <v>0.09539597328075065</v>
       </c>
       <c r="W98">
-        <v>0.2011143749265859</v>
+        <v>0.201335542137954</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.401623672232327</v>
+        <v>0.3974832220031278</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2530191748715415</v>
+        <v>0.2547868508158344</v>
       </c>
       <c r="C99">
-        <v>-5478.317697246463</v>
+        <v>-5606.364994255948</v>
       </c>
       <c r="D99">
-        <v>3507.226302753537</v>
+        <v>3480.731005744054</v>
       </c>
       <c r="E99">
-        <v>5362.644</v>
+        <v>5464.196000000002</v>
       </c>
       <c r="F99">
-        <v>9850.544</v>
+        <v>9952.096000000001</v>
       </c>
       <c r="G99">
         <v>865</v>
@@ -9411,37 +9411,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M99">
-        <v>2192.411881899893</v>
+        <v>2215.014066249376</v>
       </c>
       <c r="N99">
-        <v>-1320.964943124382</v>
+        <v>-1343.567127473866</v>
       </c>
       <c r="O99">
-        <v>-317.0315863498518</v>
+        <v>-322.4561105937278</v>
       </c>
       <c r="P99">
-        <v>-1003.933356774531</v>
+        <v>-1021.111016880138</v>
       </c>
       <c r="Q99">
-        <v>-373.0333567745307</v>
+        <v>-390.2110168801383</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.924123299924201</v>
+        <v>2.863284949886301</v>
       </c>
       <c r="T99">
-        <v>25.85582723370604</v>
+        <v>38.78374085055906</v>
       </c>
       <c r="U99">
         <v>0.2225675944292917</v>
       </c>
       <c r="V99">
-        <v>0.09539597328075065</v>
+        <v>0.09442254498196748</v>
       </c>
       <c r="W99">
-        <v>0.201335542137954</v>
+        <v>0.2015521957327636</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3974832220031278</v>
+        <v>0.3934272707581978</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2547868508158344</v>
+        <v>0.2565545267601274</v>
       </c>
       <c r="C100">
-        <v>-5606.364994255948</v>
+        <v>-5734.014976002298</v>
       </c>
       <c r="D100">
-        <v>3480.731005744054</v>
+        <v>3454.633023997703</v>
       </c>
       <c r="E100">
-        <v>5464.196000000002</v>
+        <v>5565.748000000001</v>
       </c>
       <c r="F100">
-        <v>9952.096000000001</v>
+        <v>10053.648</v>
       </c>
       <c r="G100">
         <v>865</v>
@@ -9493,37 +9493,37 @@
         <v>871.4469387755101</v>
       </c>
       <c r="M100">
-        <v>2215.014066249376</v>
+        <v>2237.61625059886</v>
       </c>
       <c r="N100">
-        <v>-1343.567127473866</v>
+        <v>-1366.16931182335</v>
       </c>
       <c r="O100">
-        <v>-322.4561105937278</v>
+        <v>-327.8806348376039</v>
       </c>
       <c r="P100">
-        <v>-1021.111016880138</v>
+        <v>-1038.288676985746</v>
       </c>
       <c r="Q100">
-        <v>-390.2110168801383</v>
+        <v>-407.388676985746</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.863284949886301</v>
+        <v>5.680769899772601</v>
       </c>
       <c r="T100">
-        <v>38.78374085055906</v>
+        <v>77.5674817011181</v>
       </c>
       <c r="U100">
         <v>0.2225675944292917</v>
       </c>
       <c r="V100">
-        <v>0.09442254498196748</v>
+        <v>0.09346878190134153</v>
       </c>
       <c r="W100">
-        <v>0.2015521957327636</v>
+        <v>0.201764472487274</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3934272707581978</v>
+        <v>0.3894532579222565</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2565545267601274</v>
-      </c>
-      <c r="C101">
-        <v>-5734.014976002298</v>
-      </c>
-      <c r="D101">
-        <v>3454.633023997703</v>
-      </c>
-      <c r="E101">
-        <v>5565.748000000001</v>
-      </c>
-      <c r="F101">
-        <v>10053.648</v>
-      </c>
-      <c r="G101">
-        <v>865</v>
-      </c>
-      <c r="H101">
-        <v>5667.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1502.34693877551</v>
-      </c>
-      <c r="K101">
-        <v>630.9</v>
-      </c>
-      <c r="L101">
-        <v>871.4469387755101</v>
-      </c>
-      <c r="M101">
-        <v>2237.61625059886</v>
-      </c>
-      <c r="N101">
-        <v>-1366.16931182335</v>
-      </c>
-      <c r="O101">
-        <v>-327.8806348376039</v>
-      </c>
-      <c r="P101">
-        <v>-1038.288676985746</v>
-      </c>
-      <c r="Q101">
-        <v>-407.388676985746</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.680769899772601</v>
-      </c>
-      <c r="T101">
-        <v>77.5674817011181</v>
-      </c>
-      <c r="U101">
-        <v>0.2225675944292917</v>
-      </c>
-      <c r="V101">
-        <v>0.09346878190134153</v>
-      </c>
-      <c r="W101">
-        <v>0.201764472487274</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3894532579222565</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
